--- a/sites.xlsx
+++ b/sites.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1370" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1369" uniqueCount="274">
   <si>
     <t>site_name</t>
   </si>
@@ -808,6 +808,9 @@
     <t>NO_NEW</t>
   </si>
   <si>
+    <t>FAIL</t>
+  </si>
+  <si>
     <t>STEP2-3</t>
   </si>
   <si>
@@ -830,6 +833,9 @@
   </si>
   <si>
     <t>PRIMARY_PARSER</t>
+  </si>
+  <si>
+    <t>selenium:detail_date</t>
   </si>
 </sst>
 </file>
@@ -1308,16 +1314,16 @@
         <v>257</v>
       </c>
       <c r="O2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W2" s="2">
         <v>46155</v>
@@ -1370,16 +1376,16 @@
         <v>257</v>
       </c>
       <c r="O3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W3" s="2">
         <v>46087</v>
@@ -1432,16 +1438,16 @@
         <v>257</v>
       </c>
       <c r="O4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W4" s="2">
         <v>46168</v>
@@ -1494,16 +1500,16 @@
         <v>257</v>
       </c>
       <c r="O5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P5" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R5" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W5" s="2">
         <v>46161</v>
@@ -1547,7 +1553,7 @@
         <v>169</v>
       </c>
       <c r="L6" s="2">
-        <v>46268.26371527778</v>
+        <v>46274.20061342593</v>
       </c>
       <c r="M6" t="s">
         <v>263</v>
@@ -1556,16 +1562,16 @@
         <v>256</v>
       </c>
       <c r="O6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W6" s="2">
         <v>46168</v>
@@ -1627,16 +1633,16 @@
         <v>257</v>
       </c>
       <c r="O7" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P7" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q7" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R7" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W7" s="2">
         <v>46164</v>
@@ -1689,16 +1695,16 @@
         <v>257</v>
       </c>
       <c r="O8" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P8" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q8" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R8" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W8" s="2">
         <v>46155</v>
@@ -1751,16 +1757,16 @@
         <v>257</v>
       </c>
       <c r="O9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W9" s="2">
         <v>46045</v>
@@ -1813,16 +1819,16 @@
         <v>257</v>
       </c>
       <c r="O10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P10" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R10" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W10" s="2">
         <v>46045</v>
@@ -1875,16 +1881,16 @@
         <v>257</v>
       </c>
       <c r="O11" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P11" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q11" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R11" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W11" s="2">
         <v>46129</v>
@@ -1937,16 +1943,16 @@
         <v>257</v>
       </c>
       <c r="O12" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P12" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q12" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R12" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W12" s="2">
         <v>46164</v>
@@ -1990,7 +1996,7 @@
         <v>170</v>
       </c>
       <c r="L13" s="2">
-        <v>46268.26371527778</v>
+        <v>46274.20061342593</v>
       </c>
       <c r="M13" t="s">
         <v>263</v>
@@ -1999,16 +2005,16 @@
         <v>256</v>
       </c>
       <c r="O13" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P13" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q13" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R13" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W13" s="2">
         <v>46254</v>
@@ -2020,7 +2026,7 @@
         <v>261</v>
       </c>
       <c r="Z13" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AA13" t="s">
         <v>263</v>
@@ -2061,7 +2067,7 @@
         <v>3534</v>
       </c>
       <c r="L14" s="2">
-        <v>46268.26371527778</v>
+        <v>46274.20061342593</v>
       </c>
       <c r="M14" t="s">
         <v>263</v>
@@ -2070,16 +2076,16 @@
         <v>256</v>
       </c>
       <c r="O14" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P14" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q14" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R14" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W14" s="2">
         <v>46258</v>
@@ -2091,7 +2097,7 @@
         <v>263</v>
       </c>
       <c r="AA14" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="15" spans="1:27">
@@ -2126,10 +2132,10 @@
         <v>1</v>
       </c>
       <c r="K15">
-        <v>3491</v>
+        <v>3517</v>
       </c>
       <c r="L15" s="2">
-        <v>46268.26371527778</v>
+        <v>46274.20061342593</v>
       </c>
       <c r="M15" t="s">
         <v>262</v>
@@ -2138,19 +2144,19 @@
         <v>256</v>
       </c>
       <c r="O15" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P15" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q15" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R15" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W15" s="2">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="Y15" t="s">
         <v>261</v>
@@ -2159,7 +2165,7 @@
         <v>263</v>
       </c>
       <c r="AA15" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="16" spans="1:27">
@@ -2194,10 +2200,10 @@
         <v>2</v>
       </c>
       <c r="K16">
-        <v>3509</v>
+        <v>3531</v>
       </c>
       <c r="L16" s="2">
-        <v>46268.26371527778</v>
+        <v>46274.20061342593</v>
       </c>
       <c r="M16" t="s">
         <v>262</v>
@@ -2206,19 +2212,19 @@
         <v>256</v>
       </c>
       <c r="O16" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P16" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q16" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R16" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W16" s="2">
-        <v>46265</v>
+        <v>46272</v>
       </c>
       <c r="Y16" t="s">
         <v>261</v>
@@ -2227,7 +2233,7 @@
         <v>263</v>
       </c>
       <c r="AA16" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="17" spans="1:27">
@@ -2274,16 +2280,16 @@
         <v>257</v>
       </c>
       <c r="O17" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P17" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q17" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R17" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W17" s="2">
         <v>46113</v>
@@ -2321,10 +2327,10 @@
         <v>0</v>
       </c>
       <c r="K18">
-        <v>3616</v>
+        <v>3622</v>
       </c>
       <c r="L18" s="2">
-        <v>46268.26371527778</v>
+        <v>46274.20061342593</v>
       </c>
       <c r="M18" t="s">
         <v>263</v>
@@ -2333,28 +2339,28 @@
         <v>256</v>
       </c>
       <c r="O18" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P18" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q18" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R18" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W18" s="2">
-        <v>46264</v>
+        <v>46271</v>
       </c>
       <c r="Y18" t="s">
         <v>261</v>
       </c>
       <c r="Z18" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AA18" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="19" spans="1:27">
@@ -2401,16 +2407,16 @@
         <v>257</v>
       </c>
       <c r="O19" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P19" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q19" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R19" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W19" s="2">
         <v>46163</v>
@@ -2460,16 +2466,16 @@
         <v>257</v>
       </c>
       <c r="O20" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P20" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q20" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R20" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W20" s="2">
         <v>46165</v>
@@ -2519,16 +2525,16 @@
         <v>257</v>
       </c>
       <c r="O21" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P21" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q21" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R21" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W21" s="2">
         <v>46166</v>
@@ -2569,7 +2575,7 @@
         <v>3591</v>
       </c>
       <c r="L22" s="2">
-        <v>46268.26371527778</v>
+        <v>46274.20061342593</v>
       </c>
       <c r="M22" t="s">
         <v>263</v>
@@ -2578,16 +2584,16 @@
         <v>256</v>
       </c>
       <c r="O22" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P22" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q22" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R22" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W22" s="2">
         <v>46168</v>
@@ -2599,7 +2605,7 @@
         <v>263</v>
       </c>
       <c r="AA22" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="23" spans="1:27">
@@ -2637,7 +2643,7 @@
         <v>3591</v>
       </c>
       <c r="L23" s="2">
-        <v>46268.26371527778</v>
+        <v>46274.20061342593</v>
       </c>
       <c r="M23" t="s">
         <v>263</v>
@@ -2646,16 +2652,16 @@
         <v>256</v>
       </c>
       <c r="O23" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P23" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q23" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R23" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W23" s="2">
         <v>46168</v>
@@ -2667,7 +2673,7 @@
         <v>263</v>
       </c>
       <c r="AA23" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="24" spans="1:27">
@@ -2705,7 +2711,7 @@
         <v>131</v>
       </c>
       <c r="L24" s="2">
-        <v>46268.26371527778</v>
+        <v>46274.20061342593</v>
       </c>
       <c r="M24" t="s">
         <v>263</v>
@@ -2714,16 +2720,16 @@
         <v>256</v>
       </c>
       <c r="O24" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P24" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q24" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R24" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W24" s="2">
         <v>46257</v>
@@ -2767,34 +2773,34 @@
         <v>1</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="L25" s="2">
-        <v>46268.26371527778</v>
+        <v>46274.20061342593</v>
       </c>
       <c r="M25" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="N25" t="s">
         <v>256</v>
       </c>
       <c r="O25" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P25" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q25" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R25" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W25" s="2">
-        <v>46256</v>
+        <v>46272</v>
       </c>
       <c r="Y25" t="s">
         <v>261</v>
@@ -2803,7 +2809,7 @@
         <v>263</v>
       </c>
       <c r="AA25" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
     </row>
     <row r="26" spans="1:27">
@@ -2841,7 +2847,7 @@
         <v>128</v>
       </c>
       <c r="L26" s="2">
-        <v>46268.26371527778</v>
+        <v>46274.20061342593</v>
       </c>
       <c r="M26" t="s">
         <v>263</v>
@@ -2850,16 +2856,16 @@
         <v>256</v>
       </c>
       <c r="O26" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P26" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q26" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R26" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W26" s="2">
         <v>46254</v>
@@ -2918,16 +2924,16 @@
         <v>257</v>
       </c>
       <c r="O27" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P27" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q27" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R27" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W27" s="2">
         <v>46172</v>
@@ -2977,16 +2983,16 @@
         <v>257</v>
       </c>
       <c r="O28" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P28" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q28" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R28" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W28" s="2">
         <v>46164</v>
@@ -3036,16 +3042,16 @@
         <v>257</v>
       </c>
       <c r="O29" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P29" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q29" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R29" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W29" s="2">
         <v>46168</v>
@@ -3095,16 +3101,16 @@
         <v>257</v>
       </c>
       <c r="O30" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P30" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q30" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R30" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W30" s="2">
         <v>46168</v>
@@ -3154,16 +3160,16 @@
         <v>257</v>
       </c>
       <c r="O31" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P31" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q31" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R31" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W31" s="2">
         <v>46168</v>
@@ -3198,13 +3204,13 @@
         <v>1</v>
       </c>
       <c r="J32">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="K32">
-        <v>8878</v>
+        <v>10456</v>
       </c>
       <c r="L32" s="2">
-        <v>46268.26371527778</v>
+        <v>46274.20061342593</v>
       </c>
       <c r="M32" t="s">
         <v>261</v>
@@ -3213,28 +3219,28 @@
         <v>256</v>
       </c>
       <c r="O32" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P32" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q32" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R32" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W32" s="2">
-        <v>46268</v>
+        <v>46274</v>
       </c>
       <c r="Y32" t="s">
         <v>261</v>
       </c>
       <c r="Z32" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AA32" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="33" spans="1:27">
@@ -3281,16 +3287,16 @@
         <v>257</v>
       </c>
       <c r="O33" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P33" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q33" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R33" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W33" s="2">
         <v>46168</v>
@@ -3340,16 +3346,16 @@
         <v>257</v>
       </c>
       <c r="O34" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P34" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q34" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R34" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W34" s="2">
         <v>46168</v>
@@ -3390,7 +3396,7 @@
         <v>3591</v>
       </c>
       <c r="L35" s="2">
-        <v>46268.26371527778</v>
+        <v>46274.20061342593</v>
       </c>
       <c r="M35" t="s">
         <v>263</v>
@@ -3399,16 +3405,16 @@
         <v>256</v>
       </c>
       <c r="O35" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P35" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q35" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R35" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W35" s="2">
         <v>46157</v>
@@ -3420,7 +3426,7 @@
         <v>263</v>
       </c>
       <c r="AA35" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="36" spans="1:27">
@@ -3458,7 +3464,7 @@
         <v>3591</v>
       </c>
       <c r="L36" s="2">
-        <v>46268.26371527778</v>
+        <v>46274.20061342593</v>
       </c>
       <c r="M36" t="s">
         <v>263</v>
@@ -3467,16 +3473,16 @@
         <v>256</v>
       </c>
       <c r="O36" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P36" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q36" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R36" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W36" s="2">
         <v>46168</v>
@@ -3488,7 +3494,7 @@
         <v>263</v>
       </c>
       <c r="AA36" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="37" spans="1:27">
@@ -3526,7 +3532,7 @@
         <v>1826</v>
       </c>
       <c r="L37" s="2">
-        <v>46268.26371527778</v>
+        <v>46274.20061342593</v>
       </c>
       <c r="M37" t="s">
         <v>263</v>
@@ -3535,16 +3541,16 @@
         <v>256</v>
       </c>
       <c r="O37" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P37" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q37" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R37" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W37" s="2">
         <v>46132</v>
@@ -3556,7 +3562,7 @@
         <v>263</v>
       </c>
       <c r="AA37" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="38" spans="1:27">
@@ -3594,7 +3600,7 @@
         <v>2937</v>
       </c>
       <c r="L38" s="2">
-        <v>46268.26371527778</v>
+        <v>46274.20061342593</v>
       </c>
       <c r="M38" t="s">
         <v>263</v>
@@ -3603,16 +3609,16 @@
         <v>256</v>
       </c>
       <c r="O38" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P38" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q38" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R38" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W38" s="2">
         <v>46113</v>
@@ -3624,7 +3630,7 @@
         <v>263</v>
       </c>
       <c r="AA38" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="39" spans="1:27">
@@ -3662,7 +3668,7 @@
         <v>3176</v>
       </c>
       <c r="L39" s="2">
-        <v>46268.26371527778</v>
+        <v>46274.20061342593</v>
       </c>
       <c r="M39" t="s">
         <v>263</v>
@@ -3671,16 +3677,16 @@
         <v>256</v>
       </c>
       <c r="O39" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P39" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q39" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R39" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W39" s="2">
         <v>46140</v>
@@ -3692,7 +3698,7 @@
         <v>263</v>
       </c>
       <c r="AA39" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="40" spans="1:27">
@@ -3730,7 +3736,7 @@
         <v>3128</v>
       </c>
       <c r="L40" s="2">
-        <v>46268.26371527778</v>
+        <v>46274.20061342593</v>
       </c>
       <c r="M40" t="s">
         <v>263</v>
@@ -3739,16 +3745,16 @@
         <v>256</v>
       </c>
       <c r="O40" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P40" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q40" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R40" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W40" s="2">
         <v>46024</v>
@@ -3760,7 +3766,7 @@
         <v>263</v>
       </c>
       <c r="AA40" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="41" spans="1:27">
@@ -3798,7 +3804,7 @@
         <v>3542</v>
       </c>
       <c r="L41" s="2">
-        <v>46268.26371527778</v>
+        <v>46274.20061342593</v>
       </c>
       <c r="M41" t="s">
         <v>263</v>
@@ -3807,16 +3813,16 @@
         <v>256</v>
       </c>
       <c r="O41" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P41" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q41" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R41" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W41" s="2">
         <v>46168</v>
@@ -3828,7 +3834,7 @@
         <v>263</v>
       </c>
       <c r="AA41" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="42" spans="1:27">
@@ -3866,7 +3872,7 @@
         <v>3533</v>
       </c>
       <c r="L42" s="2">
-        <v>46268.26371527778</v>
+        <v>46274.20061342593</v>
       </c>
       <c r="M42" t="s">
         <v>263</v>
@@ -3875,16 +3881,16 @@
         <v>256</v>
       </c>
       <c r="O42" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P42" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q42" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R42" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W42" s="2">
         <v>46164</v>
@@ -3896,7 +3902,7 @@
         <v>263</v>
       </c>
       <c r="AA42" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="43" spans="1:27">
@@ -3934,7 +3940,7 @@
         <v>3513</v>
       </c>
       <c r="L43" s="2">
-        <v>46268.26371527778</v>
+        <v>46274.20061342593</v>
       </c>
       <c r="M43" t="s">
         <v>263</v>
@@ -3943,16 +3949,16 @@
         <v>256</v>
       </c>
       <c r="O43" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P43" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q43" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R43" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W43" s="2">
         <v>46112</v>
@@ -3964,7 +3970,7 @@
         <v>263</v>
       </c>
       <c r="AA43" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="44" spans="1:27">
@@ -4011,16 +4017,16 @@
         <v>257</v>
       </c>
       <c r="O44" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P44" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q44" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R44" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W44" s="2">
         <v>46171</v>
@@ -4055,13 +4061,13 @@
         <v>1</v>
       </c>
       <c r="J45">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K45">
-        <v>3114</v>
+        <v>3263</v>
       </c>
       <c r="L45" s="2">
-        <v>46268.26371527778</v>
+        <v>46274.20061342593</v>
       </c>
       <c r="M45" t="s">
         <v>261</v>
@@ -4070,19 +4076,19 @@
         <v>256</v>
       </c>
       <c r="O45" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P45" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q45" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R45" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W45" s="2">
-        <v>46267</v>
+        <v>46273</v>
       </c>
       <c r="Y45" t="s">
         <v>261</v>
@@ -4091,7 +4097,7 @@
         <v>263</v>
       </c>
       <c r="AA45" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="46" spans="1:27">
@@ -4123,13 +4129,13 @@
         <v>1</v>
       </c>
       <c r="J46">
-        <v>20</v>
+        <v>680</v>
       </c>
       <c r="K46">
-        <v>3823</v>
+        <v>5392</v>
       </c>
       <c r="L46" s="2">
-        <v>46268.26371527778</v>
+        <v>46274.20061342593</v>
       </c>
       <c r="M46" t="s">
         <v>261</v>
@@ -4138,19 +4144,19 @@
         <v>256</v>
       </c>
       <c r="O46" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P46" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q46" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R46" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W46" s="2">
-        <v>46267</v>
+        <v>46273</v>
       </c>
       <c r="Y46" t="s">
         <v>261</v>
@@ -4159,7 +4165,7 @@
         <v>263</v>
       </c>
       <c r="AA46" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="47" spans="1:27">
@@ -4191,13 +4197,13 @@
         <v>1</v>
       </c>
       <c r="J47">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="K47">
-        <v>3677</v>
+        <v>3920</v>
       </c>
       <c r="L47" s="2">
-        <v>46268.26371527778</v>
+        <v>46274.20061342593</v>
       </c>
       <c r="M47" t="s">
         <v>261</v>
@@ -4206,19 +4212,19 @@
         <v>256</v>
       </c>
       <c r="O47" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P47" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q47" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R47" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W47" s="2">
-        <v>46267</v>
+        <v>46273</v>
       </c>
       <c r="Y47" t="s">
         <v>261</v>
@@ -4227,7 +4233,7 @@
         <v>263</v>
       </c>
       <c r="AA47" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="48" spans="1:27">
@@ -4265,7 +4271,7 @@
         <v>2299</v>
       </c>
       <c r="L48" s="2">
-        <v>46268.26371527778</v>
+        <v>46274.20061342593</v>
       </c>
       <c r="M48" t="s">
         <v>263</v>
@@ -4274,16 +4280,16 @@
         <v>256</v>
       </c>
       <c r="O48" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P48" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q48" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R48" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W48" s="2">
         <v>46168</v>
@@ -4295,7 +4301,7 @@
         <v>263</v>
       </c>
       <c r="AA48" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="49" spans="1:27">
@@ -4327,34 +4333,34 @@
         <v>1</v>
       </c>
       <c r="J49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K49">
-        <v>1485</v>
+        <v>1490</v>
       </c>
       <c r="L49" s="2">
-        <v>46268.26371527778</v>
+        <v>46274.20061342593</v>
       </c>
       <c r="M49" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="N49" t="s">
         <v>256</v>
       </c>
       <c r="O49" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P49" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q49" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R49" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W49" s="2">
-        <v>46246</v>
+        <v>46273</v>
       </c>
       <c r="Y49" t="s">
         <v>261</v>
@@ -4363,7 +4369,7 @@
         <v>263</v>
       </c>
       <c r="AA49" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="50" spans="1:27">
@@ -4395,34 +4401,34 @@
         <v>1</v>
       </c>
       <c r="J50">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K50">
-        <v>1559</v>
+        <v>1587</v>
       </c>
       <c r="L50" s="2">
-        <v>46268.26371527778</v>
+        <v>46274.20061342593</v>
       </c>
       <c r="M50" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="N50" t="s">
         <v>256</v>
       </c>
       <c r="O50" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P50" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q50" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R50" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W50" s="2">
-        <v>46266</v>
+        <v>46273</v>
       </c>
       <c r="Y50" t="s">
         <v>261</v>
@@ -4431,7 +4437,7 @@
         <v>263</v>
       </c>
       <c r="AA50" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="51" spans="1:27">
@@ -4463,31 +4469,31 @@
         <v>1</v>
       </c>
       <c r="J51">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K51">
         <v>1478</v>
       </c>
       <c r="L51" s="2">
-        <v>46268.26371527778</v>
+        <v>46274.20061342593</v>
       </c>
       <c r="M51" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N51" t="s">
         <v>256</v>
       </c>
       <c r="O51" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P51" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q51" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R51" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W51" s="2">
         <v>46265</v>
@@ -4499,7 +4505,7 @@
         <v>263</v>
       </c>
       <c r="AA51" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="52" spans="1:27">
@@ -4537,7 +4543,7 @@
         <v>1466</v>
       </c>
       <c r="L52" s="2">
-        <v>46268.26371527778</v>
+        <v>46274.20061342593</v>
       </c>
       <c r="M52" t="s">
         <v>263</v>
@@ -4546,16 +4552,16 @@
         <v>256</v>
       </c>
       <c r="O52" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P52" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q52" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R52" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W52" s="2">
         <v>46142</v>
@@ -4567,7 +4573,7 @@
         <v>263</v>
       </c>
       <c r="AA52" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="53" spans="1:27">
@@ -4599,13 +4605,13 @@
         <v>1</v>
       </c>
       <c r="J53">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K53">
-        <v>1968</v>
+        <v>2009</v>
       </c>
       <c r="L53" s="2">
-        <v>46268.26371527778</v>
+        <v>46274.20061342593</v>
       </c>
       <c r="M53" t="s">
         <v>261</v>
@@ -4614,19 +4620,19 @@
         <v>256</v>
       </c>
       <c r="O53" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P53" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q53" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R53" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W53" s="2">
-        <v>46267</v>
+        <v>46273</v>
       </c>
       <c r="Y53" t="s">
         <v>261</v>
@@ -4635,7 +4641,7 @@
         <v>263</v>
       </c>
       <c r="AA53" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="54" spans="1:27">
@@ -4667,31 +4673,31 @@
         <v>1</v>
       </c>
       <c r="J54">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K54">
-        <v>1329</v>
+        <v>1337</v>
       </c>
       <c r="L54" s="2">
-        <v>46268.26371527778</v>
+        <v>46274.20061342593</v>
       </c>
       <c r="M54" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N54" t="s">
         <v>256</v>
       </c>
       <c r="O54" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P54" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q54" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R54" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W54" s="2">
         <v>46267</v>
@@ -4703,7 +4709,7 @@
         <v>263</v>
       </c>
       <c r="AA54" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="55" spans="1:27">
@@ -4735,13 +4741,13 @@
         <v>1</v>
       </c>
       <c r="J55">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K55">
-        <v>1922</v>
+        <v>2067</v>
       </c>
       <c r="L55" s="2">
-        <v>46268.26371527778</v>
+        <v>46274.20061342593</v>
       </c>
       <c r="M55" t="s">
         <v>261</v>
@@ -4750,28 +4756,28 @@
         <v>256</v>
       </c>
       <c r="O55" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P55" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q55" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R55" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W55" s="2">
-        <v>46267</v>
+        <v>46273</v>
       </c>
       <c r="Y55" t="s">
         <v>261</v>
       </c>
       <c r="Z55" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AA55" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="56" spans="1:27">
@@ -4818,16 +4824,16 @@
         <v>257</v>
       </c>
       <c r="O56" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P56" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q56" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R56" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W56" s="2">
         <v>46161</v>
@@ -4862,34 +4868,34 @@
         <v>1</v>
       </c>
       <c r="J57">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K57">
-        <v>3792</v>
+        <v>3824</v>
       </c>
       <c r="L57" s="2">
-        <v>46268.26371527778</v>
+        <v>46274.20061342593</v>
       </c>
       <c r="M57" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="N57" t="s">
         <v>256</v>
       </c>
       <c r="O57" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P57" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q57" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R57" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W57" s="2">
-        <v>46266</v>
+        <v>46273</v>
       </c>
       <c r="Y57" t="s">
         <v>261</v>
@@ -4898,7 +4904,7 @@
         <v>263</v>
       </c>
       <c r="AA57" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="58" spans="1:27">
@@ -4945,16 +4951,16 @@
         <v>257</v>
       </c>
       <c r="O58" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P58" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q58" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R58" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W58" s="2">
         <v>46148</v>
@@ -5004,16 +5010,16 @@
         <v>257</v>
       </c>
       <c r="O59" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P59" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q59" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R59" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W59" s="2">
         <v>46168</v>
@@ -5063,16 +5069,16 @@
         <v>257</v>
       </c>
       <c r="O60" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P60" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q60" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R60" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W60" s="2">
         <v>46164</v>
@@ -5122,16 +5128,16 @@
         <v>257</v>
       </c>
       <c r="O61" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P61" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q61" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R61" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W61" s="2">
         <v>46168</v>
@@ -5169,10 +5175,10 @@
         <v>1</v>
       </c>
       <c r="K62">
-        <v>1642</v>
+        <v>1647</v>
       </c>
       <c r="L62" s="2">
-        <v>46268.26371527778</v>
+        <v>46274.20061342593</v>
       </c>
       <c r="M62" t="s">
         <v>262</v>
@@ -5181,19 +5187,19 @@
         <v>256</v>
       </c>
       <c r="O62" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P62" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q62" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R62" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W62" s="2">
-        <v>46265</v>
+        <v>46273</v>
       </c>
       <c r="Y62" t="s">
         <v>261</v>
@@ -5202,7 +5208,7 @@
         <v>263</v>
       </c>
       <c r="AA62" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="63" spans="1:27">
@@ -5249,16 +5255,16 @@
         <v>257</v>
       </c>
       <c r="O63" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P63" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q63" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R63" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W63" s="2">
         <v>46164</v>
@@ -5308,16 +5314,16 @@
         <v>257</v>
       </c>
       <c r="O64" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P64" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q64" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R64" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W64" s="2">
         <v>46168</v>
@@ -5352,13 +5358,13 @@
         <v>1</v>
       </c>
       <c r="J65">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="K65">
-        <v>3722</v>
+        <v>3952</v>
       </c>
       <c r="L65" s="2">
-        <v>46268.26371527778</v>
+        <v>46274.20061342593</v>
       </c>
       <c r="M65" t="s">
         <v>261</v>
@@ -5367,28 +5373,28 @@
         <v>256</v>
       </c>
       <c r="O65" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P65" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q65" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R65" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W65" s="2">
-        <v>46267</v>
+        <v>46274</v>
       </c>
       <c r="Y65" t="s">
         <v>261</v>
       </c>
       <c r="Z65" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AA65" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="66" spans="1:27">
@@ -5426,7 +5432,7 @@
         <v>3037</v>
       </c>
       <c r="L66" s="2">
-        <v>46268.26371527778</v>
+        <v>46274.20061342593</v>
       </c>
       <c r="M66" t="s">
         <v>263</v>
@@ -5435,16 +5441,16 @@
         <v>256</v>
       </c>
       <c r="O66" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P66" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q66" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R66" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W66" s="2">
         <v>46160</v>
@@ -5456,7 +5462,7 @@
         <v>263</v>
       </c>
       <c r="AA66" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="67" spans="1:27">
@@ -5488,43 +5494,43 @@
         <v>1</v>
       </c>
       <c r="J67">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K67">
-        <v>1674</v>
+        <v>1702</v>
       </c>
       <c r="L67" s="2">
-        <v>46268.26371527778</v>
+        <v>46274.20061342593</v>
       </c>
       <c r="M67" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="N67" t="s">
         <v>256</v>
       </c>
       <c r="O67" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P67" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q67" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R67" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W67" s="2">
-        <v>46266</v>
+        <v>46274</v>
       </c>
       <c r="Y67" t="s">
         <v>261</v>
       </c>
       <c r="Z67" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AA67" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="68" spans="1:27">
@@ -5556,13 +5562,13 @@
         <v>1</v>
       </c>
       <c r="J68">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K68">
-        <v>3528</v>
+        <v>3703</v>
       </c>
       <c r="L68" s="2">
-        <v>46268.26371527778</v>
+        <v>46274.20061342593</v>
       </c>
       <c r="M68" t="s">
         <v>261</v>
@@ -5571,28 +5577,28 @@
         <v>256</v>
       </c>
       <c r="O68" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P68" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q68" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R68" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W68" s="2">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="Y68" t="s">
         <v>261</v>
       </c>
       <c r="Z68" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AA68" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="69" spans="1:27">
@@ -5630,7 +5636,7 @@
         <v>3058</v>
       </c>
       <c r="L69" s="2">
-        <v>46268.26371527778</v>
+        <v>46274.20061342593</v>
       </c>
       <c r="M69" t="s">
         <v>263</v>
@@ -5639,16 +5645,16 @@
         <v>256</v>
       </c>
       <c r="O69" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P69" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q69" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R69" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W69" s="2">
         <v>46259</v>
@@ -5660,7 +5666,7 @@
         <v>263</v>
       </c>
       <c r="AA69" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="70" spans="1:27">
@@ -5692,13 +5698,13 @@
         <v>1</v>
       </c>
       <c r="J70">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="K70">
-        <v>2227</v>
+        <v>2362</v>
       </c>
       <c r="L70" s="2">
-        <v>46268.26371527778</v>
+        <v>46274.20061342593</v>
       </c>
       <c r="M70" t="s">
         <v>261</v>
@@ -5707,28 +5713,28 @@
         <v>256</v>
       </c>
       <c r="O70" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P70" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q70" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R70" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W70" s="2">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="Y70" t="s">
         <v>261</v>
       </c>
       <c r="Z70" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AA70" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="71" spans="1:27">
@@ -5760,13 +5766,13 @@
         <v>1</v>
       </c>
       <c r="J71">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K71">
-        <v>2215</v>
+        <v>2301</v>
       </c>
       <c r="L71" s="2">
-        <v>46268.26371527778</v>
+        <v>46274.20061342593</v>
       </c>
       <c r="M71" t="s">
         <v>261</v>
@@ -5775,28 +5781,28 @@
         <v>256</v>
       </c>
       <c r="O71" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P71" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q71" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R71" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W71" s="2">
-        <v>46267</v>
+        <v>46273</v>
       </c>
       <c r="Y71" t="s">
         <v>261</v>
       </c>
       <c r="Z71" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AA71" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="72" spans="1:27">
@@ -5843,16 +5849,16 @@
         <v>257</v>
       </c>
       <c r="O72" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P72" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q72" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R72" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W72" s="2">
         <v>46164</v>
@@ -5887,31 +5893,31 @@
         <v>1</v>
       </c>
       <c r="J73">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K73">
         <v>1307</v>
       </c>
       <c r="L73" s="2">
-        <v>46268.26371527778</v>
+        <v>46274.20061342593</v>
       </c>
       <c r="M73" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N73" t="s">
         <v>256</v>
       </c>
       <c r="O73" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P73" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q73" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R73" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W73" s="2">
         <v>46265</v>
@@ -5923,7 +5929,7 @@
         <v>263</v>
       </c>
       <c r="AA73" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="74" spans="1:27">
@@ -5961,7 +5967,7 @@
         <v>1449</v>
       </c>
       <c r="L74" s="2">
-        <v>46268.26371527778</v>
+        <v>46274.20061342593</v>
       </c>
       <c r="M74" t="s">
         <v>263</v>
@@ -5970,16 +5976,16 @@
         <v>256</v>
       </c>
       <c r="O74" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P74" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q74" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R74" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W74" s="2">
         <v>46185</v>
@@ -5991,7 +5997,7 @@
         <v>263</v>
       </c>
       <c r="AA74" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="75" spans="1:27">
@@ -6029,7 +6035,7 @@
         <v>1480</v>
       </c>
       <c r="L75" s="2">
-        <v>46268.26371527778</v>
+        <v>46274.20061342593</v>
       </c>
       <c r="M75" t="s">
         <v>263</v>
@@ -6038,16 +6044,16 @@
         <v>256</v>
       </c>
       <c r="O75" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P75" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q75" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R75" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W75" s="2">
         <v>46149</v>
@@ -6059,7 +6065,7 @@
         <v>263</v>
       </c>
       <c r="AA75" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="76" spans="1:27">
@@ -6097,7 +6103,7 @@
         <v>1524</v>
       </c>
       <c r="L76" s="2">
-        <v>46268.26371527778</v>
+        <v>46274.20061342593</v>
       </c>
       <c r="M76" t="s">
         <v>263</v>
@@ -6106,16 +6112,16 @@
         <v>256</v>
       </c>
       <c r="O76" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P76" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q76" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R76" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W76" s="2">
         <v>46149</v>
@@ -6127,7 +6133,7 @@
         <v>263</v>
       </c>
       <c r="AA76" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="77" spans="1:27">
@@ -6159,34 +6165,34 @@
         <v>1</v>
       </c>
       <c r="J77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K77">
-        <v>1537</v>
+        <v>1545</v>
       </c>
       <c r="L77" s="2">
-        <v>46268.26371527778</v>
+        <v>46274.20061342593</v>
       </c>
       <c r="M77" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="N77" t="s">
         <v>256</v>
       </c>
       <c r="O77" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P77" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q77" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R77" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W77" s="2">
-        <v>46168</v>
+        <v>46272</v>
       </c>
       <c r="Y77" t="s">
         <v>261</v>
@@ -6195,7 +6201,7 @@
         <v>263</v>
       </c>
       <c r="AA77" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="78" spans="1:27">
@@ -6227,34 +6233,34 @@
         <v>1</v>
       </c>
       <c r="J78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K78">
-        <v>1537</v>
+        <v>1545</v>
       </c>
       <c r="L78" s="2">
-        <v>46268.26371527778</v>
+        <v>46274.20061342593</v>
       </c>
       <c r="M78" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="N78" t="s">
         <v>256</v>
       </c>
       <c r="O78" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P78" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q78" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R78" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W78" s="2">
-        <v>46160</v>
+        <v>46272</v>
       </c>
       <c r="Y78" t="s">
         <v>261</v>
@@ -6263,7 +6269,7 @@
         <v>263</v>
       </c>
       <c r="AA78" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="79" spans="1:27">
@@ -6295,34 +6301,34 @@
         <v>1</v>
       </c>
       <c r="J79">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K79">
-        <v>1550</v>
+        <v>1630</v>
       </c>
       <c r="L79" s="2">
-        <v>46268.26371527778</v>
+        <v>46274.20061342593</v>
       </c>
       <c r="M79" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="N79" t="s">
         <v>256</v>
       </c>
       <c r="O79" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P79" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q79" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R79" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W79" s="2">
-        <v>46168</v>
+        <v>46273</v>
       </c>
       <c r="Y79" t="s">
         <v>261</v>
@@ -6331,7 +6337,7 @@
         <v>263</v>
       </c>
       <c r="AA79" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="80" spans="1:27">
@@ -6363,34 +6369,34 @@
         <v>1</v>
       </c>
       <c r="J80">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K80">
-        <v>1437</v>
+        <v>1458</v>
       </c>
       <c r="L80" s="2">
-        <v>46268.26371527778</v>
+        <v>46274.20061342593</v>
       </c>
       <c r="M80" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="N80" t="s">
         <v>256</v>
       </c>
       <c r="O80" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P80" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q80" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R80" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W80" s="2">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="Y80" t="s">
         <v>261</v>
@@ -6399,7 +6405,7 @@
         <v>263</v>
       </c>
       <c r="AA80" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="81" spans="1:27">
@@ -6437,7 +6443,7 @@
         <v>3591</v>
       </c>
       <c r="L81" s="2">
-        <v>46268.26371527778</v>
+        <v>46274.20061342593</v>
       </c>
       <c r="M81" t="s">
         <v>263</v>
@@ -6446,16 +6452,16 @@
         <v>256</v>
       </c>
       <c r="O81" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P81" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q81" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R81" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W81" s="2">
         <v>46160</v>
@@ -6467,7 +6473,7 @@
         <v>263</v>
       </c>
       <c r="AA81" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="82" spans="1:27">
@@ -6514,16 +6520,16 @@
         <v>257</v>
       </c>
       <c r="O82" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P82" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q82" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R82" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W82" s="2">
         <v>46161</v>
@@ -6573,16 +6579,16 @@
         <v>257</v>
       </c>
       <c r="O83" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P83" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q83" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R83" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W83" s="2">
         <v>46168</v>
@@ -6632,16 +6638,16 @@
         <v>257</v>
       </c>
       <c r="O84" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P84" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q84" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R84" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W84" s="2">
         <v>46164</v>
@@ -6691,16 +6697,16 @@
         <v>257</v>
       </c>
       <c r="O85" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P85" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q85" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R85" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W85" s="2">
         <v>46168</v>
@@ -6741,7 +6747,7 @@
         <v>652</v>
       </c>
       <c r="L86" s="2">
-        <v>46268.26371527778</v>
+        <v>46274.20061342593</v>
       </c>
       <c r="M86" t="s">
         <v>263</v>
@@ -6750,16 +6756,16 @@
         <v>256</v>
       </c>
       <c r="O86" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P86" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q86" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R86" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W86" s="2">
         <v>46164</v>
@@ -6771,7 +6777,7 @@
         <v>263</v>
       </c>
       <c r="AA86" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="87" spans="1:27">
@@ -6809,7 +6815,7 @@
         <v>3609</v>
       </c>
       <c r="L87" s="2">
-        <v>46268.26371527778</v>
+        <v>46274.20061342593</v>
       </c>
       <c r="M87" t="s">
         <v>263</v>
@@ -6818,16 +6824,16 @@
         <v>256</v>
       </c>
       <c r="O87" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P87" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q87" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R87" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W87" s="2">
         <v>46248</v>
@@ -6839,7 +6845,7 @@
         <v>263</v>
       </c>
       <c r="AA87" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="88" spans="1:27">
@@ -6877,7 +6883,7 @@
         <v>3580</v>
       </c>
       <c r="L88" s="2">
-        <v>46268.26371527778</v>
+        <v>46274.20061342593</v>
       </c>
       <c r="M88" t="s">
         <v>263</v>
@@ -6886,16 +6892,16 @@
         <v>256</v>
       </c>
       <c r="O88" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P88" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q88" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R88" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W88" s="2">
         <v>46253.16666666666</v>
@@ -6907,7 +6913,7 @@
         <v>263</v>
       </c>
       <c r="AA88" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="89" spans="1:27">
@@ -6939,16 +6945,16 @@
         <v>257</v>
       </c>
       <c r="O89" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P89" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q89" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R89" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="90" spans="1:27">
@@ -6986,25 +6992,25 @@
         <v>125</v>
       </c>
       <c r="L90" s="2">
-        <v>46268.26371527778</v>
+        <v>46274.20061342593</v>
       </c>
       <c r="M90" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="N90" t="s">
         <v>256</v>
       </c>
       <c r="O90" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P90" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q90" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R90" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W90" s="2">
         <v>46154</v>
@@ -7013,9 +7019,6 @@
         <v>261</v>
       </c>
       <c r="Z90" t="s">
-        <v>263</v>
-      </c>
-      <c r="AA90" t="s">
         <v>263</v>
       </c>
     </row>
@@ -7048,16 +7051,16 @@
         <v>256</v>
       </c>
       <c r="O91" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P91" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q91" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R91" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W91" s="2">
         <v>46154</v>
@@ -7107,16 +7110,16 @@
         <v>257</v>
       </c>
       <c r="O92" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P92" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q92" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R92" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W92" s="2">
         <v>46164</v>

--- a/sites.xlsx
+++ b/sites.xlsx
@@ -1553,7 +1553,7 @@
         <v>169</v>
       </c>
       <c r="L6" s="2">
-        <v>46274.20061342593</v>
+        <v>46276.35924768518</v>
       </c>
       <c r="M6" t="s">
         <v>263</v>
@@ -1996,7 +1996,7 @@
         <v>170</v>
       </c>
       <c r="L13" s="2">
-        <v>46274.20061342593</v>
+        <v>46276.35924768518</v>
       </c>
       <c r="M13" t="s">
         <v>263</v>
@@ -2067,7 +2067,7 @@
         <v>3534</v>
       </c>
       <c r="L14" s="2">
-        <v>46274.20061342593</v>
+        <v>46276.35924768518</v>
       </c>
       <c r="M14" t="s">
         <v>263</v>
@@ -2129,16 +2129,16 @@
         <v>1</v>
       </c>
       <c r="J15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15">
-        <v>3517</v>
+        <v>3522</v>
       </c>
       <c r="L15" s="2">
-        <v>46274.20061342593</v>
+        <v>46276.35924768518</v>
       </c>
       <c r="M15" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N15" t="s">
         <v>256</v>
@@ -2200,10 +2200,10 @@
         <v>2</v>
       </c>
       <c r="K16">
-        <v>3531</v>
+        <v>3557</v>
       </c>
       <c r="L16" s="2">
-        <v>46274.20061342593</v>
+        <v>46276.35924768518</v>
       </c>
       <c r="M16" t="s">
         <v>262</v>
@@ -2330,7 +2330,7 @@
         <v>3622</v>
       </c>
       <c r="L18" s="2">
-        <v>46274.20061342593</v>
+        <v>46276.35924768518</v>
       </c>
       <c r="M18" t="s">
         <v>263</v>
@@ -2575,7 +2575,7 @@
         <v>3591</v>
       </c>
       <c r="L22" s="2">
-        <v>46274.20061342593</v>
+        <v>46276.35924768518</v>
       </c>
       <c r="M22" t="s">
         <v>263</v>
@@ -2643,7 +2643,7 @@
         <v>3591</v>
       </c>
       <c r="L23" s="2">
-        <v>46274.20061342593</v>
+        <v>46276.35924768518</v>
       </c>
       <c r="M23" t="s">
         <v>263</v>
@@ -2711,7 +2711,7 @@
         <v>131</v>
       </c>
       <c r="L24" s="2">
-        <v>46274.20061342593</v>
+        <v>46276.35924768518</v>
       </c>
       <c r="M24" t="s">
         <v>263</v>
@@ -2773,16 +2773,16 @@
         <v>1</v>
       </c>
       <c r="J25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="L25" s="2">
-        <v>46274.20061342593</v>
+        <v>46276.35924768518</v>
       </c>
       <c r="M25" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N25" t="s">
         <v>256</v>
@@ -2809,7 +2809,7 @@
         <v>263</v>
       </c>
       <c r="AA25" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
     </row>
     <row r="26" spans="1:27">
@@ -2841,16 +2841,16 @@
         <v>1</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="L26" s="2">
-        <v>46274.20061342593</v>
+        <v>46276.35924768518</v>
       </c>
       <c r="M26" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="N26" t="s">
         <v>256</v>
@@ -2868,7 +2868,7 @@
         <v>268</v>
       </c>
       <c r="W26" s="2">
-        <v>46254</v>
+        <v>46274</v>
       </c>
       <c r="Y26" t="s">
         <v>261</v>
@@ -2877,7 +2877,7 @@
         <v>263</v>
       </c>
       <c r="AA26" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
     </row>
     <row r="27" spans="1:27">
@@ -3204,13 +3204,13 @@
         <v>1</v>
       </c>
       <c r="J32">
-        <v>106</v>
+        <v>193</v>
       </c>
       <c r="K32">
-        <v>10456</v>
+        <v>12566</v>
       </c>
       <c r="L32" s="2">
-        <v>46274.20061342593</v>
+        <v>46276.35924768518</v>
       </c>
       <c r="M32" t="s">
         <v>261</v>
@@ -3231,7 +3231,7 @@
         <v>268</v>
       </c>
       <c r="W32" s="2">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="Y32" t="s">
         <v>261</v>
@@ -3396,7 +3396,7 @@
         <v>3591</v>
       </c>
       <c r="L35" s="2">
-        <v>46274.20061342593</v>
+        <v>46276.35924768518</v>
       </c>
       <c r="M35" t="s">
         <v>263</v>
@@ -3464,7 +3464,7 @@
         <v>3591</v>
       </c>
       <c r="L36" s="2">
-        <v>46274.20061342593</v>
+        <v>46276.35924768518</v>
       </c>
       <c r="M36" t="s">
         <v>263</v>
@@ -3532,7 +3532,7 @@
         <v>1826</v>
       </c>
       <c r="L37" s="2">
-        <v>46274.20061342593</v>
+        <v>46276.35924768518</v>
       </c>
       <c r="M37" t="s">
         <v>263</v>
@@ -3600,7 +3600,7 @@
         <v>2937</v>
       </c>
       <c r="L38" s="2">
-        <v>46274.20061342593</v>
+        <v>46276.35924768518</v>
       </c>
       <c r="M38" t="s">
         <v>263</v>
@@ -3668,7 +3668,7 @@
         <v>3176</v>
       </c>
       <c r="L39" s="2">
-        <v>46274.20061342593</v>
+        <v>46276.35924768518</v>
       </c>
       <c r="M39" t="s">
         <v>263</v>
@@ -3736,7 +3736,7 @@
         <v>3128</v>
       </c>
       <c r="L40" s="2">
-        <v>46274.20061342593</v>
+        <v>46276.35924768518</v>
       </c>
       <c r="M40" t="s">
         <v>263</v>
@@ -3804,7 +3804,7 @@
         <v>3542</v>
       </c>
       <c r="L41" s="2">
-        <v>46274.20061342593</v>
+        <v>46276.35924768518</v>
       </c>
       <c r="M41" t="s">
         <v>263</v>
@@ -3872,7 +3872,7 @@
         <v>3533</v>
       </c>
       <c r="L42" s="2">
-        <v>46274.20061342593</v>
+        <v>46276.35924768518</v>
       </c>
       <c r="M42" t="s">
         <v>263</v>
@@ -3940,7 +3940,7 @@
         <v>3513</v>
       </c>
       <c r="L43" s="2">
-        <v>46274.20061342593</v>
+        <v>46276.35924768518</v>
       </c>
       <c r="M43" t="s">
         <v>263</v>
@@ -4061,13 +4061,13 @@
         <v>1</v>
       </c>
       <c r="J45">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K45">
-        <v>3263</v>
+        <v>3507</v>
       </c>
       <c r="L45" s="2">
-        <v>46274.20061342593</v>
+        <v>46276.35924768518</v>
       </c>
       <c r="M45" t="s">
         <v>261</v>
@@ -4088,7 +4088,7 @@
         <v>268</v>
       </c>
       <c r="W45" s="2">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="Y45" t="s">
         <v>261</v>
@@ -4129,13 +4129,13 @@
         <v>1</v>
       </c>
       <c r="J46">
-        <v>680</v>
+        <v>180</v>
       </c>
       <c r="K46">
-        <v>5392</v>
+        <v>8012</v>
       </c>
       <c r="L46" s="2">
-        <v>46274.20061342593</v>
+        <v>46276.35924768518</v>
       </c>
       <c r="M46" t="s">
         <v>261</v>
@@ -4156,7 +4156,7 @@
         <v>268</v>
       </c>
       <c r="W46" s="2">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="Y46" t="s">
         <v>261</v>
@@ -4197,13 +4197,13 @@
         <v>1</v>
       </c>
       <c r="J47">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K47">
-        <v>3920</v>
+        <v>4173</v>
       </c>
       <c r="L47" s="2">
-        <v>46274.20061342593</v>
+        <v>46276.35924768518</v>
       </c>
       <c r="M47" t="s">
         <v>261</v>
@@ -4224,7 +4224,7 @@
         <v>268</v>
       </c>
       <c r="W47" s="2">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="Y47" t="s">
         <v>261</v>
@@ -4271,7 +4271,7 @@
         <v>2299</v>
       </c>
       <c r="L48" s="2">
-        <v>46274.20061342593</v>
+        <v>46276.35924768518</v>
       </c>
       <c r="M48" t="s">
         <v>263</v>
@@ -4336,10 +4336,10 @@
         <v>1</v>
       </c>
       <c r="K49">
-        <v>1490</v>
+        <v>1505</v>
       </c>
       <c r="L49" s="2">
-        <v>46274.20061342593</v>
+        <v>46276.35924768518</v>
       </c>
       <c r="M49" t="s">
         <v>262</v>
@@ -4404,10 +4404,10 @@
         <v>6</v>
       </c>
       <c r="K50">
-        <v>1587</v>
+        <v>1669</v>
       </c>
       <c r="L50" s="2">
-        <v>46274.20061342593</v>
+        <v>46276.35924768518</v>
       </c>
       <c r="M50" t="s">
         <v>261</v>
@@ -4469,16 +4469,16 @@
         <v>1</v>
       </c>
       <c r="J51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K51">
-        <v>1478</v>
+        <v>1496</v>
       </c>
       <c r="L51" s="2">
-        <v>46274.20061342593</v>
+        <v>46276.35924768518</v>
       </c>
       <c r="M51" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="N51" t="s">
         <v>256</v>
@@ -4496,7 +4496,7 @@
         <v>268</v>
       </c>
       <c r="W51" s="2">
-        <v>46265</v>
+        <v>46273</v>
       </c>
       <c r="Y51" t="s">
         <v>261</v>
@@ -4543,7 +4543,7 @@
         <v>1466</v>
       </c>
       <c r="L52" s="2">
-        <v>46274.20061342593</v>
+        <v>46276.35924768518</v>
       </c>
       <c r="M52" t="s">
         <v>263</v>
@@ -4605,13 +4605,13 @@
         <v>1</v>
       </c>
       <c r="J53">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K53">
-        <v>2009</v>
+        <v>2095</v>
       </c>
       <c r="L53" s="2">
-        <v>46274.20061342593</v>
+        <v>46276.35924768518</v>
       </c>
       <c r="M53" t="s">
         <v>261</v>
@@ -4632,7 +4632,7 @@
         <v>268</v>
       </c>
       <c r="W53" s="2">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="Y53" t="s">
         <v>261</v>
@@ -4673,16 +4673,16 @@
         <v>1</v>
       </c>
       <c r="J54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K54">
-        <v>1337</v>
+        <v>1350</v>
       </c>
       <c r="L54" s="2">
-        <v>46274.20061342593</v>
+        <v>46276.35924768518</v>
       </c>
       <c r="M54" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="N54" t="s">
         <v>256</v>
@@ -4700,7 +4700,7 @@
         <v>268</v>
       </c>
       <c r="W54" s="2">
-        <v>46267</v>
+        <v>46275</v>
       </c>
       <c r="Y54" t="s">
         <v>261</v>
@@ -4741,13 +4741,13 @@
         <v>1</v>
       </c>
       <c r="J55">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K55">
-        <v>2067</v>
+        <v>2194</v>
       </c>
       <c r="L55" s="2">
-        <v>46274.20061342593</v>
+        <v>46276.35924768518</v>
       </c>
       <c r="M55" t="s">
         <v>261</v>
@@ -4768,7 +4768,7 @@
         <v>268</v>
       </c>
       <c r="W55" s="2">
-        <v>46273</v>
+        <v>46276</v>
       </c>
       <c r="Y55" t="s">
         <v>261</v>
@@ -4868,13 +4868,13 @@
         <v>1</v>
       </c>
       <c r="J57">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K57">
-        <v>3824</v>
+        <v>3936</v>
       </c>
       <c r="L57" s="2">
-        <v>46274.20061342593</v>
+        <v>46276.35924768518</v>
       </c>
       <c r="M57" t="s">
         <v>261</v>
@@ -4895,7 +4895,7 @@
         <v>268</v>
       </c>
       <c r="W57" s="2">
-        <v>46273</v>
+        <v>46276</v>
       </c>
       <c r="Y57" t="s">
         <v>261</v>
@@ -5175,10 +5175,10 @@
         <v>1</v>
       </c>
       <c r="K62">
-        <v>1647</v>
+        <v>1663</v>
       </c>
       <c r="L62" s="2">
-        <v>46274.20061342593</v>
+        <v>46276.35924768518</v>
       </c>
       <c r="M62" t="s">
         <v>262</v>
@@ -5358,13 +5358,13 @@
         <v>1</v>
       </c>
       <c r="J65">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="K65">
-        <v>3952</v>
+        <v>4283</v>
       </c>
       <c r="L65" s="2">
-        <v>46274.20061342593</v>
+        <v>46276.35924768518</v>
       </c>
       <c r="M65" t="s">
         <v>261</v>
@@ -5385,7 +5385,7 @@
         <v>268</v>
       </c>
       <c r="W65" s="2">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="Y65" t="s">
         <v>261</v>
@@ -5429,10 +5429,10 @@
         <v>0</v>
       </c>
       <c r="K66">
-        <v>3037</v>
+        <v>3062</v>
       </c>
       <c r="L66" s="2">
-        <v>46274.20061342593</v>
+        <v>46276.35924768518</v>
       </c>
       <c r="M66" t="s">
         <v>263</v>
@@ -5453,7 +5453,7 @@
         <v>268</v>
       </c>
       <c r="W66" s="2">
-        <v>46160</v>
+        <v>46261</v>
       </c>
       <c r="Y66" t="s">
         <v>261</v>
@@ -5494,16 +5494,16 @@
         <v>1</v>
       </c>
       <c r="J67">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K67">
-        <v>1702</v>
+        <v>1727</v>
       </c>
       <c r="L67" s="2">
-        <v>46274.20061342593</v>
+        <v>46276.35924768518</v>
       </c>
       <c r="M67" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="N67" t="s">
         <v>256</v>
@@ -5521,7 +5521,7 @@
         <v>268</v>
       </c>
       <c r="W67" s="2">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="Y67" t="s">
         <v>261</v>
@@ -5562,13 +5562,13 @@
         <v>1</v>
       </c>
       <c r="J68">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="K68">
-        <v>3703</v>
+        <v>3971</v>
       </c>
       <c r="L68" s="2">
-        <v>46274.20061342593</v>
+        <v>46276.35924768518</v>
       </c>
       <c r="M68" t="s">
         <v>261</v>
@@ -5589,7 +5589,7 @@
         <v>268</v>
       </c>
       <c r="W68" s="2">
-        <v>46273</v>
+        <v>46276</v>
       </c>
       <c r="Y68" t="s">
         <v>261</v>
@@ -5636,7 +5636,7 @@
         <v>3058</v>
       </c>
       <c r="L69" s="2">
-        <v>46274.20061342593</v>
+        <v>46276.35924768518</v>
       </c>
       <c r="M69" t="s">
         <v>263</v>
@@ -5698,13 +5698,13 @@
         <v>1</v>
       </c>
       <c r="J70">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="K70">
-        <v>2362</v>
+        <v>2454</v>
       </c>
       <c r="L70" s="2">
-        <v>46274.20061342593</v>
+        <v>46276.35924768518</v>
       </c>
       <c r="M70" t="s">
         <v>261</v>
@@ -5725,7 +5725,7 @@
         <v>268</v>
       </c>
       <c r="W70" s="2">
-        <v>46273</v>
+        <v>46276</v>
       </c>
       <c r="Y70" t="s">
         <v>261</v>
@@ -5766,13 +5766,13 @@
         <v>1</v>
       </c>
       <c r="J71">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K71">
-        <v>2301</v>
+        <v>2445</v>
       </c>
       <c r="L71" s="2">
-        <v>46274.20061342593</v>
+        <v>46276.35924768518</v>
       </c>
       <c r="M71" t="s">
         <v>261</v>
@@ -5793,7 +5793,7 @@
         <v>268</v>
       </c>
       <c r="W71" s="2">
-        <v>46273</v>
+        <v>46276</v>
       </c>
       <c r="Y71" t="s">
         <v>261</v>
@@ -5896,10 +5896,10 @@
         <v>0</v>
       </c>
       <c r="K73">
-        <v>1307</v>
+        <v>1316</v>
       </c>
       <c r="L73" s="2">
-        <v>46274.20061342593</v>
+        <v>46276.35924768518</v>
       </c>
       <c r="M73" t="s">
         <v>263</v>
@@ -5967,7 +5967,7 @@
         <v>1449</v>
       </c>
       <c r="L74" s="2">
-        <v>46274.20061342593</v>
+        <v>46276.35924768518</v>
       </c>
       <c r="M74" t="s">
         <v>263</v>
@@ -6032,10 +6032,10 @@
         <v>0</v>
       </c>
       <c r="K75">
-        <v>1480</v>
+        <v>1482</v>
       </c>
       <c r="L75" s="2">
-        <v>46274.20061342593</v>
+        <v>46276.35924768518</v>
       </c>
       <c r="M75" t="s">
         <v>263</v>
@@ -6056,7 +6056,7 @@
         <v>268</v>
       </c>
       <c r="W75" s="2">
-        <v>46149</v>
+        <v>46265</v>
       </c>
       <c r="Y75" t="s">
         <v>261</v>
@@ -6100,10 +6100,10 @@
         <v>0</v>
       </c>
       <c r="K76">
-        <v>1524</v>
+        <v>1527</v>
       </c>
       <c r="L76" s="2">
-        <v>46274.20061342593</v>
+        <v>46276.35924768518</v>
       </c>
       <c r="M76" t="s">
         <v>263</v>
@@ -6124,7 +6124,7 @@
         <v>268</v>
       </c>
       <c r="W76" s="2">
-        <v>46149</v>
+        <v>46262</v>
       </c>
       <c r="Y76" t="s">
         <v>261</v>
@@ -6165,16 +6165,16 @@
         <v>1</v>
       </c>
       <c r="J77">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K77">
-        <v>1545</v>
+        <v>1551</v>
       </c>
       <c r="L77" s="2">
-        <v>46274.20061342593</v>
+        <v>46276.35924768518</v>
       </c>
       <c r="M77" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N77" t="s">
         <v>256</v>
@@ -6233,16 +6233,16 @@
         <v>1</v>
       </c>
       <c r="J78">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K78">
-        <v>1545</v>
+        <v>1556</v>
       </c>
       <c r="L78" s="2">
-        <v>46274.20061342593</v>
+        <v>46276.35924768518</v>
       </c>
       <c r="M78" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N78" t="s">
         <v>256</v>
@@ -6301,13 +6301,13 @@
         <v>1</v>
       </c>
       <c r="J79">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K79">
-        <v>1630</v>
+        <v>1702</v>
       </c>
       <c r="L79" s="2">
-        <v>46274.20061342593</v>
+        <v>46276.35924768518</v>
       </c>
       <c r="M79" t="s">
         <v>261</v>
@@ -6328,7 +6328,7 @@
         <v>268</v>
       </c>
       <c r="W79" s="2">
-        <v>46273</v>
+        <v>46276</v>
       </c>
       <c r="Y79" t="s">
         <v>261</v>
@@ -6369,16 +6369,16 @@
         <v>1</v>
       </c>
       <c r="J80">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K80">
-        <v>1458</v>
+        <v>1530</v>
       </c>
       <c r="L80" s="2">
-        <v>46274.20061342593</v>
+        <v>46276.35924768518</v>
       </c>
       <c r="M80" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="N80" t="s">
         <v>256</v>
@@ -6396,7 +6396,7 @@
         <v>268</v>
       </c>
       <c r="W80" s="2">
-        <v>46268</v>
+        <v>46275</v>
       </c>
       <c r="Y80" t="s">
         <v>261</v>
@@ -6443,7 +6443,7 @@
         <v>3591</v>
       </c>
       <c r="L81" s="2">
-        <v>46274.20061342593</v>
+        <v>46276.35924768518</v>
       </c>
       <c r="M81" t="s">
         <v>263</v>
@@ -6747,7 +6747,7 @@
         <v>652</v>
       </c>
       <c r="L86" s="2">
-        <v>46274.20061342593</v>
+        <v>46276.35924768518</v>
       </c>
       <c r="M86" t="s">
         <v>263</v>
@@ -6815,7 +6815,7 @@
         <v>3609</v>
       </c>
       <c r="L87" s="2">
-        <v>46274.20061342593</v>
+        <v>46276.35924768518</v>
       </c>
       <c r="M87" t="s">
         <v>263</v>
@@ -6883,7 +6883,7 @@
         <v>3580</v>
       </c>
       <c r="L88" s="2">
-        <v>46274.20061342593</v>
+        <v>46276.35924768518</v>
       </c>
       <c r="M88" t="s">
         <v>263</v>
@@ -6992,7 +6992,7 @@
         <v>125</v>
       </c>
       <c r="L90" s="2">
-        <v>46274.20061342593</v>
+        <v>46276.35924768518</v>
       </c>
       <c r="M90" t="s">
         <v>264</v>

--- a/sites.xlsx
+++ b/sites.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1369" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1369" uniqueCount="275">
   <si>
     <t>site_name</t>
   </si>
@@ -808,6 +808,9 @@
     <t>NO_NEW</t>
   </si>
   <si>
+    <t>CHECK_REQUIRED</t>
+  </si>
+  <si>
     <t>FAIL</t>
   </si>
   <si>
@@ -835,7 +838,7 @@
     <t>PRIMARY_PARSER</t>
   </si>
   <si>
-    <t>selenium:detail_date</t>
+    <t>RECENT_HINT_BUT_ZERO</t>
   </si>
 </sst>
 </file>
@@ -1314,16 +1317,16 @@
         <v>257</v>
       </c>
       <c r="O2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W2" s="2">
         <v>46155</v>
@@ -1376,16 +1379,16 @@
         <v>257</v>
       </c>
       <c r="O3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W3" s="2">
         <v>46087</v>
@@ -1438,16 +1441,16 @@
         <v>257</v>
       </c>
       <c r="O4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W4" s="2">
         <v>46168</v>
@@ -1500,16 +1503,16 @@
         <v>257</v>
       </c>
       <c r="O5" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q5" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W5" s="2">
         <v>46161</v>
@@ -1553,7 +1556,7 @@
         <v>169</v>
       </c>
       <c r="L6" s="2">
-        <v>46276.35924768518</v>
+        <v>46279.23364583333</v>
       </c>
       <c r="M6" t="s">
         <v>263</v>
@@ -1562,16 +1565,16 @@
         <v>256</v>
       </c>
       <c r="O6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W6" s="2">
         <v>46168</v>
@@ -1633,16 +1636,16 @@
         <v>257</v>
       </c>
       <c r="O7" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P7" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R7" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W7" s="2">
         <v>46164</v>
@@ -1695,16 +1698,16 @@
         <v>257</v>
       </c>
       <c r="O8" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P8" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q8" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R8" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W8" s="2">
         <v>46155</v>
@@ -1757,16 +1760,16 @@
         <v>257</v>
       </c>
       <c r="O9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W9" s="2">
         <v>46045</v>
@@ -1819,16 +1822,16 @@
         <v>257</v>
       </c>
       <c r="O10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q10" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W10" s="2">
         <v>46045</v>
@@ -1881,16 +1884,16 @@
         <v>257</v>
       </c>
       <c r="O11" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P11" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q11" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R11" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W11" s="2">
         <v>46129</v>
@@ -1943,16 +1946,16 @@
         <v>257</v>
       </c>
       <c r="O12" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P12" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q12" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R12" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W12" s="2">
         <v>46164</v>
@@ -1996,7 +1999,7 @@
         <v>170</v>
       </c>
       <c r="L13" s="2">
-        <v>46276.35924768518</v>
+        <v>46279.23364583333</v>
       </c>
       <c r="M13" t="s">
         <v>263</v>
@@ -2005,16 +2008,16 @@
         <v>256</v>
       </c>
       <c r="O13" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P13" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q13" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R13" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W13" s="2">
         <v>46254</v>
@@ -2026,7 +2029,7 @@
         <v>261</v>
       </c>
       <c r="Z13" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AA13" t="s">
         <v>263</v>
@@ -2067,7 +2070,7 @@
         <v>3534</v>
       </c>
       <c r="L14" s="2">
-        <v>46276.35924768518</v>
+        <v>46279.23364583333</v>
       </c>
       <c r="M14" t="s">
         <v>263</v>
@@ -2076,16 +2079,16 @@
         <v>256</v>
       </c>
       <c r="O14" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P14" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q14" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R14" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W14" s="2">
         <v>46258</v>
@@ -2097,7 +2100,7 @@
         <v>263</v>
       </c>
       <c r="AA14" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="15" spans="1:27">
@@ -2135,7 +2138,7 @@
         <v>3522</v>
       </c>
       <c r="L15" s="2">
-        <v>46276.35924768518</v>
+        <v>46279.23364583333</v>
       </c>
       <c r="M15" t="s">
         <v>263</v>
@@ -2144,16 +2147,16 @@
         <v>256</v>
       </c>
       <c r="O15" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P15" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q15" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R15" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W15" s="2">
         <v>46268</v>
@@ -2165,7 +2168,7 @@
         <v>263</v>
       </c>
       <c r="AA15" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="16" spans="1:27">
@@ -2200,10 +2203,10 @@
         <v>2</v>
       </c>
       <c r="K16">
-        <v>3557</v>
+        <v>3573</v>
       </c>
       <c r="L16" s="2">
-        <v>46276.35924768518</v>
+        <v>46279.23365740741</v>
       </c>
       <c r="M16" t="s">
         <v>262</v>
@@ -2212,16 +2215,16 @@
         <v>256</v>
       </c>
       <c r="O16" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P16" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q16" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R16" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W16" s="2">
         <v>46272</v>
@@ -2233,7 +2236,7 @@
         <v>263</v>
       </c>
       <c r="AA16" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="17" spans="1:27">
@@ -2280,16 +2283,16 @@
         <v>257</v>
       </c>
       <c r="O17" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P17" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q17" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R17" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W17" s="2">
         <v>46113</v>
@@ -2324,43 +2327,43 @@
         <v>1</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18">
-        <v>3622</v>
+        <v>3627</v>
       </c>
       <c r="L18" s="2">
-        <v>46276.35924768518</v>
+        <v>46279.23365740741</v>
       </c>
       <c r="M18" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="N18" t="s">
         <v>256</v>
       </c>
       <c r="O18" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P18" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q18" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R18" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W18" s="2">
-        <v>46271</v>
+        <v>46278</v>
       </c>
       <c r="Y18" t="s">
         <v>261</v>
       </c>
       <c r="Z18" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AA18" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="19" spans="1:27">
@@ -2407,16 +2410,16 @@
         <v>257</v>
       </c>
       <c r="O19" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P19" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q19" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R19" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W19" s="2">
         <v>46163</v>
@@ -2466,16 +2469,16 @@
         <v>257</v>
       </c>
       <c r="O20" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P20" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q20" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R20" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W20" s="2">
         <v>46165</v>
@@ -2525,16 +2528,16 @@
         <v>257</v>
       </c>
       <c r="O21" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P21" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q21" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R21" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W21" s="2">
         <v>46166</v>
@@ -2575,7 +2578,7 @@
         <v>3591</v>
       </c>
       <c r="L22" s="2">
-        <v>46276.35924768518</v>
+        <v>46279.23365740741</v>
       </c>
       <c r="M22" t="s">
         <v>263</v>
@@ -2584,16 +2587,16 @@
         <v>256</v>
       </c>
       <c r="O22" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P22" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q22" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R22" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W22" s="2">
         <v>46168</v>
@@ -2605,7 +2608,7 @@
         <v>263</v>
       </c>
       <c r="AA22" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="23" spans="1:27">
@@ -2643,7 +2646,7 @@
         <v>3591</v>
       </c>
       <c r="L23" s="2">
-        <v>46276.35924768518</v>
+        <v>46279.23365740741</v>
       </c>
       <c r="M23" t="s">
         <v>263</v>
@@ -2652,16 +2655,16 @@
         <v>256</v>
       </c>
       <c r="O23" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P23" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q23" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R23" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W23" s="2">
         <v>46168</v>
@@ -2673,7 +2676,7 @@
         <v>263</v>
       </c>
       <c r="AA23" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="24" spans="1:27">
@@ -2711,7 +2714,7 @@
         <v>131</v>
       </c>
       <c r="L24" s="2">
-        <v>46276.35924768518</v>
+        <v>46279.23365740741</v>
       </c>
       <c r="M24" t="s">
         <v>263</v>
@@ -2720,16 +2723,16 @@
         <v>256</v>
       </c>
       <c r="O24" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P24" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q24" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R24" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W24" s="2">
         <v>46257</v>
@@ -2779,7 +2782,7 @@
         <v>145</v>
       </c>
       <c r="L25" s="2">
-        <v>46276.35924768518</v>
+        <v>46279.23365740741</v>
       </c>
       <c r="M25" t="s">
         <v>263</v>
@@ -2788,16 +2791,16 @@
         <v>256</v>
       </c>
       <c r="O25" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P25" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q25" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R25" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W25" s="2">
         <v>46272</v>
@@ -2841,34 +2844,34 @@
         <v>1</v>
       </c>
       <c r="J26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="L26" s="2">
-        <v>46276.35924768518</v>
+        <v>46279.23365740741</v>
       </c>
       <c r="M26" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="N26" t="s">
         <v>256</v>
       </c>
       <c r="O26" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P26" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q26" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R26" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W26" s="2">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="Y26" t="s">
         <v>261</v>
@@ -2877,7 +2880,7 @@
         <v>263</v>
       </c>
       <c r="AA26" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="27" spans="1:27">
@@ -2924,16 +2927,16 @@
         <v>257</v>
       </c>
       <c r="O27" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P27" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q27" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R27" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W27" s="2">
         <v>46172</v>
@@ -2983,16 +2986,16 @@
         <v>257</v>
       </c>
       <c r="O28" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P28" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q28" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R28" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W28" s="2">
         <v>46164</v>
@@ -3042,16 +3045,16 @@
         <v>257</v>
       </c>
       <c r="O29" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P29" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q29" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R29" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W29" s="2">
         <v>46168</v>
@@ -3101,16 +3104,16 @@
         <v>257</v>
       </c>
       <c r="O30" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P30" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q30" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R30" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W30" s="2">
         <v>46168</v>
@@ -3160,16 +3163,16 @@
         <v>257</v>
       </c>
       <c r="O31" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P31" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q31" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R31" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W31" s="2">
         <v>46168</v>
@@ -3204,13 +3207,13 @@
         <v>1</v>
       </c>
       <c r="J32">
-        <v>193</v>
+        <v>117</v>
       </c>
       <c r="K32">
-        <v>12566</v>
+        <v>12800</v>
       </c>
       <c r="L32" s="2">
-        <v>46276.35924768518</v>
+        <v>46279.23365740741</v>
       </c>
       <c r="M32" t="s">
         <v>261</v>
@@ -3219,28 +3222,28 @@
         <v>256</v>
       </c>
       <c r="O32" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P32" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q32" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R32" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W32" s="2">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="Y32" t="s">
         <v>261</v>
       </c>
       <c r="Z32" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AA32" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="33" spans="1:27">
@@ -3287,16 +3290,16 @@
         <v>257</v>
       </c>
       <c r="O33" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P33" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q33" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R33" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W33" s="2">
         <v>46168</v>
@@ -3346,16 +3349,16 @@
         <v>257</v>
       </c>
       <c r="O34" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P34" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q34" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R34" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W34" s="2">
         <v>46168</v>
@@ -3396,7 +3399,7 @@
         <v>3591</v>
       </c>
       <c r="L35" s="2">
-        <v>46276.35924768518</v>
+        <v>46279.23365740741</v>
       </c>
       <c r="M35" t="s">
         <v>263</v>
@@ -3405,16 +3408,16 @@
         <v>256</v>
       </c>
       <c r="O35" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P35" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q35" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R35" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W35" s="2">
         <v>46157</v>
@@ -3426,7 +3429,7 @@
         <v>263</v>
       </c>
       <c r="AA35" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="36" spans="1:27">
@@ -3464,7 +3467,7 @@
         <v>3591</v>
       </c>
       <c r="L36" s="2">
-        <v>46276.35924768518</v>
+        <v>46279.23365740741</v>
       </c>
       <c r="M36" t="s">
         <v>263</v>
@@ -3473,16 +3476,16 @@
         <v>256</v>
       </c>
       <c r="O36" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P36" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q36" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R36" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W36" s="2">
         <v>46168</v>
@@ -3494,7 +3497,7 @@
         <v>263</v>
       </c>
       <c r="AA36" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="37" spans="1:27">
@@ -3532,7 +3535,7 @@
         <v>1826</v>
       </c>
       <c r="L37" s="2">
-        <v>46276.35924768518</v>
+        <v>46279.23365740741</v>
       </c>
       <c r="M37" t="s">
         <v>263</v>
@@ -3541,16 +3544,16 @@
         <v>256</v>
       </c>
       <c r="O37" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P37" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q37" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R37" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W37" s="2">
         <v>46132</v>
@@ -3562,7 +3565,7 @@
         <v>263</v>
       </c>
       <c r="AA37" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="38" spans="1:27">
@@ -3600,7 +3603,7 @@
         <v>2937</v>
       </c>
       <c r="L38" s="2">
-        <v>46276.35924768518</v>
+        <v>46279.23365740741</v>
       </c>
       <c r="M38" t="s">
         <v>263</v>
@@ -3609,16 +3612,16 @@
         <v>256</v>
       </c>
       <c r="O38" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P38" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q38" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R38" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W38" s="2">
         <v>46113</v>
@@ -3630,7 +3633,7 @@
         <v>263</v>
       </c>
       <c r="AA38" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="39" spans="1:27">
@@ -3668,7 +3671,7 @@
         <v>3176</v>
       </c>
       <c r="L39" s="2">
-        <v>46276.35924768518</v>
+        <v>46279.23365740741</v>
       </c>
       <c r="M39" t="s">
         <v>263</v>
@@ -3677,16 +3680,16 @@
         <v>256</v>
       </c>
       <c r="O39" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P39" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q39" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R39" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W39" s="2">
         <v>46140</v>
@@ -3698,7 +3701,7 @@
         <v>263</v>
       </c>
       <c r="AA39" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="40" spans="1:27">
@@ -3736,7 +3739,7 @@
         <v>3128</v>
       </c>
       <c r="L40" s="2">
-        <v>46276.35924768518</v>
+        <v>46279.23365740741</v>
       </c>
       <c r="M40" t="s">
         <v>263</v>
@@ -3745,16 +3748,16 @@
         <v>256</v>
       </c>
       <c r="O40" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P40" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q40" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R40" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W40" s="2">
         <v>46024</v>
@@ -3766,7 +3769,7 @@
         <v>263</v>
       </c>
       <c r="AA40" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="41" spans="1:27">
@@ -3804,7 +3807,7 @@
         <v>3542</v>
       </c>
       <c r="L41" s="2">
-        <v>46276.35924768518</v>
+        <v>46279.23365740741</v>
       </c>
       <c r="M41" t="s">
         <v>263</v>
@@ -3813,16 +3816,16 @@
         <v>256</v>
       </c>
       <c r="O41" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P41" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q41" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R41" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W41" s="2">
         <v>46168</v>
@@ -3834,7 +3837,7 @@
         <v>263</v>
       </c>
       <c r="AA41" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="42" spans="1:27">
@@ -3872,7 +3875,7 @@
         <v>3533</v>
       </c>
       <c r="L42" s="2">
-        <v>46276.35924768518</v>
+        <v>46279.23365740741</v>
       </c>
       <c r="M42" t="s">
         <v>263</v>
@@ -3881,16 +3884,16 @@
         <v>256</v>
       </c>
       <c r="O42" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P42" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q42" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R42" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W42" s="2">
         <v>46164</v>
@@ -3902,7 +3905,7 @@
         <v>263</v>
       </c>
       <c r="AA42" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="43" spans="1:27">
@@ -3940,7 +3943,7 @@
         <v>3513</v>
       </c>
       <c r="L43" s="2">
-        <v>46276.35924768518</v>
+        <v>46279.23365740741</v>
       </c>
       <c r="M43" t="s">
         <v>263</v>
@@ -3949,16 +3952,16 @@
         <v>256</v>
       </c>
       <c r="O43" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P43" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q43" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R43" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W43" s="2">
         <v>46112</v>
@@ -3970,7 +3973,7 @@
         <v>263</v>
       </c>
       <c r="AA43" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="44" spans="1:27">
@@ -4017,16 +4020,16 @@
         <v>257</v>
       </c>
       <c r="O44" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P44" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q44" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R44" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W44" s="2">
         <v>46171</v>
@@ -4061,34 +4064,34 @@
         <v>1</v>
       </c>
       <c r="J45">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="K45">
-        <v>3507</v>
+        <v>3569</v>
       </c>
       <c r="L45" s="2">
-        <v>46276.35924768518</v>
+        <v>46279.23365740741</v>
       </c>
       <c r="M45" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N45" t="s">
         <v>256</v>
       </c>
       <c r="O45" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P45" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q45" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R45" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W45" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="Y45" t="s">
         <v>261</v>
@@ -4097,7 +4100,7 @@
         <v>263</v>
       </c>
       <c r="AA45" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="46" spans="1:27">
@@ -4129,13 +4132,13 @@
         <v>1</v>
       </c>
       <c r="J46">
-        <v>180</v>
+        <v>36</v>
       </c>
       <c r="K46">
-        <v>8012</v>
+        <v>8741</v>
       </c>
       <c r="L46" s="2">
-        <v>46276.35924768518</v>
+        <v>46279.23365740741</v>
       </c>
       <c r="M46" t="s">
         <v>261</v>
@@ -4144,19 +4147,19 @@
         <v>256</v>
       </c>
       <c r="O46" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P46" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q46" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R46" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W46" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="Y46" t="s">
         <v>261</v>
@@ -4165,7 +4168,7 @@
         <v>263</v>
       </c>
       <c r="AA46" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="47" spans="1:27">
@@ -4197,13 +4200,13 @@
         <v>1</v>
       </c>
       <c r="J47">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K47">
-        <v>4173</v>
+        <v>4323</v>
       </c>
       <c r="L47" s="2">
-        <v>46276.35924768518</v>
+        <v>46279.23365740741</v>
       </c>
       <c r="M47" t="s">
         <v>261</v>
@@ -4212,19 +4215,19 @@
         <v>256</v>
       </c>
       <c r="O47" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P47" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q47" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R47" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W47" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="Y47" t="s">
         <v>261</v>
@@ -4233,7 +4236,7 @@
         <v>263</v>
       </c>
       <c r="AA47" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="48" spans="1:27">
@@ -4271,7 +4274,7 @@
         <v>2299</v>
       </c>
       <c r="L48" s="2">
-        <v>46276.35924768518</v>
+        <v>46279.23365740741</v>
       </c>
       <c r="M48" t="s">
         <v>263</v>
@@ -4280,16 +4283,16 @@
         <v>256</v>
       </c>
       <c r="O48" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P48" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q48" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R48" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W48" s="2">
         <v>46168</v>
@@ -4301,7 +4304,7 @@
         <v>263</v>
       </c>
       <c r="AA48" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="49" spans="1:27">
@@ -4333,31 +4336,31 @@
         <v>1</v>
       </c>
       <c r="J49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K49">
         <v>1505</v>
       </c>
       <c r="L49" s="2">
-        <v>46276.35924768518</v>
+        <v>46279.23365740741</v>
       </c>
       <c r="M49" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N49" t="s">
         <v>256</v>
       </c>
       <c r="O49" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P49" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q49" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R49" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W49" s="2">
         <v>46273</v>
@@ -4369,7 +4372,7 @@
         <v>263</v>
       </c>
       <c r="AA49" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="50" spans="1:27">
@@ -4401,34 +4404,34 @@
         <v>1</v>
       </c>
       <c r="J50">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K50">
-        <v>1669</v>
+        <v>1691</v>
       </c>
       <c r="L50" s="2">
-        <v>46276.35924768518</v>
+        <v>46279.23365740741</v>
       </c>
       <c r="M50" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N50" t="s">
         <v>256</v>
       </c>
       <c r="O50" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P50" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q50" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R50" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W50" s="2">
-        <v>46273</v>
+        <v>46276</v>
       </c>
       <c r="Y50" t="s">
         <v>261</v>
@@ -4437,7 +4440,7 @@
         <v>263</v>
       </c>
       <c r="AA50" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="51" spans="1:27">
@@ -4469,31 +4472,31 @@
         <v>1</v>
       </c>
       <c r="J51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K51">
         <v>1496</v>
       </c>
       <c r="L51" s="2">
-        <v>46276.35924768518</v>
+        <v>46279.23365740741</v>
       </c>
       <c r="M51" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N51" t="s">
         <v>256</v>
       </c>
       <c r="O51" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P51" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q51" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R51" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W51" s="2">
         <v>46273</v>
@@ -4505,7 +4508,7 @@
         <v>263</v>
       </c>
       <c r="AA51" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="52" spans="1:27">
@@ -4543,7 +4546,7 @@
         <v>1466</v>
       </c>
       <c r="L52" s="2">
-        <v>46276.35924768518</v>
+        <v>46279.23365740741</v>
       </c>
       <c r="M52" t="s">
         <v>263</v>
@@ -4552,16 +4555,16 @@
         <v>256</v>
       </c>
       <c r="O52" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P52" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q52" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R52" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W52" s="2">
         <v>46142</v>
@@ -4573,7 +4576,7 @@
         <v>263</v>
       </c>
       <c r="AA52" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="53" spans="1:27">
@@ -4605,13 +4608,13 @@
         <v>1</v>
       </c>
       <c r="J53">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K53">
-        <v>2095</v>
+        <v>2139</v>
       </c>
       <c r="L53" s="2">
-        <v>46276.35924768518</v>
+        <v>46279.23365740741</v>
       </c>
       <c r="M53" t="s">
         <v>261</v>
@@ -4620,19 +4623,19 @@
         <v>256</v>
       </c>
       <c r="O53" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P53" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q53" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R53" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W53" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="Y53" t="s">
         <v>261</v>
@@ -4641,7 +4644,7 @@
         <v>263</v>
       </c>
       <c r="AA53" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="54" spans="1:27">
@@ -4673,31 +4676,31 @@
         <v>1</v>
       </c>
       <c r="J54">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K54">
-        <v>1350</v>
+        <v>1356</v>
       </c>
       <c r="L54" s="2">
-        <v>46276.35924768518</v>
+        <v>46279.23365740741</v>
       </c>
       <c r="M54" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N54" t="s">
         <v>256</v>
       </c>
       <c r="O54" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P54" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q54" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R54" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W54" s="2">
         <v>46275</v>
@@ -4709,7 +4712,7 @@
         <v>263</v>
       </c>
       <c r="AA54" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="55" spans="1:27">
@@ -4741,31 +4744,31 @@
         <v>1</v>
       </c>
       <c r="J55">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="K55">
-        <v>2194</v>
+        <v>2258</v>
       </c>
       <c r="L55" s="2">
-        <v>46276.35924768518</v>
+        <v>46279.23365740741</v>
       </c>
       <c r="M55" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N55" t="s">
         <v>256</v>
       </c>
       <c r="O55" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P55" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q55" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R55" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W55" s="2">
         <v>46276</v>
@@ -4774,10 +4777,10 @@
         <v>261</v>
       </c>
       <c r="Z55" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AA55" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="56" spans="1:27">
@@ -4824,16 +4827,16 @@
         <v>257</v>
       </c>
       <c r="O56" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P56" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q56" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R56" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W56" s="2">
         <v>46161</v>
@@ -4868,31 +4871,31 @@
         <v>1</v>
       </c>
       <c r="J57">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K57">
-        <v>3936</v>
+        <v>3950</v>
       </c>
       <c r="L57" s="2">
-        <v>46276.35924768518</v>
+        <v>46279.23365740741</v>
       </c>
       <c r="M57" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N57" t="s">
         <v>256</v>
       </c>
       <c r="O57" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P57" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q57" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R57" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W57" s="2">
         <v>46276</v>
@@ -4904,7 +4907,7 @@
         <v>263</v>
       </c>
       <c r="AA57" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="58" spans="1:27">
@@ -4951,16 +4954,16 @@
         <v>257</v>
       </c>
       <c r="O58" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P58" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q58" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R58" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W58" s="2">
         <v>46148</v>
@@ -5010,16 +5013,16 @@
         <v>257</v>
       </c>
       <c r="O59" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P59" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q59" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R59" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W59" s="2">
         <v>46168</v>
@@ -5069,16 +5072,16 @@
         <v>257</v>
       </c>
       <c r="O60" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P60" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q60" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R60" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W60" s="2">
         <v>46164</v>
@@ -5128,16 +5131,16 @@
         <v>257</v>
       </c>
       <c r="O61" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P61" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q61" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R61" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W61" s="2">
         <v>46168</v>
@@ -5172,31 +5175,31 @@
         <v>1</v>
       </c>
       <c r="J62">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K62">
         <v>1663</v>
       </c>
       <c r="L62" s="2">
-        <v>46276.35924768518</v>
+        <v>46279.23365740741</v>
       </c>
       <c r="M62" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N62" t="s">
         <v>256</v>
       </c>
       <c r="O62" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P62" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q62" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R62" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W62" s="2">
         <v>46273</v>
@@ -5208,7 +5211,7 @@
         <v>263</v>
       </c>
       <c r="AA62" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="63" spans="1:27">
@@ -5255,16 +5258,16 @@
         <v>257</v>
       </c>
       <c r="O63" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P63" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q63" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R63" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W63" s="2">
         <v>46164</v>
@@ -5314,16 +5317,16 @@
         <v>257</v>
       </c>
       <c r="O64" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P64" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q64" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R64" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W64" s="2">
         <v>46168</v>
@@ -5358,13 +5361,13 @@
         <v>1</v>
       </c>
       <c r="J65">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="K65">
-        <v>4283</v>
+        <v>4421</v>
       </c>
       <c r="L65" s="2">
-        <v>46276.35924768518</v>
+        <v>46279.23365740741</v>
       </c>
       <c r="M65" t="s">
         <v>261</v>
@@ -5373,28 +5376,28 @@
         <v>256</v>
       </c>
       <c r="O65" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P65" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q65" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R65" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W65" s="2">
-        <v>46275</v>
+        <v>46279</v>
       </c>
       <c r="Y65" t="s">
         <v>261</v>
       </c>
       <c r="Z65" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AA65" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="66" spans="1:27">
@@ -5432,7 +5435,7 @@
         <v>3062</v>
       </c>
       <c r="L66" s="2">
-        <v>46276.35924768518</v>
+        <v>46279.23365740741</v>
       </c>
       <c r="M66" t="s">
         <v>263</v>
@@ -5441,16 +5444,16 @@
         <v>256</v>
       </c>
       <c r="O66" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P66" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q66" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R66" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W66" s="2">
         <v>46261</v>
@@ -5462,7 +5465,7 @@
         <v>263</v>
       </c>
       <c r="AA66" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="67" spans="1:27">
@@ -5500,7 +5503,7 @@
         <v>1727</v>
       </c>
       <c r="L67" s="2">
-        <v>46276.35924768518</v>
+        <v>46279.23365740741</v>
       </c>
       <c r="M67" t="s">
         <v>263</v>
@@ -5509,16 +5512,16 @@
         <v>256</v>
       </c>
       <c r="O67" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P67" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q67" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R67" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W67" s="2">
         <v>46275</v>
@@ -5527,10 +5530,10 @@
         <v>261</v>
       </c>
       <c r="Z67" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AA67" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="68" spans="1:27">
@@ -5562,13 +5565,13 @@
         <v>1</v>
       </c>
       <c r="J68">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="K68">
-        <v>3971</v>
+        <v>4115</v>
       </c>
       <c r="L68" s="2">
-        <v>46276.35924768518</v>
+        <v>46279.23365740741</v>
       </c>
       <c r="M68" t="s">
         <v>261</v>
@@ -5577,16 +5580,16 @@
         <v>256</v>
       </c>
       <c r="O68" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P68" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q68" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R68" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W68" s="2">
         <v>46276</v>
@@ -5595,10 +5598,10 @@
         <v>261</v>
       </c>
       <c r="Z68" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AA68" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="69" spans="1:27">
@@ -5636,7 +5639,7 @@
         <v>3058</v>
       </c>
       <c r="L69" s="2">
-        <v>46276.35924768518</v>
+        <v>46279.23365740741</v>
       </c>
       <c r="M69" t="s">
         <v>263</v>
@@ -5645,16 +5648,16 @@
         <v>256</v>
       </c>
       <c r="O69" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P69" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q69" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R69" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W69" s="2">
         <v>46259</v>
@@ -5666,7 +5669,7 @@
         <v>263</v>
       </c>
       <c r="AA69" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="70" spans="1:27">
@@ -5698,31 +5701,31 @@
         <v>1</v>
       </c>
       <c r="J70">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K70">
-        <v>2454</v>
+        <v>2476</v>
       </c>
       <c r="L70" s="2">
-        <v>46276.35924768518</v>
+        <v>46279.23365740741</v>
       </c>
       <c r="M70" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N70" t="s">
         <v>256</v>
       </c>
       <c r="O70" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P70" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q70" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R70" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W70" s="2">
         <v>46276</v>
@@ -5731,10 +5734,10 @@
         <v>261</v>
       </c>
       <c r="Z70" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AA70" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="71" spans="1:27">
@@ -5766,13 +5769,13 @@
         <v>1</v>
       </c>
       <c r="J71">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K71">
-        <v>2445</v>
+        <v>2529</v>
       </c>
       <c r="L71" s="2">
-        <v>46276.35924768518</v>
+        <v>46279.23365740741</v>
       </c>
       <c r="M71" t="s">
         <v>261</v>
@@ -5781,16 +5784,16 @@
         <v>256</v>
       </c>
       <c r="O71" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P71" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q71" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R71" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W71" s="2">
         <v>46276</v>
@@ -5799,10 +5802,10 @@
         <v>261</v>
       </c>
       <c r="Z71" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AA71" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="72" spans="1:27">
@@ -5849,16 +5852,16 @@
         <v>257</v>
       </c>
       <c r="O72" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P72" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q72" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R72" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W72" s="2">
         <v>46164</v>
@@ -5893,34 +5896,34 @@
         <v>1</v>
       </c>
       <c r="J73">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K73">
-        <v>1316</v>
+        <v>1350</v>
       </c>
       <c r="L73" s="2">
-        <v>46276.35924768518</v>
+        <v>46279.23365740741</v>
       </c>
       <c r="M73" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="N73" t="s">
         <v>256</v>
       </c>
       <c r="O73" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P73" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q73" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R73" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W73" s="2">
-        <v>46265</v>
+        <v>46279</v>
       </c>
       <c r="Y73" t="s">
         <v>261</v>
@@ -5929,7 +5932,7 @@
         <v>263</v>
       </c>
       <c r="AA73" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="74" spans="1:27">
@@ -5967,7 +5970,7 @@
         <v>1449</v>
       </c>
       <c r="L74" s="2">
-        <v>46276.35924768518</v>
+        <v>46279.23365740741</v>
       </c>
       <c r="M74" t="s">
         <v>263</v>
@@ -5976,16 +5979,16 @@
         <v>256</v>
       </c>
       <c r="O74" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P74" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q74" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R74" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W74" s="2">
         <v>46185</v>
@@ -5997,7 +6000,7 @@
         <v>263</v>
       </c>
       <c r="AA74" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="75" spans="1:27">
@@ -6035,7 +6038,7 @@
         <v>1482</v>
       </c>
       <c r="L75" s="2">
-        <v>46276.35924768518</v>
+        <v>46279.23365740741</v>
       </c>
       <c r="M75" t="s">
         <v>263</v>
@@ -6044,16 +6047,16 @@
         <v>256</v>
       </c>
       <c r="O75" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P75" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q75" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R75" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W75" s="2">
         <v>46265</v>
@@ -6065,7 +6068,7 @@
         <v>263</v>
       </c>
       <c r="AA75" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="76" spans="1:27">
@@ -6103,7 +6106,7 @@
         <v>1527</v>
       </c>
       <c r="L76" s="2">
-        <v>46276.35924768518</v>
+        <v>46279.23365740741</v>
       </c>
       <c r="M76" t="s">
         <v>263</v>
@@ -6112,16 +6115,16 @@
         <v>256</v>
       </c>
       <c r="O76" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P76" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q76" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R76" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W76" s="2">
         <v>46262</v>
@@ -6133,7 +6136,7 @@
         <v>263</v>
       </c>
       <c r="AA76" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="77" spans="1:27">
@@ -6171,7 +6174,7 @@
         <v>1551</v>
       </c>
       <c r="L77" s="2">
-        <v>46276.35924768518</v>
+        <v>46279.23365740741</v>
       </c>
       <c r="M77" t="s">
         <v>263</v>
@@ -6180,16 +6183,16 @@
         <v>256</v>
       </c>
       <c r="O77" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P77" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q77" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R77" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W77" s="2">
         <v>46272</v>
@@ -6201,7 +6204,7 @@
         <v>263</v>
       </c>
       <c r="AA77" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="78" spans="1:27">
@@ -6233,34 +6236,34 @@
         <v>1</v>
       </c>
       <c r="J78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K78">
-        <v>1556</v>
+        <v>1564</v>
       </c>
       <c r="L78" s="2">
-        <v>46276.35924768518</v>
+        <v>46279.23365740741</v>
       </c>
       <c r="M78" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="N78" t="s">
         <v>256</v>
       </c>
       <c r="O78" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P78" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q78" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R78" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W78" s="2">
-        <v>46272</v>
+        <v>46276</v>
       </c>
       <c r="Y78" t="s">
         <v>261</v>
@@ -6269,7 +6272,7 @@
         <v>263</v>
       </c>
       <c r="AA78" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="79" spans="1:27">
@@ -6301,13 +6304,13 @@
         <v>1</v>
       </c>
       <c r="J79">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K79">
-        <v>1702</v>
+        <v>1729</v>
       </c>
       <c r="L79" s="2">
-        <v>46276.35924768518</v>
+        <v>46279.23365740741</v>
       </c>
       <c r="M79" t="s">
         <v>261</v>
@@ -6316,16 +6319,16 @@
         <v>256</v>
       </c>
       <c r="O79" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P79" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q79" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R79" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W79" s="2">
         <v>46276</v>
@@ -6337,7 +6340,7 @@
         <v>263</v>
       </c>
       <c r="AA79" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="80" spans="1:27">
@@ -6369,31 +6372,31 @@
         <v>1</v>
       </c>
       <c r="J80">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K80">
-        <v>1530</v>
+        <v>1572</v>
       </c>
       <c r="L80" s="2">
-        <v>46276.35924768518</v>
+        <v>46279.23365740741</v>
       </c>
       <c r="M80" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="N80" t="s">
         <v>256</v>
       </c>
       <c r="O80" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P80" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q80" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R80" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W80" s="2">
         <v>46275</v>
@@ -6405,7 +6408,7 @@
         <v>263</v>
       </c>
       <c r="AA80" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="81" spans="1:27">
@@ -6443,7 +6446,7 @@
         <v>3591</v>
       </c>
       <c r="L81" s="2">
-        <v>46276.35924768518</v>
+        <v>46279.23365740741</v>
       </c>
       <c r="M81" t="s">
         <v>263</v>
@@ -6452,16 +6455,16 @@
         <v>256</v>
       </c>
       <c r="O81" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P81" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q81" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R81" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W81" s="2">
         <v>46160</v>
@@ -6473,7 +6476,7 @@
         <v>263</v>
       </c>
       <c r="AA81" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="82" spans="1:27">
@@ -6520,16 +6523,16 @@
         <v>257</v>
       </c>
       <c r="O82" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P82" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q82" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R82" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W82" s="2">
         <v>46161</v>
@@ -6579,16 +6582,16 @@
         <v>257</v>
       </c>
       <c r="O83" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P83" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q83" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R83" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W83" s="2">
         <v>46168</v>
@@ -6638,16 +6641,16 @@
         <v>257</v>
       </c>
       <c r="O84" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P84" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q84" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R84" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W84" s="2">
         <v>46164</v>
@@ -6697,16 +6700,16 @@
         <v>257</v>
       </c>
       <c r="O85" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P85" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q85" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R85" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W85" s="2">
         <v>46168</v>
@@ -6747,7 +6750,7 @@
         <v>652</v>
       </c>
       <c r="L86" s="2">
-        <v>46276.35924768518</v>
+        <v>46279.23365740741</v>
       </c>
       <c r="M86" t="s">
         <v>263</v>
@@ -6756,16 +6759,16 @@
         <v>256</v>
       </c>
       <c r="O86" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P86" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q86" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R86" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W86" s="2">
         <v>46164</v>
@@ -6777,7 +6780,7 @@
         <v>263</v>
       </c>
       <c r="AA86" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="87" spans="1:27">
@@ -6815,7 +6818,7 @@
         <v>3609</v>
       </c>
       <c r="L87" s="2">
-        <v>46276.35924768518</v>
+        <v>46279.23365740741</v>
       </c>
       <c r="M87" t="s">
         <v>263</v>
@@ -6824,16 +6827,16 @@
         <v>256</v>
       </c>
       <c r="O87" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P87" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q87" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R87" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W87" s="2">
         <v>46248</v>
@@ -6845,7 +6848,7 @@
         <v>263</v>
       </c>
       <c r="AA87" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="88" spans="1:27">
@@ -6883,7 +6886,7 @@
         <v>3580</v>
       </c>
       <c r="L88" s="2">
-        <v>46276.35924768518</v>
+        <v>46279.23365740741</v>
       </c>
       <c r="M88" t="s">
         <v>263</v>
@@ -6892,16 +6895,16 @@
         <v>256</v>
       </c>
       <c r="O88" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P88" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q88" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R88" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W88" s="2">
         <v>46253.16666666666</v>
@@ -6913,7 +6916,7 @@
         <v>263</v>
       </c>
       <c r="AA88" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="89" spans="1:27">
@@ -6945,16 +6948,16 @@
         <v>257</v>
       </c>
       <c r="O89" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P89" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q89" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R89" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="90" spans="1:27">
@@ -6992,25 +6995,25 @@
         <v>125</v>
       </c>
       <c r="L90" s="2">
-        <v>46276.35924768518</v>
+        <v>46279.23365740741</v>
       </c>
       <c r="M90" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N90" t="s">
         <v>256</v>
       </c>
       <c r="O90" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P90" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q90" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R90" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W90" s="2">
         <v>46154</v>
@@ -7051,16 +7054,16 @@
         <v>256</v>
       </c>
       <c r="O91" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P91" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q91" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R91" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W91" s="2">
         <v>46154</v>
@@ -7110,16 +7113,16 @@
         <v>257</v>
       </c>
       <c r="O92" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P92" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q92" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R92" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W92" s="2">
         <v>46164</v>

--- a/sites.xlsx
+++ b/sites.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1369" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1369" uniqueCount="273">
   <si>
     <t>site_name</t>
   </si>
@@ -808,9 +808,6 @@
     <t>NO_NEW</t>
   </si>
   <si>
-    <t>CHECK_REQUIRED</t>
-  </si>
-  <si>
     <t>FAIL</t>
   </si>
   <si>
@@ -836,9 +833,6 @@
   </si>
   <si>
     <t>PRIMARY_PARSER</t>
-  </si>
-  <si>
-    <t>RECENT_HINT_BUT_ZERO</t>
   </si>
 </sst>
 </file>
@@ -1317,16 +1311,16 @@
         <v>257</v>
       </c>
       <c r="O2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W2" s="2">
         <v>46155</v>
@@ -1379,16 +1373,16 @@
         <v>257</v>
       </c>
       <c r="O3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W3" s="2">
         <v>46087</v>
@@ -1441,16 +1435,16 @@
         <v>257</v>
       </c>
       <c r="O4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W4" s="2">
         <v>46168</v>
@@ -1503,16 +1497,16 @@
         <v>257</v>
       </c>
       <c r="O5" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P5" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R5" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W5" s="2">
         <v>46161</v>
@@ -1556,7 +1550,7 @@
         <v>169</v>
       </c>
       <c r="L6" s="2">
-        <v>46279.23364583333</v>
+        <v>46282.24168981481</v>
       </c>
       <c r="M6" t="s">
         <v>263</v>
@@ -1565,16 +1559,16 @@
         <v>256</v>
       </c>
       <c r="O6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W6" s="2">
         <v>46168</v>
@@ -1636,16 +1630,16 @@
         <v>257</v>
       </c>
       <c r="O7" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P7" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R7" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W7" s="2">
         <v>46164</v>
@@ -1698,16 +1692,16 @@
         <v>257</v>
       </c>
       <c r="O8" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P8" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q8" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R8" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W8" s="2">
         <v>46155</v>
@@ -1760,16 +1754,16 @@
         <v>257</v>
       </c>
       <c r="O9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P9" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q9" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R9" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W9" s="2">
         <v>46045</v>
@@ -1822,16 +1816,16 @@
         <v>257</v>
       </c>
       <c r="O10" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P10" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q10" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R10" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W10" s="2">
         <v>46045</v>
@@ -1884,16 +1878,16 @@
         <v>257</v>
       </c>
       <c r="O11" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P11" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q11" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R11" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W11" s="2">
         <v>46129</v>
@@ -1946,16 +1940,16 @@
         <v>257</v>
       </c>
       <c r="O12" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P12" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R12" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W12" s="2">
         <v>46164</v>
@@ -1999,7 +1993,7 @@
         <v>170</v>
       </c>
       <c r="L13" s="2">
-        <v>46279.23364583333</v>
+        <v>46282.24168981481</v>
       </c>
       <c r="M13" t="s">
         <v>263</v>
@@ -2008,16 +2002,16 @@
         <v>256</v>
       </c>
       <c r="O13" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P13" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q13" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R13" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W13" s="2">
         <v>46254</v>
@@ -2029,7 +2023,7 @@
         <v>261</v>
       </c>
       <c r="Z13" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="AA13" t="s">
         <v>263</v>
@@ -2064,34 +2058,34 @@
         <v>1</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14">
-        <v>3534</v>
+        <v>3540</v>
       </c>
       <c r="L14" s="2">
-        <v>46279.23364583333</v>
+        <v>46282.24168981481</v>
       </c>
       <c r="M14" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="N14" t="s">
         <v>256</v>
       </c>
       <c r="O14" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P14" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q14" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R14" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W14" s="2">
-        <v>46258</v>
+        <v>46280</v>
       </c>
       <c r="Y14" t="s">
         <v>261</v>
@@ -2100,7 +2094,7 @@
         <v>263</v>
       </c>
       <c r="AA14" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="15" spans="1:27">
@@ -2132,34 +2126,34 @@
         <v>1</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15">
-        <v>3522</v>
+        <v>3531</v>
       </c>
       <c r="L15" s="2">
-        <v>46279.23364583333</v>
+        <v>46282.24168981481</v>
       </c>
       <c r="M15" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="N15" t="s">
         <v>256</v>
       </c>
       <c r="O15" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P15" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q15" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R15" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W15" s="2">
-        <v>46268</v>
+        <v>46279</v>
       </c>
       <c r="Y15" t="s">
         <v>261</v>
@@ -2168,7 +2162,7 @@
         <v>263</v>
       </c>
       <c r="AA15" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="16" spans="1:27">
@@ -2203,10 +2197,10 @@
         <v>2</v>
       </c>
       <c r="K16">
-        <v>3573</v>
+        <v>3586</v>
       </c>
       <c r="L16" s="2">
-        <v>46279.23365740741</v>
+        <v>46282.24168981481</v>
       </c>
       <c r="M16" t="s">
         <v>262</v>
@@ -2215,19 +2209,19 @@
         <v>256</v>
       </c>
       <c r="O16" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P16" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q16" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R16" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W16" s="2">
-        <v>46272</v>
+        <v>46281</v>
       </c>
       <c r="Y16" t="s">
         <v>261</v>
@@ -2236,7 +2230,7 @@
         <v>263</v>
       </c>
       <c r="AA16" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="17" spans="1:27">
@@ -2283,16 +2277,16 @@
         <v>257</v>
       </c>
       <c r="O17" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P17" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q17" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R17" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W17" s="2">
         <v>46113</v>
@@ -2327,31 +2321,31 @@
         <v>1</v>
       </c>
       <c r="J18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18">
-        <v>3627</v>
+        <v>3630</v>
       </c>
       <c r="L18" s="2">
-        <v>46279.23365740741</v>
+        <v>46282.24168981481</v>
       </c>
       <c r="M18" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N18" t="s">
         <v>256</v>
       </c>
       <c r="O18" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P18" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q18" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R18" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W18" s="2">
         <v>46278</v>
@@ -2360,10 +2354,10 @@
         <v>261</v>
       </c>
       <c r="Z18" t="s">
+        <v>271</v>
+      </c>
+      <c r="AA18" t="s">
         <v>272</v>
-      </c>
-      <c r="AA18" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="19" spans="1:27">
@@ -2410,16 +2404,16 @@
         <v>257</v>
       </c>
       <c r="O19" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P19" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q19" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R19" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W19" s="2">
         <v>46163</v>
@@ -2469,16 +2463,16 @@
         <v>257</v>
       </c>
       <c r="O20" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P20" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q20" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R20" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W20" s="2">
         <v>46165</v>
@@ -2528,16 +2522,16 @@
         <v>257</v>
       </c>
       <c r="O21" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P21" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q21" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R21" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W21" s="2">
         <v>46166</v>
@@ -2578,7 +2572,7 @@
         <v>3591</v>
       </c>
       <c r="L22" s="2">
-        <v>46279.23365740741</v>
+        <v>46282.24168981481</v>
       </c>
       <c r="M22" t="s">
         <v>263</v>
@@ -2587,16 +2581,16 @@
         <v>256</v>
       </c>
       <c r="O22" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P22" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q22" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R22" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W22" s="2">
         <v>46168</v>
@@ -2608,7 +2602,7 @@
         <v>263</v>
       </c>
       <c r="AA22" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="23" spans="1:27">
@@ -2646,7 +2640,7 @@
         <v>3591</v>
       </c>
       <c r="L23" s="2">
-        <v>46279.23365740741</v>
+        <v>46282.24168981481</v>
       </c>
       <c r="M23" t="s">
         <v>263</v>
@@ -2655,16 +2649,16 @@
         <v>256</v>
       </c>
       <c r="O23" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q23" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W23" s="2">
         <v>46168</v>
@@ -2676,7 +2670,7 @@
         <v>263</v>
       </c>
       <c r="AA23" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="24" spans="1:27">
@@ -2714,7 +2708,7 @@
         <v>131</v>
       </c>
       <c r="L24" s="2">
-        <v>46279.23365740741</v>
+        <v>46282.24168981481</v>
       </c>
       <c r="M24" t="s">
         <v>263</v>
@@ -2723,16 +2717,16 @@
         <v>256</v>
       </c>
       <c r="O24" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P24" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q24" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R24" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W24" s="2">
         <v>46257</v>
@@ -2782,7 +2776,7 @@
         <v>145</v>
       </c>
       <c r="L25" s="2">
-        <v>46279.23365740741</v>
+        <v>46282.24168981481</v>
       </c>
       <c r="M25" t="s">
         <v>263</v>
@@ -2791,16 +2785,16 @@
         <v>256</v>
       </c>
       <c r="O25" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P25" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q25" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R25" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W25" s="2">
         <v>46272</v>
@@ -2847,28 +2841,28 @@
         <v>0</v>
       </c>
       <c r="K26">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L26" s="2">
-        <v>46279.23365740741</v>
+        <v>46282.24168981481</v>
       </c>
       <c r="M26" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="N26" t="s">
         <v>256</v>
       </c>
       <c r="O26" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P26" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q26" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R26" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W26" s="2">
         <v>46276</v>
@@ -2880,7 +2874,7 @@
         <v>263</v>
       </c>
       <c r="AA26" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
     </row>
     <row r="27" spans="1:27">
@@ -2927,16 +2921,16 @@
         <v>257</v>
       </c>
       <c r="O27" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P27" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q27" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R27" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W27" s="2">
         <v>46172</v>
@@ -2986,16 +2980,16 @@
         <v>257</v>
       </c>
       <c r="O28" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P28" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q28" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R28" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W28" s="2">
         <v>46164</v>
@@ -3045,16 +3039,16 @@
         <v>257</v>
       </c>
       <c r="O29" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P29" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q29" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R29" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W29" s="2">
         <v>46168</v>
@@ -3104,16 +3098,16 @@
         <v>257</v>
       </c>
       <c r="O30" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P30" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q30" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R30" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W30" s="2">
         <v>46168</v>
@@ -3163,16 +3157,16 @@
         <v>257</v>
       </c>
       <c r="O31" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P31" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q31" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R31" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W31" s="2">
         <v>46168</v>
@@ -3207,13 +3201,13 @@
         <v>1</v>
       </c>
       <c r="J32">
-        <v>117</v>
+        <v>85</v>
       </c>
       <c r="K32">
-        <v>12800</v>
+        <v>13811</v>
       </c>
       <c r="L32" s="2">
-        <v>46279.23365740741</v>
+        <v>46282.24168981481</v>
       </c>
       <c r="M32" t="s">
         <v>261</v>
@@ -3222,28 +3216,28 @@
         <v>256</v>
       </c>
       <c r="O32" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P32" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q32" t="s">
+        <v>270</v>
+      </c>
+      <c r="R32" t="s">
+        <v>268</v>
+      </c>
+      <c r="W32" s="2">
+        <v>46282</v>
+      </c>
+      <c r="Y32" t="s">
+        <v>261</v>
+      </c>
+      <c r="Z32" t="s">
         <v>271</v>
       </c>
-      <c r="R32" t="s">
-        <v>269</v>
-      </c>
-      <c r="W32" s="2">
-        <v>46279</v>
-      </c>
-      <c r="Y32" t="s">
-        <v>261</v>
-      </c>
-      <c r="Z32" t="s">
+      <c r="AA32" t="s">
         <v>272</v>
-      </c>
-      <c r="AA32" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="33" spans="1:27">
@@ -3290,16 +3284,16 @@
         <v>257</v>
       </c>
       <c r="O33" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P33" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q33" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R33" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W33" s="2">
         <v>46168</v>
@@ -3349,16 +3343,16 @@
         <v>257</v>
       </c>
       <c r="O34" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P34" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R34" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W34" s="2">
         <v>46168</v>
@@ -3399,7 +3393,7 @@
         <v>3591</v>
       </c>
       <c r="L35" s="2">
-        <v>46279.23365740741</v>
+        <v>46282.24168981481</v>
       </c>
       <c r="M35" t="s">
         <v>263</v>
@@ -3408,16 +3402,16 @@
         <v>256</v>
       </c>
       <c r="O35" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P35" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q35" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R35" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W35" s="2">
         <v>46157</v>
@@ -3429,7 +3423,7 @@
         <v>263</v>
       </c>
       <c r="AA35" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="36" spans="1:27">
@@ -3467,7 +3461,7 @@
         <v>3591</v>
       </c>
       <c r="L36" s="2">
-        <v>46279.23365740741</v>
+        <v>46282.24168981481</v>
       </c>
       <c r="M36" t="s">
         <v>263</v>
@@ -3476,16 +3470,16 @@
         <v>256</v>
       </c>
       <c r="O36" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P36" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q36" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R36" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W36" s="2">
         <v>46168</v>
@@ -3497,7 +3491,7 @@
         <v>263</v>
       </c>
       <c r="AA36" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="37" spans="1:27">
@@ -3535,7 +3529,7 @@
         <v>1826</v>
       </c>
       <c r="L37" s="2">
-        <v>46279.23365740741</v>
+        <v>46282.24168981481</v>
       </c>
       <c r="M37" t="s">
         <v>263</v>
@@ -3544,16 +3538,16 @@
         <v>256</v>
       </c>
       <c r="O37" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P37" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q37" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R37" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W37" s="2">
         <v>46132</v>
@@ -3565,7 +3559,7 @@
         <v>263</v>
       </c>
       <c r="AA37" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="38" spans="1:27">
@@ -3603,7 +3597,7 @@
         <v>2937</v>
       </c>
       <c r="L38" s="2">
-        <v>46279.23365740741</v>
+        <v>46282.24168981481</v>
       </c>
       <c r="M38" t="s">
         <v>263</v>
@@ -3612,16 +3606,16 @@
         <v>256</v>
       </c>
       <c r="O38" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P38" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q38" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R38" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W38" s="2">
         <v>46113</v>
@@ -3633,7 +3627,7 @@
         <v>263</v>
       </c>
       <c r="AA38" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="39" spans="1:27">
@@ -3671,7 +3665,7 @@
         <v>3176</v>
       </c>
       <c r="L39" s="2">
-        <v>46279.23365740741</v>
+        <v>46282.24168981481</v>
       </c>
       <c r="M39" t="s">
         <v>263</v>
@@ -3680,16 +3674,16 @@
         <v>256</v>
       </c>
       <c r="O39" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P39" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q39" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R39" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W39" s="2">
         <v>46140</v>
@@ -3701,7 +3695,7 @@
         <v>263</v>
       </c>
       <c r="AA39" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="40" spans="1:27">
@@ -3739,7 +3733,7 @@
         <v>3128</v>
       </c>
       <c r="L40" s="2">
-        <v>46279.23365740741</v>
+        <v>46282.24168981481</v>
       </c>
       <c r="M40" t="s">
         <v>263</v>
@@ -3748,16 +3742,16 @@
         <v>256</v>
       </c>
       <c r="O40" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P40" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q40" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R40" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W40" s="2">
         <v>46024</v>
@@ -3769,7 +3763,7 @@
         <v>263</v>
       </c>
       <c r="AA40" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="41" spans="1:27">
@@ -3807,7 +3801,7 @@
         <v>3542</v>
       </c>
       <c r="L41" s="2">
-        <v>46279.23365740741</v>
+        <v>46282.24168981481</v>
       </c>
       <c r="M41" t="s">
         <v>263</v>
@@ -3816,16 +3810,16 @@
         <v>256</v>
       </c>
       <c r="O41" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P41" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q41" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R41" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W41" s="2">
         <v>46168</v>
@@ -3837,7 +3831,7 @@
         <v>263</v>
       </c>
       <c r="AA41" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="42" spans="1:27">
@@ -3875,7 +3869,7 @@
         <v>3533</v>
       </c>
       <c r="L42" s="2">
-        <v>46279.23365740741</v>
+        <v>46282.24168981481</v>
       </c>
       <c r="M42" t="s">
         <v>263</v>
@@ -3884,16 +3878,16 @@
         <v>256</v>
       </c>
       <c r="O42" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P42" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q42" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R42" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W42" s="2">
         <v>46164</v>
@@ -3905,7 +3899,7 @@
         <v>263</v>
       </c>
       <c r="AA42" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="43" spans="1:27">
@@ -3943,7 +3937,7 @@
         <v>3513</v>
       </c>
       <c r="L43" s="2">
-        <v>46279.23365740741</v>
+        <v>46282.24168981481</v>
       </c>
       <c r="M43" t="s">
         <v>263</v>
@@ -3952,16 +3946,16 @@
         <v>256</v>
       </c>
       <c r="O43" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P43" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q43" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R43" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W43" s="2">
         <v>46112</v>
@@ -3973,7 +3967,7 @@
         <v>263</v>
       </c>
       <c r="AA43" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="44" spans="1:27">
@@ -4020,16 +4014,16 @@
         <v>257</v>
       </c>
       <c r="O44" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P44" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q44" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R44" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W44" s="2">
         <v>46171</v>
@@ -4064,34 +4058,34 @@
         <v>1</v>
       </c>
       <c r="J45">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K45">
-        <v>3569</v>
+        <v>3623</v>
       </c>
       <c r="L45" s="2">
-        <v>46279.23365740741</v>
+        <v>46282.24168981481</v>
       </c>
       <c r="M45" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="N45" t="s">
         <v>256</v>
       </c>
       <c r="O45" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P45" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q45" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R45" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W45" s="2">
-        <v>46276</v>
+        <v>46281</v>
       </c>
       <c r="Y45" t="s">
         <v>261</v>
@@ -4100,7 +4094,7 @@
         <v>263</v>
       </c>
       <c r="AA45" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="46" spans="1:27">
@@ -4132,13 +4126,13 @@
         <v>1</v>
       </c>
       <c r="J46">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="K46">
-        <v>8741</v>
+        <v>9074</v>
       </c>
       <c r="L46" s="2">
-        <v>46279.23365740741</v>
+        <v>46282.24168981481</v>
       </c>
       <c r="M46" t="s">
         <v>261</v>
@@ -4147,19 +4141,19 @@
         <v>256</v>
       </c>
       <c r="O46" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P46" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q46" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R46" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W46" s="2">
-        <v>46276</v>
+        <v>46281</v>
       </c>
       <c r="Y46" t="s">
         <v>261</v>
@@ -4168,7 +4162,7 @@
         <v>263</v>
       </c>
       <c r="AA46" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="47" spans="1:27">
@@ -4200,13 +4194,13 @@
         <v>1</v>
       </c>
       <c r="J47">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K47">
-        <v>4323</v>
+        <v>4501</v>
       </c>
       <c r="L47" s="2">
-        <v>46279.23365740741</v>
+        <v>46282.24168981481</v>
       </c>
       <c r="M47" t="s">
         <v>261</v>
@@ -4215,19 +4209,19 @@
         <v>256</v>
       </c>
       <c r="O47" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P47" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q47" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R47" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W47" s="2">
-        <v>46276</v>
+        <v>46281</v>
       </c>
       <c r="Y47" t="s">
         <v>261</v>
@@ -4236,7 +4230,7 @@
         <v>263</v>
       </c>
       <c r="AA47" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="48" spans="1:27">
@@ -4274,7 +4268,7 @@
         <v>2299</v>
       </c>
       <c r="L48" s="2">
-        <v>46279.23365740741</v>
+        <v>46282.24168981481</v>
       </c>
       <c r="M48" t="s">
         <v>263</v>
@@ -4283,16 +4277,16 @@
         <v>256</v>
       </c>
       <c r="O48" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P48" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q48" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R48" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W48" s="2">
         <v>46168</v>
@@ -4304,7 +4298,7 @@
         <v>263</v>
       </c>
       <c r="AA48" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="49" spans="1:27">
@@ -4342,7 +4336,7 @@
         <v>1505</v>
       </c>
       <c r="L49" s="2">
-        <v>46279.23365740741</v>
+        <v>46282.24168981481</v>
       </c>
       <c r="M49" t="s">
         <v>263</v>
@@ -4351,16 +4345,16 @@
         <v>256</v>
       </c>
       <c r="O49" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P49" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q49" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R49" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W49" s="2">
         <v>46273</v>
@@ -4372,7 +4366,7 @@
         <v>263</v>
       </c>
       <c r="AA49" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="50" spans="1:27">
@@ -4404,34 +4398,34 @@
         <v>1</v>
       </c>
       <c r="J50">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K50">
-        <v>1691</v>
+        <v>1747</v>
       </c>
       <c r="L50" s="2">
-        <v>46279.23365740741</v>
+        <v>46282.24168981481</v>
       </c>
       <c r="M50" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="N50" t="s">
         <v>256</v>
       </c>
       <c r="O50" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P50" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q50" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R50" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W50" s="2">
-        <v>46276</v>
+        <v>46280</v>
       </c>
       <c r="Y50" t="s">
         <v>261</v>
@@ -4440,7 +4434,7 @@
         <v>263</v>
       </c>
       <c r="AA50" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="51" spans="1:27">
@@ -4472,34 +4466,34 @@
         <v>1</v>
       </c>
       <c r="J51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K51">
-        <v>1496</v>
+        <v>1504</v>
       </c>
       <c r="L51" s="2">
-        <v>46279.23365740741</v>
+        <v>46282.24168981481</v>
       </c>
       <c r="M51" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="N51" t="s">
         <v>256</v>
       </c>
       <c r="O51" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P51" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q51" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R51" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W51" s="2">
-        <v>46273</v>
+        <v>46279</v>
       </c>
       <c r="Y51" t="s">
         <v>261</v>
@@ -4508,7 +4502,7 @@
         <v>263</v>
       </c>
       <c r="AA51" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="52" spans="1:27">
@@ -4546,7 +4540,7 @@
         <v>1466</v>
       </c>
       <c r="L52" s="2">
-        <v>46279.23365740741</v>
+        <v>46282.24168981481</v>
       </c>
       <c r="M52" t="s">
         <v>263</v>
@@ -4555,16 +4549,16 @@
         <v>256</v>
       </c>
       <c r="O52" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P52" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q52" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R52" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W52" s="2">
         <v>46142</v>
@@ -4576,7 +4570,7 @@
         <v>263</v>
       </c>
       <c r="AA52" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="53" spans="1:27">
@@ -4608,13 +4602,13 @@
         <v>1</v>
       </c>
       <c r="J53">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K53">
-        <v>2139</v>
+        <v>2168</v>
       </c>
       <c r="L53" s="2">
-        <v>46279.23365740741</v>
+        <v>46282.24168981481</v>
       </c>
       <c r="M53" t="s">
         <v>261</v>
@@ -4623,19 +4617,19 @@
         <v>256</v>
       </c>
       <c r="O53" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P53" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q53" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R53" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W53" s="2">
-        <v>46276</v>
+        <v>46281</v>
       </c>
       <c r="Y53" t="s">
         <v>261</v>
@@ -4644,7 +4638,7 @@
         <v>263</v>
       </c>
       <c r="AA53" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="54" spans="1:27">
@@ -4676,34 +4670,34 @@
         <v>1</v>
       </c>
       <c r="J54">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K54">
-        <v>1356</v>
+        <v>1373</v>
       </c>
       <c r="L54" s="2">
-        <v>46279.23365740741</v>
+        <v>46282.24168981481</v>
       </c>
       <c r="M54" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="N54" t="s">
         <v>256</v>
       </c>
       <c r="O54" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P54" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q54" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R54" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W54" s="2">
-        <v>46275</v>
+        <v>46281</v>
       </c>
       <c r="Y54" t="s">
         <v>261</v>
@@ -4712,7 +4706,7 @@
         <v>263</v>
       </c>
       <c r="AA54" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="55" spans="1:27">
@@ -4744,43 +4738,43 @@
         <v>1</v>
       </c>
       <c r="J55">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K55">
-        <v>2258</v>
+        <v>2348</v>
       </c>
       <c r="L55" s="2">
-        <v>46279.23365740741</v>
+        <v>46282.24168981481</v>
       </c>
       <c r="M55" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="N55" t="s">
         <v>256</v>
       </c>
       <c r="O55" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P55" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q55" t="s">
+        <v>270</v>
+      </c>
+      <c r="R55" t="s">
+        <v>268</v>
+      </c>
+      <c r="W55" s="2">
+        <v>46281</v>
+      </c>
+      <c r="Y55" t="s">
+        <v>261</v>
+      </c>
+      <c r="Z55" t="s">
         <v>271</v>
       </c>
-      <c r="R55" t="s">
-        <v>269</v>
-      </c>
-      <c r="W55" s="2">
-        <v>46276</v>
-      </c>
-      <c r="Y55" t="s">
-        <v>261</v>
-      </c>
-      <c r="Z55" t="s">
+      <c r="AA55" t="s">
         <v>272</v>
-      </c>
-      <c r="AA55" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="56" spans="1:27">
@@ -4827,16 +4821,16 @@
         <v>257</v>
       </c>
       <c r="O56" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P56" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q56" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R56" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W56" s="2">
         <v>46161</v>
@@ -4871,34 +4865,34 @@
         <v>1</v>
       </c>
       <c r="J57">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K57">
-        <v>3950</v>
+        <v>3978</v>
       </c>
       <c r="L57" s="2">
-        <v>46279.23365740741</v>
+        <v>46282.24168981481</v>
       </c>
       <c r="M57" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="N57" t="s">
         <v>256</v>
       </c>
       <c r="O57" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P57" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q57" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R57" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W57" s="2">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="Y57" t="s">
         <v>261</v>
@@ -4907,7 +4901,7 @@
         <v>263</v>
       </c>
       <c r="AA57" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="58" spans="1:27">
@@ -4954,16 +4948,16 @@
         <v>257</v>
       </c>
       <c r="O58" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P58" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q58" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R58" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W58" s="2">
         <v>46148</v>
@@ -5013,16 +5007,16 @@
         <v>257</v>
       </c>
       <c r="O59" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P59" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q59" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R59" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W59" s="2">
         <v>46168</v>
@@ -5072,16 +5066,16 @@
         <v>257</v>
       </c>
       <c r="O60" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P60" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q60" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R60" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W60" s="2">
         <v>46164</v>
@@ -5131,16 +5125,16 @@
         <v>257</v>
       </c>
       <c r="O61" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P61" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q61" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R61" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W61" s="2">
         <v>46168</v>
@@ -5175,34 +5169,34 @@
         <v>1</v>
       </c>
       <c r="J62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K62">
-        <v>1663</v>
+        <v>1669</v>
       </c>
       <c r="L62" s="2">
-        <v>46279.23365740741</v>
+        <v>46282.24168981481</v>
       </c>
       <c r="M62" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="N62" t="s">
         <v>256</v>
       </c>
       <c r="O62" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P62" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q62" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R62" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W62" s="2">
-        <v>46273</v>
+        <v>46280</v>
       </c>
       <c r="Y62" t="s">
         <v>261</v>
@@ -5211,7 +5205,7 @@
         <v>263</v>
       </c>
       <c r="AA62" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="63" spans="1:27">
@@ -5258,16 +5252,16 @@
         <v>257</v>
       </c>
       <c r="O63" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P63" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q63" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R63" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W63" s="2">
         <v>46164</v>
@@ -5317,16 +5311,16 @@
         <v>257</v>
       </c>
       <c r="O64" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P64" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q64" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R64" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W64" s="2">
         <v>46168</v>
@@ -5361,13 +5355,13 @@
         <v>1</v>
       </c>
       <c r="J65">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="K65">
-        <v>4421</v>
+        <v>4525</v>
       </c>
       <c r="L65" s="2">
-        <v>46279.23365740741</v>
+        <v>46282.24168981481</v>
       </c>
       <c r="M65" t="s">
         <v>261</v>
@@ -5376,28 +5370,28 @@
         <v>256</v>
       </c>
       <c r="O65" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P65" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q65" t="s">
+        <v>270</v>
+      </c>
+      <c r="R65" t="s">
+        <v>268</v>
+      </c>
+      <c r="W65" s="2">
+        <v>46281</v>
+      </c>
+      <c r="Y65" t="s">
+        <v>261</v>
+      </c>
+      <c r="Z65" t="s">
         <v>271</v>
       </c>
-      <c r="R65" t="s">
-        <v>269</v>
-      </c>
-      <c r="W65" s="2">
-        <v>46279</v>
-      </c>
-      <c r="Y65" t="s">
-        <v>261</v>
-      </c>
-      <c r="Z65" t="s">
+      <c r="AA65" t="s">
         <v>272</v>
-      </c>
-      <c r="AA65" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="66" spans="1:27">
@@ -5435,7 +5429,7 @@
         <v>3062</v>
       </c>
       <c r="L66" s="2">
-        <v>46279.23365740741</v>
+        <v>46282.24168981481</v>
       </c>
       <c r="M66" t="s">
         <v>263</v>
@@ -5444,16 +5438,16 @@
         <v>256</v>
       </c>
       <c r="O66" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P66" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q66" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R66" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W66" s="2">
         <v>46261</v>
@@ -5465,7 +5459,7 @@
         <v>263</v>
       </c>
       <c r="AA66" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="67" spans="1:27">
@@ -5497,43 +5491,43 @@
         <v>1</v>
       </c>
       <c r="J67">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K67">
-        <v>1727</v>
+        <v>1751</v>
       </c>
       <c r="L67" s="2">
-        <v>46279.23365740741</v>
+        <v>46282.24168981481</v>
       </c>
       <c r="M67" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="N67" t="s">
         <v>256</v>
       </c>
       <c r="O67" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P67" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q67" t="s">
+        <v>270</v>
+      </c>
+      <c r="R67" t="s">
+        <v>268</v>
+      </c>
+      <c r="W67" s="2">
+        <v>46280</v>
+      </c>
+      <c r="Y67" t="s">
+        <v>261</v>
+      </c>
+      <c r="Z67" t="s">
         <v>271</v>
       </c>
-      <c r="R67" t="s">
-        <v>269</v>
-      </c>
-      <c r="W67" s="2">
-        <v>46275</v>
-      </c>
-      <c r="Y67" t="s">
-        <v>261</v>
-      </c>
-      <c r="Z67" t="s">
+      <c r="AA67" t="s">
         <v>272</v>
-      </c>
-      <c r="AA67" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="68" spans="1:27">
@@ -5565,13 +5559,13 @@
         <v>1</v>
       </c>
       <c r="J68">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="K68">
-        <v>4115</v>
+        <v>4205</v>
       </c>
       <c r="L68" s="2">
-        <v>46279.23365740741</v>
+        <v>46282.24168981481</v>
       </c>
       <c r="M68" t="s">
         <v>261</v>
@@ -5580,28 +5574,28 @@
         <v>256</v>
       </c>
       <c r="O68" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P68" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q68" t="s">
+        <v>270</v>
+      </c>
+      <c r="R68" t="s">
+        <v>268</v>
+      </c>
+      <c r="W68" s="2">
+        <v>46280</v>
+      </c>
+      <c r="Y68" t="s">
+        <v>261</v>
+      </c>
+      <c r="Z68" t="s">
         <v>271</v>
       </c>
-      <c r="R68" t="s">
-        <v>269</v>
-      </c>
-      <c r="W68" s="2">
-        <v>46276</v>
-      </c>
-      <c r="Y68" t="s">
-        <v>261</v>
-      </c>
-      <c r="Z68" t="s">
+      <c r="AA68" t="s">
         <v>272</v>
-      </c>
-      <c r="AA68" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="69" spans="1:27">
@@ -5636,10 +5630,10 @@
         <v>0</v>
       </c>
       <c r="K69">
-        <v>3058</v>
+        <v>3069</v>
       </c>
       <c r="L69" s="2">
-        <v>46279.23365740741</v>
+        <v>46282.24168981481</v>
       </c>
       <c r="M69" t="s">
         <v>263</v>
@@ -5648,19 +5642,19 @@
         <v>256</v>
       </c>
       <c r="O69" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P69" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q69" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R69" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W69" s="2">
-        <v>46259</v>
+        <v>46280</v>
       </c>
       <c r="Y69" t="s">
         <v>261</v>
@@ -5669,7 +5663,7 @@
         <v>263</v>
       </c>
       <c r="AA69" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="70" spans="1:27">
@@ -5701,43 +5695,43 @@
         <v>1</v>
       </c>
       <c r="J70">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="K70">
-        <v>2476</v>
+        <v>2590</v>
       </c>
       <c r="L70" s="2">
-        <v>46279.23365740741</v>
+        <v>46282.24168981481</v>
       </c>
       <c r="M70" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="N70" t="s">
         <v>256</v>
       </c>
       <c r="O70" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P70" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q70" t="s">
+        <v>270</v>
+      </c>
+      <c r="R70" t="s">
+        <v>268</v>
+      </c>
+      <c r="W70" s="2">
+        <v>46280</v>
+      </c>
+      <c r="Y70" t="s">
+        <v>261</v>
+      </c>
+      <c r="Z70" t="s">
         <v>271</v>
       </c>
-      <c r="R70" t="s">
-        <v>269</v>
-      </c>
-      <c r="W70" s="2">
-        <v>46276</v>
-      </c>
-      <c r="Y70" t="s">
-        <v>261</v>
-      </c>
-      <c r="Z70" t="s">
+      <c r="AA70" t="s">
         <v>272</v>
-      </c>
-      <c r="AA70" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="71" spans="1:27">
@@ -5769,13 +5763,13 @@
         <v>1</v>
       </c>
       <c r="J71">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K71">
-        <v>2529</v>
+        <v>2631</v>
       </c>
       <c r="L71" s="2">
-        <v>46279.23365740741</v>
+        <v>46282.24168981481</v>
       </c>
       <c r="M71" t="s">
         <v>261</v>
@@ -5784,28 +5778,28 @@
         <v>256</v>
       </c>
       <c r="O71" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P71" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q71" t="s">
+        <v>270</v>
+      </c>
+      <c r="R71" t="s">
+        <v>268</v>
+      </c>
+      <c r="W71" s="2">
+        <v>46280</v>
+      </c>
+      <c r="Y71" t="s">
+        <v>261</v>
+      </c>
+      <c r="Z71" t="s">
         <v>271</v>
       </c>
-      <c r="R71" t="s">
-        <v>269</v>
-      </c>
-      <c r="W71" s="2">
-        <v>46276</v>
-      </c>
-      <c r="Y71" t="s">
-        <v>261</v>
-      </c>
-      <c r="Z71" t="s">
+      <c r="AA71" t="s">
         <v>272</v>
-      </c>
-      <c r="AA71" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="72" spans="1:27">
@@ -5852,16 +5846,16 @@
         <v>257</v>
       </c>
       <c r="O72" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P72" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q72" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R72" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W72" s="2">
         <v>46164</v>
@@ -5896,31 +5890,31 @@
         <v>1</v>
       </c>
       <c r="J73">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K73">
-        <v>1350</v>
+        <v>1371</v>
       </c>
       <c r="L73" s="2">
-        <v>46279.23365740741</v>
+        <v>46282.24168981481</v>
       </c>
       <c r="M73" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N73" t="s">
         <v>256</v>
       </c>
       <c r="O73" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P73" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q73" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R73" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W73" s="2">
         <v>46279</v>
@@ -5932,7 +5926,7 @@
         <v>263</v>
       </c>
       <c r="AA73" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="74" spans="1:27">
@@ -5970,7 +5964,7 @@
         <v>1449</v>
       </c>
       <c r="L74" s="2">
-        <v>46279.23365740741</v>
+        <v>46282.24168981481</v>
       </c>
       <c r="M74" t="s">
         <v>263</v>
@@ -5979,16 +5973,16 @@
         <v>256</v>
       </c>
       <c r="O74" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P74" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q74" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R74" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W74" s="2">
         <v>46185</v>
@@ -6000,7 +5994,7 @@
         <v>263</v>
       </c>
       <c r="AA74" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="75" spans="1:27">
@@ -6038,7 +6032,7 @@
         <v>1482</v>
       </c>
       <c r="L75" s="2">
-        <v>46279.23365740741</v>
+        <v>46282.24168981481</v>
       </c>
       <c r="M75" t="s">
         <v>263</v>
@@ -6047,16 +6041,16 @@
         <v>256</v>
       </c>
       <c r="O75" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P75" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q75" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R75" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W75" s="2">
         <v>46265</v>
@@ -6068,7 +6062,7 @@
         <v>263</v>
       </c>
       <c r="AA75" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="76" spans="1:27">
@@ -6100,34 +6094,34 @@
         <v>1</v>
       </c>
       <c r="J76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K76">
-        <v>1527</v>
+        <v>1536</v>
       </c>
       <c r="L76" s="2">
-        <v>46279.23365740741</v>
+        <v>46282.24168981481</v>
       </c>
       <c r="M76" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="N76" t="s">
         <v>256</v>
       </c>
       <c r="O76" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P76" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q76" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R76" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W76" s="2">
-        <v>46262</v>
+        <v>46279</v>
       </c>
       <c r="Y76" t="s">
         <v>261</v>
@@ -6136,7 +6130,7 @@
         <v>263</v>
       </c>
       <c r="AA76" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="77" spans="1:27">
@@ -6168,34 +6162,34 @@
         <v>1</v>
       </c>
       <c r="J77">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K77">
-        <v>1551</v>
+        <v>1555</v>
       </c>
       <c r="L77" s="2">
-        <v>46279.23365740741</v>
+        <v>46282.24168981481</v>
       </c>
       <c r="M77" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="N77" t="s">
         <v>256</v>
       </c>
       <c r="O77" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P77" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q77" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R77" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W77" s="2">
-        <v>46272</v>
+        <v>46281</v>
       </c>
       <c r="Y77" t="s">
         <v>261</v>
@@ -6204,7 +6198,7 @@
         <v>263</v>
       </c>
       <c r="AA77" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="78" spans="1:27">
@@ -6236,31 +6230,31 @@
         <v>1</v>
       </c>
       <c r="J78">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K78">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="L78" s="2">
-        <v>46279.23365740741</v>
+        <v>46282.24168981481</v>
       </c>
       <c r="M78" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N78" t="s">
         <v>256</v>
       </c>
       <c r="O78" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P78" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q78" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R78" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W78" s="2">
         <v>46276</v>
@@ -6272,7 +6266,7 @@
         <v>263</v>
       </c>
       <c r="AA78" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="79" spans="1:27">
@@ -6304,13 +6298,13 @@
         <v>1</v>
       </c>
       <c r="J79">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K79">
-        <v>1729</v>
+        <v>1768</v>
       </c>
       <c r="L79" s="2">
-        <v>46279.23365740741</v>
+        <v>46282.24168981481</v>
       </c>
       <c r="M79" t="s">
         <v>261</v>
@@ -6319,19 +6313,19 @@
         <v>256</v>
       </c>
       <c r="O79" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P79" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q79" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R79" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W79" s="2">
-        <v>46276</v>
+        <v>46282</v>
       </c>
       <c r="Y79" t="s">
         <v>261</v>
@@ -6340,7 +6334,7 @@
         <v>263</v>
       </c>
       <c r="AA79" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="80" spans="1:27">
@@ -6372,34 +6366,34 @@
         <v>1</v>
       </c>
       <c r="J80">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K80">
-        <v>1572</v>
+        <v>1574</v>
       </c>
       <c r="L80" s="2">
-        <v>46279.23365740741</v>
+        <v>46282.24168981481</v>
       </c>
       <c r="M80" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="N80" t="s">
         <v>256</v>
       </c>
       <c r="O80" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P80" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q80" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R80" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W80" s="2">
-        <v>46275</v>
+        <v>46280</v>
       </c>
       <c r="Y80" t="s">
         <v>261</v>
@@ -6408,7 +6402,7 @@
         <v>263</v>
       </c>
       <c r="AA80" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="81" spans="1:27">
@@ -6446,7 +6440,7 @@
         <v>3591</v>
       </c>
       <c r="L81" s="2">
-        <v>46279.23365740741</v>
+        <v>46282.24168981481</v>
       </c>
       <c r="M81" t="s">
         <v>263</v>
@@ -6455,16 +6449,16 @@
         <v>256</v>
       </c>
       <c r="O81" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P81" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q81" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R81" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W81" s="2">
         <v>46160</v>
@@ -6476,7 +6470,7 @@
         <v>263</v>
       </c>
       <c r="AA81" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="82" spans="1:27">
@@ -6523,16 +6517,16 @@
         <v>257</v>
       </c>
       <c r="O82" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P82" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q82" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R82" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W82" s="2">
         <v>46161</v>
@@ -6582,16 +6576,16 @@
         <v>257</v>
       </c>
       <c r="O83" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P83" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q83" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R83" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W83" s="2">
         <v>46168</v>
@@ -6641,16 +6635,16 @@
         <v>257</v>
       </c>
       <c r="O84" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P84" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q84" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R84" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W84" s="2">
         <v>46164</v>
@@ -6700,16 +6694,16 @@
         <v>257</v>
       </c>
       <c r="O85" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P85" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q85" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R85" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W85" s="2">
         <v>46168</v>
@@ -6750,7 +6744,7 @@
         <v>652</v>
       </c>
       <c r="L86" s="2">
-        <v>46279.23365740741</v>
+        <v>46282.24168981481</v>
       </c>
       <c r="M86" t="s">
         <v>263</v>
@@ -6759,16 +6753,16 @@
         <v>256</v>
       </c>
       <c r="O86" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P86" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q86" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R86" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W86" s="2">
         <v>46164</v>
@@ -6780,7 +6774,7 @@
         <v>263</v>
       </c>
       <c r="AA86" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="87" spans="1:27">
@@ -6818,7 +6812,7 @@
         <v>3609</v>
       </c>
       <c r="L87" s="2">
-        <v>46279.23365740741</v>
+        <v>46282.24168981481</v>
       </c>
       <c r="M87" t="s">
         <v>263</v>
@@ -6827,16 +6821,16 @@
         <v>256</v>
       </c>
       <c r="O87" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P87" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q87" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R87" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W87" s="2">
         <v>46248</v>
@@ -6848,7 +6842,7 @@
         <v>263</v>
       </c>
       <c r="AA87" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="88" spans="1:27">
@@ -6886,7 +6880,7 @@
         <v>3580</v>
       </c>
       <c r="L88" s="2">
-        <v>46279.23365740741</v>
+        <v>46282.24168981481</v>
       </c>
       <c r="M88" t="s">
         <v>263</v>
@@ -6895,16 +6889,16 @@
         <v>256</v>
       </c>
       <c r="O88" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P88" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q88" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R88" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W88" s="2">
         <v>46253.16666666666</v>
@@ -6916,7 +6910,7 @@
         <v>263</v>
       </c>
       <c r="AA88" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="89" spans="1:27">
@@ -6948,16 +6942,16 @@
         <v>257</v>
       </c>
       <c r="O89" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P89" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q89" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R89" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="90" spans="1:27">
@@ -6995,25 +6989,25 @@
         <v>125</v>
       </c>
       <c r="L90" s="2">
-        <v>46279.23365740741</v>
+        <v>46282.24168981481</v>
       </c>
       <c r="M90" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="N90" t="s">
         <v>256</v>
       </c>
       <c r="O90" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P90" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q90" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R90" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W90" s="2">
         <v>46154</v>
@@ -7054,16 +7048,16 @@
         <v>256</v>
       </c>
       <c r="O91" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P91" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q91" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R91" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W91" s="2">
         <v>46154</v>
@@ -7113,16 +7107,16 @@
         <v>257</v>
       </c>
       <c r="O92" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P92" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q92" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R92" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W92" s="2">
         <v>46164</v>

--- a/sites.xlsx
+++ b/sites.xlsx
@@ -1550,7 +1550,7 @@
         <v>169</v>
       </c>
       <c r="L6" s="2">
-        <v>46282.24168981481</v>
+        <v>46282.27054398148</v>
       </c>
       <c r="M6" t="s">
         <v>263</v>
@@ -1993,7 +1993,7 @@
         <v>170</v>
       </c>
       <c r="L13" s="2">
-        <v>46282.24168981481</v>
+        <v>46282.27054398148</v>
       </c>
       <c r="M13" t="s">
         <v>263</v>
@@ -2061,10 +2061,10 @@
         <v>1</v>
       </c>
       <c r="K14">
-        <v>3540</v>
+        <v>3541</v>
       </c>
       <c r="L14" s="2">
-        <v>46282.24168981481</v>
+        <v>46282.27054398148</v>
       </c>
       <c r="M14" t="s">
         <v>262</v>
@@ -2129,10 +2129,10 @@
         <v>1</v>
       </c>
       <c r="K15">
-        <v>3531</v>
+        <v>3532</v>
       </c>
       <c r="L15" s="2">
-        <v>46282.24168981481</v>
+        <v>46282.27054398148</v>
       </c>
       <c r="M15" t="s">
         <v>262</v>
@@ -2197,10 +2197,10 @@
         <v>2</v>
       </c>
       <c r="K16">
-        <v>3586</v>
+        <v>3588</v>
       </c>
       <c r="L16" s="2">
-        <v>46282.24168981481</v>
+        <v>46282.27054398148</v>
       </c>
       <c r="M16" t="s">
         <v>262</v>
@@ -2327,7 +2327,7 @@
         <v>3630</v>
       </c>
       <c r="L18" s="2">
-        <v>46282.24168981481</v>
+        <v>46282.27054398148</v>
       </c>
       <c r="M18" t="s">
         <v>263</v>
@@ -2572,7 +2572,7 @@
         <v>3591</v>
       </c>
       <c r="L22" s="2">
-        <v>46282.24168981481</v>
+        <v>46282.27054398148</v>
       </c>
       <c r="M22" t="s">
         <v>263</v>
@@ -2640,7 +2640,7 @@
         <v>3591</v>
       </c>
       <c r="L23" s="2">
-        <v>46282.24168981481</v>
+        <v>46282.27054398148</v>
       </c>
       <c r="M23" t="s">
         <v>263</v>
@@ -2708,7 +2708,7 @@
         <v>131</v>
       </c>
       <c r="L24" s="2">
-        <v>46282.24168981481</v>
+        <v>46282.27054398148</v>
       </c>
       <c r="M24" t="s">
         <v>263</v>
@@ -2776,7 +2776,7 @@
         <v>145</v>
       </c>
       <c r="L25" s="2">
-        <v>46282.24168981481</v>
+        <v>46282.27054398148</v>
       </c>
       <c r="M25" t="s">
         <v>263</v>
@@ -2844,7 +2844,7 @@
         <v>150</v>
       </c>
       <c r="L26" s="2">
-        <v>46282.24168981481</v>
+        <v>46282.27054398148</v>
       </c>
       <c r="M26" t="s">
         <v>263</v>
@@ -3204,10 +3204,10 @@
         <v>85</v>
       </c>
       <c r="K32">
-        <v>13811</v>
+        <v>13896</v>
       </c>
       <c r="L32" s="2">
-        <v>46282.24168981481</v>
+        <v>46282.27054398148</v>
       </c>
       <c r="M32" t="s">
         <v>261</v>
@@ -3393,7 +3393,7 @@
         <v>3591</v>
       </c>
       <c r="L35" s="2">
-        <v>46282.24168981481</v>
+        <v>46282.27054398148</v>
       </c>
       <c r="M35" t="s">
         <v>263</v>
@@ -3461,7 +3461,7 @@
         <v>3591</v>
       </c>
       <c r="L36" s="2">
-        <v>46282.24168981481</v>
+        <v>46282.27054398148</v>
       </c>
       <c r="M36" t="s">
         <v>263</v>
@@ -3529,7 +3529,7 @@
         <v>1826</v>
       </c>
       <c r="L37" s="2">
-        <v>46282.24168981481</v>
+        <v>46282.27054398148</v>
       </c>
       <c r="M37" t="s">
         <v>263</v>
@@ -3597,7 +3597,7 @@
         <v>2937</v>
       </c>
       <c r="L38" s="2">
-        <v>46282.24168981481</v>
+        <v>46282.27054398148</v>
       </c>
       <c r="M38" t="s">
         <v>263</v>
@@ -3665,7 +3665,7 @@
         <v>3176</v>
       </c>
       <c r="L39" s="2">
-        <v>46282.24168981481</v>
+        <v>46282.27054398148</v>
       </c>
       <c r="M39" t="s">
         <v>263</v>
@@ -3733,7 +3733,7 @@
         <v>3128</v>
       </c>
       <c r="L40" s="2">
-        <v>46282.24168981481</v>
+        <v>46282.27054398148</v>
       </c>
       <c r="M40" t="s">
         <v>263</v>
@@ -3801,7 +3801,7 @@
         <v>3542</v>
       </c>
       <c r="L41" s="2">
-        <v>46282.24168981481</v>
+        <v>46282.27054398148</v>
       </c>
       <c r="M41" t="s">
         <v>263</v>
@@ -3869,7 +3869,7 @@
         <v>3533</v>
       </c>
       <c r="L42" s="2">
-        <v>46282.24168981481</v>
+        <v>46282.27054398148</v>
       </c>
       <c r="M42" t="s">
         <v>263</v>
@@ -3937,7 +3937,7 @@
         <v>3513</v>
       </c>
       <c r="L43" s="2">
-        <v>46282.24168981481</v>
+        <v>46282.27054398148</v>
       </c>
       <c r="M43" t="s">
         <v>263</v>
@@ -4061,10 +4061,10 @@
         <v>12</v>
       </c>
       <c r="K45">
-        <v>3623</v>
+        <v>3635</v>
       </c>
       <c r="L45" s="2">
-        <v>46282.24168981481</v>
+        <v>46282.27054398148</v>
       </c>
       <c r="M45" t="s">
         <v>261</v>
@@ -4129,10 +4129,10 @@
         <v>51</v>
       </c>
       <c r="K46">
-        <v>9074</v>
+        <v>9125</v>
       </c>
       <c r="L46" s="2">
-        <v>46282.24168981481</v>
+        <v>46282.27054398148</v>
       </c>
       <c r="M46" t="s">
         <v>261</v>
@@ -4197,10 +4197,10 @@
         <v>19</v>
       </c>
       <c r="K47">
-        <v>4501</v>
+        <v>4520</v>
       </c>
       <c r="L47" s="2">
-        <v>46282.24168981481</v>
+        <v>46282.27054398148</v>
       </c>
       <c r="M47" t="s">
         <v>261</v>
@@ -4268,7 +4268,7 @@
         <v>2299</v>
       </c>
       <c r="L48" s="2">
-        <v>46282.24168981481</v>
+        <v>46282.27054398148</v>
       </c>
       <c r="M48" t="s">
         <v>263</v>
@@ -4336,7 +4336,7 @@
         <v>1505</v>
       </c>
       <c r="L49" s="2">
-        <v>46282.24168981481</v>
+        <v>46282.27054398148</v>
       </c>
       <c r="M49" t="s">
         <v>263</v>
@@ -4401,10 +4401,10 @@
         <v>9</v>
       </c>
       <c r="K50">
-        <v>1747</v>
+        <v>1756</v>
       </c>
       <c r="L50" s="2">
-        <v>46282.24168981481</v>
+        <v>46282.27054398148</v>
       </c>
       <c r="M50" t="s">
         <v>261</v>
@@ -4469,10 +4469,10 @@
         <v>1</v>
       </c>
       <c r="K51">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="L51" s="2">
-        <v>46282.24168981481</v>
+        <v>46282.27054398148</v>
       </c>
       <c r="M51" t="s">
         <v>262</v>
@@ -4540,7 +4540,7 @@
         <v>1466</v>
       </c>
       <c r="L52" s="2">
-        <v>46282.24168981481</v>
+        <v>46282.27054398148</v>
       </c>
       <c r="M52" t="s">
         <v>263</v>
@@ -4605,10 +4605,10 @@
         <v>3</v>
       </c>
       <c r="K53">
-        <v>2168</v>
+        <v>2171</v>
       </c>
       <c r="L53" s="2">
-        <v>46282.24168981481</v>
+        <v>46282.27054398148</v>
       </c>
       <c r="M53" t="s">
         <v>261</v>
@@ -4673,10 +4673,10 @@
         <v>3</v>
       </c>
       <c r="K54">
-        <v>1373</v>
+        <v>1376</v>
       </c>
       <c r="L54" s="2">
-        <v>46282.24168981481</v>
+        <v>46282.27054398148</v>
       </c>
       <c r="M54" t="s">
         <v>261</v>
@@ -4741,10 +4741,10 @@
         <v>10</v>
       </c>
       <c r="K55">
-        <v>2348</v>
+        <v>2358</v>
       </c>
       <c r="L55" s="2">
-        <v>46282.24168981481</v>
+        <v>46282.27054398148</v>
       </c>
       <c r="M55" t="s">
         <v>261</v>
@@ -4868,10 +4868,10 @@
         <v>3</v>
       </c>
       <c r="K57">
-        <v>3978</v>
+        <v>3981</v>
       </c>
       <c r="L57" s="2">
-        <v>46282.24168981481</v>
+        <v>46282.27054398148</v>
       </c>
       <c r="M57" t="s">
         <v>261</v>
@@ -5172,10 +5172,10 @@
         <v>1</v>
       </c>
       <c r="K62">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="L62" s="2">
-        <v>46282.24168981481</v>
+        <v>46282.27054398148</v>
       </c>
       <c r="M62" t="s">
         <v>262</v>
@@ -5358,10 +5358,10 @@
         <v>20</v>
       </c>
       <c r="K65">
-        <v>4525</v>
+        <v>4545</v>
       </c>
       <c r="L65" s="2">
-        <v>46282.24168981481</v>
+        <v>46282.27054398148</v>
       </c>
       <c r="M65" t="s">
         <v>261</v>
@@ -5429,7 +5429,7 @@
         <v>3062</v>
       </c>
       <c r="L66" s="2">
-        <v>46282.24168981481</v>
+        <v>46282.27054398148</v>
       </c>
       <c r="M66" t="s">
         <v>263</v>
@@ -5494,10 +5494,10 @@
         <v>3</v>
       </c>
       <c r="K67">
-        <v>1751</v>
+        <v>1754</v>
       </c>
       <c r="L67" s="2">
-        <v>46282.24168981481</v>
+        <v>46282.27054398148</v>
       </c>
       <c r="M67" t="s">
         <v>261</v>
@@ -5559,13 +5559,13 @@
         <v>1</v>
       </c>
       <c r="J68">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K68">
-        <v>4205</v>
+        <v>4214</v>
       </c>
       <c r="L68" s="2">
-        <v>46282.24168981481</v>
+        <v>46282.27054398148</v>
       </c>
       <c r="M68" t="s">
         <v>261</v>
@@ -5633,7 +5633,7 @@
         <v>3069</v>
       </c>
       <c r="L69" s="2">
-        <v>46282.24168981481</v>
+        <v>46282.27054398148</v>
       </c>
       <c r="M69" t="s">
         <v>263</v>
@@ -5698,10 +5698,10 @@
         <v>11</v>
       </c>
       <c r="K70">
-        <v>2590</v>
+        <v>2601</v>
       </c>
       <c r="L70" s="2">
-        <v>46282.24168981481</v>
+        <v>46282.27054398148</v>
       </c>
       <c r="M70" t="s">
         <v>261</v>
@@ -5766,10 +5766,10 @@
         <v>12</v>
       </c>
       <c r="K71">
-        <v>2631</v>
+        <v>2643</v>
       </c>
       <c r="L71" s="2">
-        <v>46282.24168981481</v>
+        <v>46282.27054398148</v>
       </c>
       <c r="M71" t="s">
         <v>261</v>
@@ -5893,10 +5893,10 @@
         <v>2</v>
       </c>
       <c r="K73">
-        <v>1371</v>
+        <v>1373</v>
       </c>
       <c r="L73" s="2">
-        <v>46282.24168981481</v>
+        <v>46282.27054398148</v>
       </c>
       <c r="M73" t="s">
         <v>262</v>
@@ -5964,7 +5964,7 @@
         <v>1449</v>
       </c>
       <c r="L74" s="2">
-        <v>46282.24168981481</v>
+        <v>46282.27054398148</v>
       </c>
       <c r="M74" t="s">
         <v>263</v>
@@ -6032,7 +6032,7 @@
         <v>1482</v>
       </c>
       <c r="L75" s="2">
-        <v>46282.24168981481</v>
+        <v>46282.27054398148</v>
       </c>
       <c r="M75" t="s">
         <v>263</v>
@@ -6097,10 +6097,10 @@
         <v>1</v>
       </c>
       <c r="K76">
-        <v>1536</v>
+        <v>1537</v>
       </c>
       <c r="L76" s="2">
-        <v>46282.24168981481</v>
+        <v>46282.27054398148</v>
       </c>
       <c r="M76" t="s">
         <v>262</v>
@@ -6165,10 +6165,10 @@
         <v>2</v>
       </c>
       <c r="K77">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="L77" s="2">
-        <v>46282.24168981481</v>
+        <v>46282.27054398148</v>
       </c>
       <c r="M77" t="s">
         <v>262</v>
@@ -6236,7 +6236,7 @@
         <v>1565</v>
       </c>
       <c r="L78" s="2">
-        <v>46282.24168981481</v>
+        <v>46282.27054398148</v>
       </c>
       <c r="M78" t="s">
         <v>263</v>
@@ -6301,10 +6301,10 @@
         <v>7</v>
       </c>
       <c r="K79">
-        <v>1768</v>
+        <v>1775</v>
       </c>
       <c r="L79" s="2">
-        <v>46282.24168981481</v>
+        <v>46282.27054398148</v>
       </c>
       <c r="M79" t="s">
         <v>261</v>
@@ -6369,10 +6369,10 @@
         <v>1</v>
       </c>
       <c r="K80">
-        <v>1574</v>
+        <v>1575</v>
       </c>
       <c r="L80" s="2">
-        <v>46282.24168981481</v>
+        <v>46282.27054398148</v>
       </c>
       <c r="M80" t="s">
         <v>262</v>
@@ -6440,7 +6440,7 @@
         <v>3591</v>
       </c>
       <c r="L81" s="2">
-        <v>46282.24168981481</v>
+        <v>46282.27054398148</v>
       </c>
       <c r="M81" t="s">
         <v>263</v>
@@ -6744,7 +6744,7 @@
         <v>652</v>
       </c>
       <c r="L86" s="2">
-        <v>46282.24168981481</v>
+        <v>46282.27054398148</v>
       </c>
       <c r="M86" t="s">
         <v>263</v>
@@ -6812,7 +6812,7 @@
         <v>3609</v>
       </c>
       <c r="L87" s="2">
-        <v>46282.24168981481</v>
+        <v>46282.27054398148</v>
       </c>
       <c r="M87" t="s">
         <v>263</v>
@@ -6880,7 +6880,7 @@
         <v>3580</v>
       </c>
       <c r="L88" s="2">
-        <v>46282.24168981481</v>
+        <v>46282.27054398148</v>
       </c>
       <c r="M88" t="s">
         <v>263</v>
@@ -6989,7 +6989,7 @@
         <v>125</v>
       </c>
       <c r="L90" s="2">
-        <v>46282.24168981481</v>
+        <v>46282.27054398148</v>
       </c>
       <c r="M90" t="s">
         <v>264</v>

--- a/sites.xlsx
+++ b/sites.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1369" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1369" uniqueCount="274">
   <si>
     <t>site_name</t>
   </si>
@@ -833,6 +833,9 @@
   </si>
   <si>
     <t>PRIMARY_PARSER</t>
+  </si>
+  <si>
+    <t>selenium:detail_date</t>
   </si>
 </sst>
 </file>
@@ -1550,7 +1553,7 @@
         <v>169</v>
       </c>
       <c r="L6" s="2">
-        <v>46282.27054398148</v>
+        <v>46283.18092592592</v>
       </c>
       <c r="M6" t="s">
         <v>263</v>
@@ -1993,7 +1996,7 @@
         <v>170</v>
       </c>
       <c r="L13" s="2">
-        <v>46282.27054398148</v>
+        <v>46283.18092592592</v>
       </c>
       <c r="M13" t="s">
         <v>263</v>
@@ -2061,10 +2064,10 @@
         <v>1</v>
       </c>
       <c r="K14">
-        <v>3541</v>
+        <v>3542</v>
       </c>
       <c r="L14" s="2">
-        <v>46282.27054398148</v>
+        <v>46283.18092592592</v>
       </c>
       <c r="M14" t="s">
         <v>262</v>
@@ -2129,10 +2132,10 @@
         <v>1</v>
       </c>
       <c r="K15">
-        <v>3532</v>
+        <v>3533</v>
       </c>
       <c r="L15" s="2">
-        <v>46282.27054398148</v>
+        <v>46283.18092592592</v>
       </c>
       <c r="M15" t="s">
         <v>262</v>
@@ -2197,10 +2200,10 @@
         <v>2</v>
       </c>
       <c r="K16">
-        <v>3588</v>
+        <v>3590</v>
       </c>
       <c r="L16" s="2">
-        <v>46282.27054398148</v>
+        <v>46283.18092592592</v>
       </c>
       <c r="M16" t="s">
         <v>262</v>
@@ -2327,7 +2330,7 @@
         <v>3630</v>
       </c>
       <c r="L18" s="2">
-        <v>46282.27054398148</v>
+        <v>46283.18092592592</v>
       </c>
       <c r="M18" t="s">
         <v>263</v>
@@ -2572,7 +2575,7 @@
         <v>3591</v>
       </c>
       <c r="L22" s="2">
-        <v>46282.27054398148</v>
+        <v>46283.18092592592</v>
       </c>
       <c r="M22" t="s">
         <v>263</v>
@@ -2640,7 +2643,7 @@
         <v>3591</v>
       </c>
       <c r="L23" s="2">
-        <v>46282.27054398148</v>
+        <v>46283.18092592592</v>
       </c>
       <c r="M23" t="s">
         <v>263</v>
@@ -2708,7 +2711,7 @@
         <v>131</v>
       </c>
       <c r="L24" s="2">
-        <v>46282.27054398148</v>
+        <v>46283.18092592592</v>
       </c>
       <c r="M24" t="s">
         <v>263</v>
@@ -2776,7 +2779,7 @@
         <v>145</v>
       </c>
       <c r="L25" s="2">
-        <v>46282.27054398148</v>
+        <v>46283.18092592592</v>
       </c>
       <c r="M25" t="s">
         <v>263</v>
@@ -2838,16 +2841,16 @@
         <v>1</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K26">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="L26" s="2">
-        <v>46282.27054398148</v>
+        <v>46283.18092592592</v>
       </c>
       <c r="M26" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="N26" t="s">
         <v>256</v>
@@ -2865,7 +2868,7 @@
         <v>268</v>
       </c>
       <c r="W26" s="2">
-        <v>46276</v>
+        <v>46282</v>
       </c>
       <c r="Y26" t="s">
         <v>261</v>
@@ -2874,7 +2877,7 @@
         <v>263</v>
       </c>
       <c r="AA26" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
     </row>
     <row r="27" spans="1:27">
@@ -3201,13 +3204,13 @@
         <v>1</v>
       </c>
       <c r="J32">
-        <v>85</v>
+        <v>147</v>
       </c>
       <c r="K32">
-        <v>13896</v>
+        <v>14043</v>
       </c>
       <c r="L32" s="2">
-        <v>46282.27054398148</v>
+        <v>46283.18092592592</v>
       </c>
       <c r="M32" t="s">
         <v>261</v>
@@ -3228,7 +3231,7 @@
         <v>268</v>
       </c>
       <c r="W32" s="2">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="Y32" t="s">
         <v>261</v>
@@ -3393,7 +3396,7 @@
         <v>3591</v>
       </c>
       <c r="L35" s="2">
-        <v>46282.27054398148</v>
+        <v>46283.18092592592</v>
       </c>
       <c r="M35" t="s">
         <v>263</v>
@@ -3461,7 +3464,7 @@
         <v>3591</v>
       </c>
       <c r="L36" s="2">
-        <v>46282.27054398148</v>
+        <v>46283.18092592592</v>
       </c>
       <c r="M36" t="s">
         <v>263</v>
@@ -3529,7 +3532,7 @@
         <v>1826</v>
       </c>
       <c r="L37" s="2">
-        <v>46282.27054398148</v>
+        <v>46283.18092592592</v>
       </c>
       <c r="M37" t="s">
         <v>263</v>
@@ -3597,7 +3600,7 @@
         <v>2937</v>
       </c>
       <c r="L38" s="2">
-        <v>46282.27054398148</v>
+        <v>46283.18092592592</v>
       </c>
       <c r="M38" t="s">
         <v>263</v>
@@ -3665,7 +3668,7 @@
         <v>3176</v>
       </c>
       <c r="L39" s="2">
-        <v>46282.27054398148</v>
+        <v>46283.18092592592</v>
       </c>
       <c r="M39" t="s">
         <v>263</v>
@@ -3733,7 +3736,7 @@
         <v>3128</v>
       </c>
       <c r="L40" s="2">
-        <v>46282.27054398148</v>
+        <v>46283.18092592592</v>
       </c>
       <c r="M40" t="s">
         <v>263</v>
@@ -3801,7 +3804,7 @@
         <v>3542</v>
       </c>
       <c r="L41" s="2">
-        <v>46282.27054398148</v>
+        <v>46283.18092592592</v>
       </c>
       <c r="M41" t="s">
         <v>263</v>
@@ -3869,7 +3872,7 @@
         <v>3533</v>
       </c>
       <c r="L42" s="2">
-        <v>46282.27054398148</v>
+        <v>46283.18092592592</v>
       </c>
       <c r="M42" t="s">
         <v>263</v>
@@ -3937,7 +3940,7 @@
         <v>3513</v>
       </c>
       <c r="L43" s="2">
-        <v>46282.27054398148</v>
+        <v>46283.18092592592</v>
       </c>
       <c r="M43" t="s">
         <v>263</v>
@@ -4058,13 +4061,13 @@
         <v>1</v>
       </c>
       <c r="J45">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K45">
-        <v>3635</v>
+        <v>3649</v>
       </c>
       <c r="L45" s="2">
-        <v>46282.27054398148</v>
+        <v>46283.18092592592</v>
       </c>
       <c r="M45" t="s">
         <v>261</v>
@@ -4085,7 +4088,7 @@
         <v>268</v>
       </c>
       <c r="W45" s="2">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="Y45" t="s">
         <v>261</v>
@@ -4126,13 +4129,13 @@
         <v>1</v>
       </c>
       <c r="J46">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="K46">
-        <v>9125</v>
+        <v>9185</v>
       </c>
       <c r="L46" s="2">
-        <v>46282.27054398148</v>
+        <v>46283.18092592592</v>
       </c>
       <c r="M46" t="s">
         <v>261</v>
@@ -4153,7 +4156,7 @@
         <v>268</v>
       </c>
       <c r="W46" s="2">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="Y46" t="s">
         <v>261</v>
@@ -4197,10 +4200,10 @@
         <v>19</v>
       </c>
       <c r="K47">
-        <v>4520</v>
+        <v>4539</v>
       </c>
       <c r="L47" s="2">
-        <v>46282.27054398148</v>
+        <v>46283.18092592592</v>
       </c>
       <c r="M47" t="s">
         <v>261</v>
@@ -4221,7 +4224,7 @@
         <v>268</v>
       </c>
       <c r="W47" s="2">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="Y47" t="s">
         <v>261</v>
@@ -4268,7 +4271,7 @@
         <v>2299</v>
       </c>
       <c r="L48" s="2">
-        <v>46282.27054398148</v>
+        <v>46283.18092592592</v>
       </c>
       <c r="M48" t="s">
         <v>263</v>
@@ -4336,7 +4339,7 @@
         <v>1505</v>
       </c>
       <c r="L49" s="2">
-        <v>46282.27054398148</v>
+        <v>46283.18092592592</v>
       </c>
       <c r="M49" t="s">
         <v>263</v>
@@ -4401,10 +4404,10 @@
         <v>9</v>
       </c>
       <c r="K50">
-        <v>1756</v>
+        <v>1765</v>
       </c>
       <c r="L50" s="2">
-        <v>46282.27054398148</v>
+        <v>46283.18092592592</v>
       </c>
       <c r="M50" t="s">
         <v>261</v>
@@ -4466,13 +4469,13 @@
         <v>1</v>
       </c>
       <c r="J51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K51">
-        <v>1505</v>
+        <v>1507</v>
       </c>
       <c r="L51" s="2">
-        <v>46282.27054398148</v>
+        <v>46283.18092592592</v>
       </c>
       <c r="M51" t="s">
         <v>262</v>
@@ -4493,7 +4496,7 @@
         <v>268</v>
       </c>
       <c r="W51" s="2">
-        <v>46279</v>
+        <v>46281</v>
       </c>
       <c r="Y51" t="s">
         <v>261</v>
@@ -4540,7 +4543,7 @@
         <v>1466</v>
       </c>
       <c r="L52" s="2">
-        <v>46282.27054398148</v>
+        <v>46283.18092592592</v>
       </c>
       <c r="M52" t="s">
         <v>263</v>
@@ -4605,10 +4608,10 @@
         <v>3</v>
       </c>
       <c r="K53">
-        <v>2171</v>
+        <v>2174</v>
       </c>
       <c r="L53" s="2">
-        <v>46282.27054398148</v>
+        <v>46283.18092592592</v>
       </c>
       <c r="M53" t="s">
         <v>261</v>
@@ -4629,7 +4632,7 @@
         <v>268</v>
       </c>
       <c r="W53" s="2">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="Y53" t="s">
         <v>261</v>
@@ -4670,16 +4673,16 @@
         <v>1</v>
       </c>
       <c r="J54">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K54">
-        <v>1376</v>
+        <v>1378</v>
       </c>
       <c r="L54" s="2">
-        <v>46282.27054398148</v>
+        <v>46283.18092592592</v>
       </c>
       <c r="M54" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N54" t="s">
         <v>256</v>
@@ -4738,13 +4741,13 @@
         <v>1</v>
       </c>
       <c r="J55">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K55">
-        <v>2358</v>
+        <v>2367</v>
       </c>
       <c r="L55" s="2">
-        <v>46282.27054398148</v>
+        <v>46283.18092592592</v>
       </c>
       <c r="M55" t="s">
         <v>261</v>
@@ -4765,7 +4768,7 @@
         <v>268</v>
       </c>
       <c r="W55" s="2">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="Y55" t="s">
         <v>261</v>
@@ -4865,16 +4868,16 @@
         <v>1</v>
       </c>
       <c r="J57">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K57">
         <v>3981</v>
       </c>
       <c r="L57" s="2">
-        <v>46282.27054398148</v>
+        <v>46283.18092592592</v>
       </c>
       <c r="M57" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="N57" t="s">
         <v>256</v>
@@ -5172,10 +5175,10 @@
         <v>1</v>
       </c>
       <c r="K62">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="L62" s="2">
-        <v>46282.27054398148</v>
+        <v>46283.18092592592</v>
       </c>
       <c r="M62" t="s">
         <v>262</v>
@@ -5355,13 +5358,13 @@
         <v>1</v>
       </c>
       <c r="J65">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K65">
-        <v>4545</v>
+        <v>4567</v>
       </c>
       <c r="L65" s="2">
-        <v>46282.27054398148</v>
+        <v>46283.18092592592</v>
       </c>
       <c r="M65" t="s">
         <v>261</v>
@@ -5382,7 +5385,7 @@
         <v>268</v>
       </c>
       <c r="W65" s="2">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="Y65" t="s">
         <v>261</v>
@@ -5429,7 +5432,7 @@
         <v>3062</v>
       </c>
       <c r="L66" s="2">
-        <v>46282.27054398148</v>
+        <v>46283.18092592592</v>
       </c>
       <c r="M66" t="s">
         <v>263</v>
@@ -5491,16 +5494,16 @@
         <v>1</v>
       </c>
       <c r="J67">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K67">
-        <v>1754</v>
+        <v>1755</v>
       </c>
       <c r="L67" s="2">
-        <v>46282.27054398148</v>
+        <v>46283.18092592592</v>
       </c>
       <c r="M67" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N67" t="s">
         <v>256</v>
@@ -5559,13 +5562,13 @@
         <v>1</v>
       </c>
       <c r="J68">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="K68">
-        <v>4214</v>
+        <v>4228</v>
       </c>
       <c r="L68" s="2">
-        <v>46282.27054398148</v>
+        <v>46283.18092592592</v>
       </c>
       <c r="M68" t="s">
         <v>261</v>
@@ -5586,7 +5589,7 @@
         <v>268</v>
       </c>
       <c r="W68" s="2">
-        <v>46280</v>
+        <v>46283</v>
       </c>
       <c r="Y68" t="s">
         <v>261</v>
@@ -5633,7 +5636,7 @@
         <v>3069</v>
       </c>
       <c r="L69" s="2">
-        <v>46282.27054398148</v>
+        <v>46283.18092592592</v>
       </c>
       <c r="M69" t="s">
         <v>263</v>
@@ -5698,10 +5701,10 @@
         <v>11</v>
       </c>
       <c r="K70">
-        <v>2601</v>
+        <v>2612</v>
       </c>
       <c r="L70" s="2">
-        <v>46282.27054398148</v>
+        <v>46283.18092592592</v>
       </c>
       <c r="M70" t="s">
         <v>261</v>
@@ -5722,7 +5725,7 @@
         <v>268</v>
       </c>
       <c r="W70" s="2">
-        <v>46280</v>
+        <v>46283</v>
       </c>
       <c r="Y70" t="s">
         <v>261</v>
@@ -5763,13 +5766,13 @@
         <v>1</v>
       </c>
       <c r="J71">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K71">
-        <v>2643</v>
+        <v>2651</v>
       </c>
       <c r="L71" s="2">
-        <v>46282.27054398148</v>
+        <v>46283.18092592592</v>
       </c>
       <c r="M71" t="s">
         <v>261</v>
@@ -5790,7 +5793,7 @@
         <v>268</v>
       </c>
       <c r="W71" s="2">
-        <v>46280</v>
+        <v>46283</v>
       </c>
       <c r="Y71" t="s">
         <v>261</v>
@@ -5890,16 +5893,16 @@
         <v>1</v>
       </c>
       <c r="J73">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K73">
         <v>1373</v>
       </c>
       <c r="L73" s="2">
-        <v>46282.27054398148</v>
+        <v>46283.18092592592</v>
       </c>
       <c r="M73" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N73" t="s">
         <v>256</v>
@@ -5964,7 +5967,7 @@
         <v>1449</v>
       </c>
       <c r="L74" s="2">
-        <v>46282.27054398148</v>
+        <v>46283.18092592592</v>
       </c>
       <c r="M74" t="s">
         <v>263</v>
@@ -6032,7 +6035,7 @@
         <v>1482</v>
       </c>
       <c r="L75" s="2">
-        <v>46282.27054398148</v>
+        <v>46283.18092592592</v>
       </c>
       <c r="M75" t="s">
         <v>263</v>
@@ -6097,10 +6100,10 @@
         <v>1</v>
       </c>
       <c r="K76">
-        <v>1537</v>
+        <v>1538</v>
       </c>
       <c r="L76" s="2">
-        <v>46282.27054398148</v>
+        <v>46283.18092592592</v>
       </c>
       <c r="M76" t="s">
         <v>262</v>
@@ -6121,7 +6124,7 @@
         <v>268</v>
       </c>
       <c r="W76" s="2">
-        <v>46279</v>
+        <v>46282</v>
       </c>
       <c r="Y76" t="s">
         <v>261</v>
@@ -6165,10 +6168,10 @@
         <v>2</v>
       </c>
       <c r="K77">
-        <v>1557</v>
+        <v>1559</v>
       </c>
       <c r="L77" s="2">
-        <v>46282.27054398148</v>
+        <v>46283.18092592592</v>
       </c>
       <c r="M77" t="s">
         <v>262</v>
@@ -6236,7 +6239,7 @@
         <v>1565</v>
       </c>
       <c r="L78" s="2">
-        <v>46282.27054398148</v>
+        <v>46283.18092592592</v>
       </c>
       <c r="M78" t="s">
         <v>263</v>
@@ -6298,13 +6301,13 @@
         <v>1</v>
       </c>
       <c r="J79">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K79">
-        <v>1775</v>
+        <v>1783</v>
       </c>
       <c r="L79" s="2">
-        <v>46282.27054398148</v>
+        <v>46283.18092592592</v>
       </c>
       <c r="M79" t="s">
         <v>261</v>
@@ -6325,7 +6328,7 @@
         <v>268</v>
       </c>
       <c r="W79" s="2">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="Y79" t="s">
         <v>261</v>
@@ -6369,10 +6372,10 @@
         <v>1</v>
       </c>
       <c r="K80">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="L80" s="2">
-        <v>46282.27054398148</v>
+        <v>46283.18092592592</v>
       </c>
       <c r="M80" t="s">
         <v>262</v>
@@ -6440,7 +6443,7 @@
         <v>3591</v>
       </c>
       <c r="L81" s="2">
-        <v>46282.27054398148</v>
+        <v>46283.18092592592</v>
       </c>
       <c r="M81" t="s">
         <v>263</v>
@@ -6744,7 +6747,7 @@
         <v>652</v>
       </c>
       <c r="L86" s="2">
-        <v>46282.27054398148</v>
+        <v>46283.18092592592</v>
       </c>
       <c r="M86" t="s">
         <v>263</v>
@@ -6812,7 +6815,7 @@
         <v>3609</v>
       </c>
       <c r="L87" s="2">
-        <v>46282.27054398148</v>
+        <v>46283.18092592592</v>
       </c>
       <c r="M87" t="s">
         <v>263</v>
@@ -6880,7 +6883,7 @@
         <v>3580</v>
       </c>
       <c r="L88" s="2">
-        <v>46282.27054398148</v>
+        <v>46283.18092592592</v>
       </c>
       <c r="M88" t="s">
         <v>263</v>
@@ -6989,7 +6992,7 @@
         <v>125</v>
       </c>
       <c r="L90" s="2">
-        <v>46282.27054398148</v>
+        <v>46283.18092592592</v>
       </c>
       <c r="M90" t="s">
         <v>264</v>

--- a/sites.xlsx
+++ b/sites.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1369" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1368" uniqueCount="276">
   <si>
     <t>site_name</t>
   </si>
@@ -811,6 +811,9 @@
     <t>FAIL</t>
   </si>
   <si>
+    <t>CHECK_REQUIRED</t>
+  </si>
+  <si>
     <t>STEP2-3</t>
   </si>
   <si>
@@ -836,6 +839,9 @@
   </si>
   <si>
     <t>selenium:detail_date</t>
+  </si>
+  <si>
+    <t>RECENT_HINT_BUT_ZERO</t>
   </si>
 </sst>
 </file>
@@ -1314,16 +1320,16 @@
         <v>257</v>
       </c>
       <c r="O2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W2" s="2">
         <v>46155</v>
@@ -1376,16 +1382,16 @@
         <v>257</v>
       </c>
       <c r="O3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W3" s="2">
         <v>46087</v>
@@ -1438,16 +1444,16 @@
         <v>257</v>
       </c>
       <c r="O4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W4" s="2">
         <v>46168</v>
@@ -1500,16 +1506,16 @@
         <v>257</v>
       </c>
       <c r="O5" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q5" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W5" s="2">
         <v>46161</v>
@@ -1553,7 +1559,7 @@
         <v>169</v>
       </c>
       <c r="L6" s="2">
-        <v>46283.18092592592</v>
+        <v>46284.15655092592</v>
       </c>
       <c r="M6" t="s">
         <v>263</v>
@@ -1562,16 +1568,16 @@
         <v>256</v>
       </c>
       <c r="O6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W6" s="2">
         <v>46168</v>
@@ -1633,16 +1639,16 @@
         <v>257</v>
       </c>
       <c r="O7" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P7" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R7" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W7" s="2">
         <v>46164</v>
@@ -1695,16 +1701,16 @@
         <v>257</v>
       </c>
       <c r="O8" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P8" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q8" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R8" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W8" s="2">
         <v>46155</v>
@@ -1757,16 +1763,16 @@
         <v>257</v>
       </c>
       <c r="O9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W9" s="2">
         <v>46045</v>
@@ -1819,16 +1825,16 @@
         <v>257</v>
       </c>
       <c r="O10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q10" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W10" s="2">
         <v>46045</v>
@@ -1881,16 +1887,16 @@
         <v>257</v>
       </c>
       <c r="O11" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P11" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q11" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R11" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W11" s="2">
         <v>46129</v>
@@ -1943,16 +1949,16 @@
         <v>257</v>
       </c>
       <c r="O12" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P12" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q12" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R12" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W12" s="2">
         <v>46164</v>
@@ -1996,25 +2002,25 @@
         <v>170</v>
       </c>
       <c r="L13" s="2">
-        <v>46283.18092592592</v>
+        <v>46284.15655092592</v>
       </c>
       <c r="M13" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="N13" t="s">
         <v>256</v>
       </c>
       <c r="O13" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P13" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q13" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R13" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W13" s="2">
         <v>46254</v>
@@ -2026,10 +2032,7 @@
         <v>261</v>
       </c>
       <c r="Z13" t="s">
-        <v>271</v>
-      </c>
-      <c r="AA13" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
     </row>
     <row r="14" spans="1:27">
@@ -2064,10 +2067,10 @@
         <v>1</v>
       </c>
       <c r="K14">
-        <v>3542</v>
+        <v>3544</v>
       </c>
       <c r="L14" s="2">
-        <v>46283.18092592592</v>
+        <v>46284.15655092592</v>
       </c>
       <c r="M14" t="s">
         <v>262</v>
@@ -2076,16 +2079,16 @@
         <v>256</v>
       </c>
       <c r="O14" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P14" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q14" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R14" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W14" s="2">
         <v>46280</v>
@@ -2097,7 +2100,7 @@
         <v>263</v>
       </c>
       <c r="AA14" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="15" spans="1:27">
@@ -2132,10 +2135,10 @@
         <v>1</v>
       </c>
       <c r="K15">
-        <v>3533</v>
+        <v>3535</v>
       </c>
       <c r="L15" s="2">
-        <v>46283.18092592592</v>
+        <v>46284.15655092592</v>
       </c>
       <c r="M15" t="s">
         <v>262</v>
@@ -2144,16 +2147,16 @@
         <v>256</v>
       </c>
       <c r="O15" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P15" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q15" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R15" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W15" s="2">
         <v>46279</v>
@@ -2165,7 +2168,7 @@
         <v>263</v>
       </c>
       <c r="AA15" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="16" spans="1:27">
@@ -2200,10 +2203,10 @@
         <v>2</v>
       </c>
       <c r="K16">
-        <v>3590</v>
+        <v>3594</v>
       </c>
       <c r="L16" s="2">
-        <v>46283.18092592592</v>
+        <v>46284.15655092592</v>
       </c>
       <c r="M16" t="s">
         <v>262</v>
@@ -2212,16 +2215,16 @@
         <v>256</v>
       </c>
       <c r="O16" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P16" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q16" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R16" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W16" s="2">
         <v>46281</v>
@@ -2233,7 +2236,7 @@
         <v>263</v>
       </c>
       <c r="AA16" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="17" spans="1:27">
@@ -2280,16 +2283,16 @@
         <v>257</v>
       </c>
       <c r="O17" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P17" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q17" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R17" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W17" s="2">
         <v>46113</v>
@@ -2330,7 +2333,7 @@
         <v>3630</v>
       </c>
       <c r="L18" s="2">
-        <v>46283.18092592592</v>
+        <v>46284.15655092592</v>
       </c>
       <c r="M18" t="s">
         <v>263</v>
@@ -2339,16 +2342,16 @@
         <v>256</v>
       </c>
       <c r="O18" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P18" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q18" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R18" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W18" s="2">
         <v>46278</v>
@@ -2357,10 +2360,10 @@
         <v>261</v>
       </c>
       <c r="Z18" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AA18" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="19" spans="1:27">
@@ -2407,16 +2410,16 @@
         <v>257</v>
       </c>
       <c r="O19" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P19" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q19" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R19" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W19" s="2">
         <v>46163</v>
@@ -2466,16 +2469,16 @@
         <v>257</v>
       </c>
       <c r="O20" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P20" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q20" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R20" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W20" s="2">
         <v>46165</v>
@@ -2525,16 +2528,16 @@
         <v>257</v>
       </c>
       <c r="O21" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P21" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q21" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R21" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W21" s="2">
         <v>46166</v>
@@ -2575,7 +2578,7 @@
         <v>3591</v>
       </c>
       <c r="L22" s="2">
-        <v>46283.18092592592</v>
+        <v>46284.15655092592</v>
       </c>
       <c r="M22" t="s">
         <v>263</v>
@@ -2584,16 +2587,16 @@
         <v>256</v>
       </c>
       <c r="O22" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P22" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q22" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R22" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W22" s="2">
         <v>46168</v>
@@ -2605,7 +2608,7 @@
         <v>263</v>
       </c>
       <c r="AA22" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="23" spans="1:27">
@@ -2643,7 +2646,7 @@
         <v>3591</v>
       </c>
       <c r="L23" s="2">
-        <v>46283.18092592592</v>
+        <v>46284.15655092592</v>
       </c>
       <c r="M23" t="s">
         <v>263</v>
@@ -2652,16 +2655,16 @@
         <v>256</v>
       </c>
       <c r="O23" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P23" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q23" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R23" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W23" s="2">
         <v>46168</v>
@@ -2673,7 +2676,7 @@
         <v>263</v>
       </c>
       <c r="AA23" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="24" spans="1:27">
@@ -2711,7 +2714,7 @@
         <v>131</v>
       </c>
       <c r="L24" s="2">
-        <v>46283.18092592592</v>
+        <v>46284.15655092592</v>
       </c>
       <c r="M24" t="s">
         <v>263</v>
@@ -2720,16 +2723,16 @@
         <v>256</v>
       </c>
       <c r="O24" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P24" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q24" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R24" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W24" s="2">
         <v>46257</v>
@@ -2779,7 +2782,7 @@
         <v>145</v>
       </c>
       <c r="L25" s="2">
-        <v>46283.18092592592</v>
+        <v>46284.15655092592</v>
       </c>
       <c r="M25" t="s">
         <v>263</v>
@@ -2788,16 +2791,16 @@
         <v>256</v>
       </c>
       <c r="O25" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P25" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q25" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R25" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W25" s="2">
         <v>46272</v>
@@ -2841,34 +2844,34 @@
         <v>1</v>
       </c>
       <c r="J26">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K26">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="L26" s="2">
-        <v>46283.18092592592</v>
+        <v>46284.15655092592</v>
       </c>
       <c r="M26" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="N26" t="s">
         <v>256</v>
       </c>
       <c r="O26" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P26" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q26" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R26" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W26" s="2">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="Y26" t="s">
         <v>261</v>
@@ -2877,7 +2880,7 @@
         <v>263</v>
       </c>
       <c r="AA26" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="27" spans="1:27">
@@ -2924,16 +2927,16 @@
         <v>257</v>
       </c>
       <c r="O27" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P27" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q27" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R27" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W27" s="2">
         <v>46172</v>
@@ -2983,16 +2986,16 @@
         <v>257</v>
       </c>
       <c r="O28" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P28" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q28" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R28" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W28" s="2">
         <v>46164</v>
@@ -3042,16 +3045,16 @@
         <v>257</v>
       </c>
       <c r="O29" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P29" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q29" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R29" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W29" s="2">
         <v>46168</v>
@@ -3101,16 +3104,16 @@
         <v>257</v>
       </c>
       <c r="O30" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P30" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q30" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R30" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W30" s="2">
         <v>46168</v>
@@ -3160,16 +3163,16 @@
         <v>257</v>
       </c>
       <c r="O31" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P31" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q31" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R31" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W31" s="2">
         <v>46168</v>
@@ -3204,31 +3207,31 @@
         <v>1</v>
       </c>
       <c r="J32">
-        <v>147</v>
+        <v>0</v>
       </c>
       <c r="K32">
         <v>14043</v>
       </c>
       <c r="L32" s="2">
-        <v>46283.18092592592</v>
+        <v>46284.15655092592</v>
       </c>
       <c r="M32" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="N32" t="s">
         <v>256</v>
       </c>
       <c r="O32" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P32" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q32" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R32" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W32" s="2">
         <v>46283</v>
@@ -3237,10 +3240,10 @@
         <v>261</v>
       </c>
       <c r="Z32" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AA32" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="33" spans="1:27">
@@ -3287,16 +3290,16 @@
         <v>257</v>
       </c>
       <c r="O33" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P33" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q33" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R33" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W33" s="2">
         <v>46168</v>
@@ -3346,16 +3349,16 @@
         <v>257</v>
       </c>
       <c r="O34" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P34" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q34" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R34" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W34" s="2">
         <v>46168</v>
@@ -3396,7 +3399,7 @@
         <v>3591</v>
       </c>
       <c r="L35" s="2">
-        <v>46283.18092592592</v>
+        <v>46284.15655092592</v>
       </c>
       <c r="M35" t="s">
         <v>263</v>
@@ -3405,16 +3408,16 @@
         <v>256</v>
       </c>
       <c r="O35" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P35" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q35" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R35" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W35" s="2">
         <v>46157</v>
@@ -3426,7 +3429,7 @@
         <v>263</v>
       </c>
       <c r="AA35" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="36" spans="1:27">
@@ -3464,7 +3467,7 @@
         <v>3591</v>
       </c>
       <c r="L36" s="2">
-        <v>46283.18092592592</v>
+        <v>46284.15655092592</v>
       </c>
       <c r="M36" t="s">
         <v>263</v>
@@ -3473,16 +3476,16 @@
         <v>256</v>
       </c>
       <c r="O36" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P36" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q36" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R36" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W36" s="2">
         <v>46168</v>
@@ -3494,7 +3497,7 @@
         <v>263</v>
       </c>
       <c r="AA36" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="37" spans="1:27">
@@ -3532,7 +3535,7 @@
         <v>1826</v>
       </c>
       <c r="L37" s="2">
-        <v>46283.18092592592</v>
+        <v>46284.15655092592</v>
       </c>
       <c r="M37" t="s">
         <v>263</v>
@@ -3541,16 +3544,16 @@
         <v>256</v>
       </c>
       <c r="O37" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P37" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q37" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R37" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W37" s="2">
         <v>46132</v>
@@ -3562,7 +3565,7 @@
         <v>263</v>
       </c>
       <c r="AA37" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="38" spans="1:27">
@@ -3600,7 +3603,7 @@
         <v>2937</v>
       </c>
       <c r="L38" s="2">
-        <v>46283.18092592592</v>
+        <v>46284.15655092592</v>
       </c>
       <c r="M38" t="s">
         <v>263</v>
@@ -3609,16 +3612,16 @@
         <v>256</v>
       </c>
       <c r="O38" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P38" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q38" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R38" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W38" s="2">
         <v>46113</v>
@@ -3630,7 +3633,7 @@
         <v>263</v>
       </c>
       <c r="AA38" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="39" spans="1:27">
@@ -3668,7 +3671,7 @@
         <v>3176</v>
       </c>
       <c r="L39" s="2">
-        <v>46283.18092592592</v>
+        <v>46284.15655092592</v>
       </c>
       <c r="M39" t="s">
         <v>263</v>
@@ -3677,16 +3680,16 @@
         <v>256</v>
       </c>
       <c r="O39" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P39" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q39" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R39" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W39" s="2">
         <v>46140</v>
@@ -3698,7 +3701,7 @@
         <v>263</v>
       </c>
       <c r="AA39" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="40" spans="1:27">
@@ -3736,7 +3739,7 @@
         <v>3128</v>
       </c>
       <c r="L40" s="2">
-        <v>46283.18092592592</v>
+        <v>46284.15655092592</v>
       </c>
       <c r="M40" t="s">
         <v>263</v>
@@ -3745,16 +3748,16 @@
         <v>256</v>
       </c>
       <c r="O40" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P40" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q40" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R40" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W40" s="2">
         <v>46024</v>
@@ -3766,7 +3769,7 @@
         <v>263</v>
       </c>
       <c r="AA40" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="41" spans="1:27">
@@ -3804,7 +3807,7 @@
         <v>3542</v>
       </c>
       <c r="L41" s="2">
-        <v>46283.18092592592</v>
+        <v>46284.15655092592</v>
       </c>
       <c r="M41" t="s">
         <v>263</v>
@@ -3813,16 +3816,16 @@
         <v>256</v>
       </c>
       <c r="O41" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P41" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q41" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R41" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W41" s="2">
         <v>46168</v>
@@ -3834,7 +3837,7 @@
         <v>263</v>
       </c>
       <c r="AA41" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="42" spans="1:27">
@@ -3872,7 +3875,7 @@
         <v>3533</v>
       </c>
       <c r="L42" s="2">
-        <v>46283.18092592592</v>
+        <v>46284.15655092592</v>
       </c>
       <c r="M42" t="s">
         <v>263</v>
@@ -3881,16 +3884,16 @@
         <v>256</v>
       </c>
       <c r="O42" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P42" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q42" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R42" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W42" s="2">
         <v>46164</v>
@@ -3902,7 +3905,7 @@
         <v>263</v>
       </c>
       <c r="AA42" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="43" spans="1:27">
@@ -3940,7 +3943,7 @@
         <v>3513</v>
       </c>
       <c r="L43" s="2">
-        <v>46283.18092592592</v>
+        <v>46284.15655092592</v>
       </c>
       <c r="M43" t="s">
         <v>263</v>
@@ -3949,16 +3952,16 @@
         <v>256</v>
       </c>
       <c r="O43" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P43" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q43" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R43" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W43" s="2">
         <v>46112</v>
@@ -3970,7 +3973,7 @@
         <v>263</v>
       </c>
       <c r="AA43" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="44" spans="1:27">
@@ -4017,16 +4020,16 @@
         <v>257</v>
       </c>
       <c r="O44" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P44" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q44" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R44" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W44" s="2">
         <v>46171</v>
@@ -4061,13 +4064,13 @@
         <v>1</v>
       </c>
       <c r="J45">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K45">
-        <v>3649</v>
+        <v>3681</v>
       </c>
       <c r="L45" s="2">
-        <v>46283.18092592592</v>
+        <v>46284.15655092592</v>
       </c>
       <c r="M45" t="s">
         <v>261</v>
@@ -4076,19 +4079,19 @@
         <v>256</v>
       </c>
       <c r="O45" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P45" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q45" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R45" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W45" s="2">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="Y45" t="s">
         <v>261</v>
@@ -4097,7 +4100,7 @@
         <v>263</v>
       </c>
       <c r="AA45" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="46" spans="1:27">
@@ -4129,13 +4132,13 @@
         <v>1</v>
       </c>
       <c r="J46">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="K46">
-        <v>9185</v>
+        <v>9333</v>
       </c>
       <c r="L46" s="2">
-        <v>46283.18092592592</v>
+        <v>46284.15655092592</v>
       </c>
       <c r="M46" t="s">
         <v>261</v>
@@ -4144,19 +4147,19 @@
         <v>256</v>
       </c>
       <c r="O46" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P46" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q46" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R46" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W46" s="2">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="Y46" t="s">
         <v>261</v>
@@ -4165,7 +4168,7 @@
         <v>263</v>
       </c>
       <c r="AA46" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="47" spans="1:27">
@@ -4197,13 +4200,13 @@
         <v>1</v>
       </c>
       <c r="J47">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K47">
-        <v>4539</v>
+        <v>4575</v>
       </c>
       <c r="L47" s="2">
-        <v>46283.18092592592</v>
+        <v>46284.15655092592</v>
       </c>
       <c r="M47" t="s">
         <v>261</v>
@@ -4212,19 +4215,19 @@
         <v>256</v>
       </c>
       <c r="O47" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P47" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q47" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R47" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W47" s="2">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="Y47" t="s">
         <v>261</v>
@@ -4233,7 +4236,7 @@
         <v>263</v>
       </c>
       <c r="AA47" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="48" spans="1:27">
@@ -4271,7 +4274,7 @@
         <v>2299</v>
       </c>
       <c r="L48" s="2">
-        <v>46283.18092592592</v>
+        <v>46284.15655092592</v>
       </c>
       <c r="M48" t="s">
         <v>263</v>
@@ -4280,16 +4283,16 @@
         <v>256</v>
       </c>
       <c r="O48" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P48" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q48" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R48" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W48" s="2">
         <v>46168</v>
@@ -4301,7 +4304,7 @@
         <v>263</v>
       </c>
       <c r="AA48" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="49" spans="1:27">
@@ -4339,7 +4342,7 @@
         <v>1505</v>
       </c>
       <c r="L49" s="2">
-        <v>46283.18092592592</v>
+        <v>46284.15655092592</v>
       </c>
       <c r="M49" t="s">
         <v>263</v>
@@ -4348,16 +4351,16 @@
         <v>256</v>
       </c>
       <c r="O49" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P49" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q49" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R49" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W49" s="2">
         <v>46273</v>
@@ -4369,7 +4372,7 @@
         <v>263</v>
       </c>
       <c r="AA49" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="50" spans="1:27">
@@ -4401,31 +4404,31 @@
         <v>1</v>
       </c>
       <c r="J50">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K50">
         <v>1765</v>
       </c>
       <c r="L50" s="2">
-        <v>46283.18092592592</v>
+        <v>46284.15655092592</v>
       </c>
       <c r="M50" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="N50" t="s">
         <v>256</v>
       </c>
       <c r="O50" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P50" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q50" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R50" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W50" s="2">
         <v>46280</v>
@@ -4437,7 +4440,7 @@
         <v>263</v>
       </c>
       <c r="AA50" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="51" spans="1:27">
@@ -4469,13 +4472,13 @@
         <v>1</v>
       </c>
       <c r="J51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K51">
-        <v>1507</v>
+        <v>1509</v>
       </c>
       <c r="L51" s="2">
-        <v>46283.18092592592</v>
+        <v>46284.15655092592</v>
       </c>
       <c r="M51" t="s">
         <v>262</v>
@@ -4484,16 +4487,16 @@
         <v>256</v>
       </c>
       <c r="O51" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P51" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q51" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R51" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W51" s="2">
         <v>46281</v>
@@ -4505,7 +4508,7 @@
         <v>263</v>
       </c>
       <c r="AA51" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="52" spans="1:27">
@@ -4543,7 +4546,7 @@
         <v>1466</v>
       </c>
       <c r="L52" s="2">
-        <v>46283.18092592592</v>
+        <v>46284.15655092592</v>
       </c>
       <c r="M52" t="s">
         <v>263</v>
@@ -4552,16 +4555,16 @@
         <v>256</v>
       </c>
       <c r="O52" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P52" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q52" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R52" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W52" s="2">
         <v>46142</v>
@@ -4573,7 +4576,7 @@
         <v>263</v>
       </c>
       <c r="AA52" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="53" spans="1:27">
@@ -4608,10 +4611,10 @@
         <v>3</v>
       </c>
       <c r="K53">
-        <v>2174</v>
+        <v>2180</v>
       </c>
       <c r="L53" s="2">
-        <v>46283.18092592592</v>
+        <v>46284.15655092592</v>
       </c>
       <c r="M53" t="s">
         <v>261</v>
@@ -4620,16 +4623,16 @@
         <v>256</v>
       </c>
       <c r="O53" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P53" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q53" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R53" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W53" s="2">
         <v>46282</v>
@@ -4641,7 +4644,7 @@
         <v>263</v>
       </c>
       <c r="AA53" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="54" spans="1:27">
@@ -4673,13 +4676,13 @@
         <v>1</v>
       </c>
       <c r="J54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K54">
-        <v>1378</v>
+        <v>1380</v>
       </c>
       <c r="L54" s="2">
-        <v>46283.18092592592</v>
+        <v>46284.15655092592</v>
       </c>
       <c r="M54" t="s">
         <v>262</v>
@@ -4688,16 +4691,16 @@
         <v>256</v>
       </c>
       <c r="O54" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P54" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q54" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R54" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W54" s="2">
         <v>46281</v>
@@ -4709,7 +4712,7 @@
         <v>263</v>
       </c>
       <c r="AA54" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="55" spans="1:27">
@@ -4744,10 +4747,10 @@
         <v>9</v>
       </c>
       <c r="K55">
-        <v>2367</v>
+        <v>2385</v>
       </c>
       <c r="L55" s="2">
-        <v>46283.18092592592</v>
+        <v>46284.15655092592</v>
       </c>
       <c r="M55" t="s">
         <v>261</v>
@@ -4756,16 +4759,16 @@
         <v>256</v>
       </c>
       <c r="O55" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P55" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q55" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R55" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W55" s="2">
         <v>46282</v>
@@ -4774,10 +4777,10 @@
         <v>261</v>
       </c>
       <c r="Z55" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AA55" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="56" spans="1:27">
@@ -4824,16 +4827,16 @@
         <v>257</v>
       </c>
       <c r="O56" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P56" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q56" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R56" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W56" s="2">
         <v>46161</v>
@@ -4868,34 +4871,34 @@
         <v>1</v>
       </c>
       <c r="J57">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K57">
-        <v>3981</v>
+        <v>3985</v>
       </c>
       <c r="L57" s="2">
-        <v>46283.18092592592</v>
+        <v>46284.15655092592</v>
       </c>
       <c r="M57" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="N57" t="s">
         <v>256</v>
       </c>
       <c r="O57" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P57" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q57" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R57" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W57" s="2">
-        <v>46279</v>
+        <v>46283</v>
       </c>
       <c r="Y57" t="s">
         <v>261</v>
@@ -4904,7 +4907,7 @@
         <v>263</v>
       </c>
       <c r="AA57" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="58" spans="1:27">
@@ -4951,16 +4954,16 @@
         <v>257</v>
       </c>
       <c r="O58" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P58" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q58" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R58" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W58" s="2">
         <v>46148</v>
@@ -5010,16 +5013,16 @@
         <v>257</v>
       </c>
       <c r="O59" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P59" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q59" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R59" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W59" s="2">
         <v>46168</v>
@@ -5069,16 +5072,16 @@
         <v>257</v>
       </c>
       <c r="O60" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P60" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q60" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R60" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W60" s="2">
         <v>46164</v>
@@ -5128,16 +5131,16 @@
         <v>257</v>
       </c>
       <c r="O61" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P61" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q61" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R61" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W61" s="2">
         <v>46168</v>
@@ -5172,31 +5175,31 @@
         <v>1</v>
       </c>
       <c r="J62">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K62">
         <v>1671</v>
       </c>
       <c r="L62" s="2">
-        <v>46283.18092592592</v>
+        <v>46284.15655092592</v>
       </c>
       <c r="M62" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N62" t="s">
         <v>256</v>
       </c>
       <c r="O62" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P62" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q62" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R62" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W62" s="2">
         <v>46280</v>
@@ -5208,7 +5211,7 @@
         <v>263</v>
       </c>
       <c r="AA62" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="63" spans="1:27">
@@ -5255,16 +5258,16 @@
         <v>257</v>
       </c>
       <c r="O63" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P63" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q63" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R63" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W63" s="2">
         <v>46164</v>
@@ -5314,16 +5317,16 @@
         <v>257</v>
       </c>
       <c r="O64" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P64" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q64" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R64" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W64" s="2">
         <v>46168</v>
@@ -5358,13 +5361,13 @@
         <v>1</v>
       </c>
       <c r="J65">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="K65">
-        <v>4567</v>
+        <v>4603</v>
       </c>
       <c r="L65" s="2">
-        <v>46283.18092592592</v>
+        <v>46284.15655092592</v>
       </c>
       <c r="M65" t="s">
         <v>261</v>
@@ -5373,28 +5376,28 @@
         <v>256</v>
       </c>
       <c r="O65" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P65" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q65" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R65" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W65" s="2">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="Y65" t="s">
         <v>261</v>
       </c>
       <c r="Z65" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AA65" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="66" spans="1:27">
@@ -5432,7 +5435,7 @@
         <v>3062</v>
       </c>
       <c r="L66" s="2">
-        <v>46283.18092592592</v>
+        <v>46284.15655092592</v>
       </c>
       <c r="M66" t="s">
         <v>263</v>
@@ -5441,16 +5444,16 @@
         <v>256</v>
       </c>
       <c r="O66" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P66" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q66" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R66" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W66" s="2">
         <v>46261</v>
@@ -5462,7 +5465,7 @@
         <v>263</v>
       </c>
       <c r="AA66" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="67" spans="1:27">
@@ -5494,31 +5497,31 @@
         <v>1</v>
       </c>
       <c r="J67">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K67">
         <v>1755</v>
       </c>
       <c r="L67" s="2">
-        <v>46283.18092592592</v>
+        <v>46284.15655092592</v>
       </c>
       <c r="M67" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N67" t="s">
         <v>256</v>
       </c>
       <c r="O67" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P67" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q67" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R67" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W67" s="2">
         <v>46280</v>
@@ -5527,10 +5530,10 @@
         <v>261</v>
       </c>
       <c r="Z67" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AA67" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="68" spans="1:27">
@@ -5562,13 +5565,13 @@
         <v>1</v>
       </c>
       <c r="J68">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="K68">
-        <v>4228</v>
+        <v>4242</v>
       </c>
       <c r="L68" s="2">
-        <v>46283.18092592592</v>
+        <v>46284.15655092592</v>
       </c>
       <c r="M68" t="s">
         <v>261</v>
@@ -5577,16 +5580,16 @@
         <v>256</v>
       </c>
       <c r="O68" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P68" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q68" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R68" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W68" s="2">
         <v>46283</v>
@@ -5595,10 +5598,10 @@
         <v>261</v>
       </c>
       <c r="Z68" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AA68" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="69" spans="1:27">
@@ -5636,7 +5639,7 @@
         <v>3069</v>
       </c>
       <c r="L69" s="2">
-        <v>46283.18092592592</v>
+        <v>46284.15655092592</v>
       </c>
       <c r="M69" t="s">
         <v>263</v>
@@ -5645,16 +5648,16 @@
         <v>256</v>
       </c>
       <c r="O69" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P69" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q69" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R69" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W69" s="2">
         <v>46280</v>
@@ -5666,7 +5669,7 @@
         <v>263</v>
       </c>
       <c r="AA69" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="70" spans="1:27">
@@ -5698,31 +5701,31 @@
         <v>1</v>
       </c>
       <c r="J70">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K70">
         <v>2612</v>
       </c>
       <c r="L70" s="2">
-        <v>46283.18092592592</v>
+        <v>46284.15655092592</v>
       </c>
       <c r="M70" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="N70" t="s">
         <v>256</v>
       </c>
       <c r="O70" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P70" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q70" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R70" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W70" s="2">
         <v>46283</v>
@@ -5731,10 +5734,10 @@
         <v>261</v>
       </c>
       <c r="Z70" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AA70" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="71" spans="1:27">
@@ -5766,13 +5769,13 @@
         <v>1</v>
       </c>
       <c r="J71">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K71">
-        <v>2651</v>
+        <v>2663</v>
       </c>
       <c r="L71" s="2">
-        <v>46283.18092592592</v>
+        <v>46284.15655092592</v>
       </c>
       <c r="M71" t="s">
         <v>261</v>
@@ -5781,16 +5784,16 @@
         <v>256</v>
       </c>
       <c r="O71" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P71" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q71" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R71" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W71" s="2">
         <v>46283</v>
@@ -5799,10 +5802,10 @@
         <v>261</v>
       </c>
       <c r="Z71" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AA71" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="72" spans="1:27">
@@ -5849,16 +5852,16 @@
         <v>257</v>
       </c>
       <c r="O72" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P72" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q72" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R72" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W72" s="2">
         <v>46164</v>
@@ -5893,34 +5896,34 @@
         <v>1</v>
       </c>
       <c r="J73">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K73">
-        <v>1373</v>
+        <v>1377</v>
       </c>
       <c r="L73" s="2">
-        <v>46283.18092592592</v>
+        <v>46284.15655092592</v>
       </c>
       <c r="M73" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="N73" t="s">
         <v>256</v>
       </c>
       <c r="O73" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P73" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q73" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R73" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W73" s="2">
-        <v>46279</v>
+        <v>46283</v>
       </c>
       <c r="Y73" t="s">
         <v>261</v>
@@ -5929,7 +5932,7 @@
         <v>263</v>
       </c>
       <c r="AA73" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="74" spans="1:27">
@@ -5967,7 +5970,7 @@
         <v>1449</v>
       </c>
       <c r="L74" s="2">
-        <v>46283.18092592592</v>
+        <v>46284.15655092592</v>
       </c>
       <c r="M74" t="s">
         <v>263</v>
@@ -5976,16 +5979,16 @@
         <v>256</v>
       </c>
       <c r="O74" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P74" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q74" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R74" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W74" s="2">
         <v>46185</v>
@@ -5997,7 +6000,7 @@
         <v>263</v>
       </c>
       <c r="AA74" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="75" spans="1:27">
@@ -6035,7 +6038,7 @@
         <v>1482</v>
       </c>
       <c r="L75" s="2">
-        <v>46283.18092592592</v>
+        <v>46284.15655092592</v>
       </c>
       <c r="M75" t="s">
         <v>263</v>
@@ -6044,16 +6047,16 @@
         <v>256</v>
       </c>
       <c r="O75" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P75" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q75" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R75" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W75" s="2">
         <v>46265</v>
@@ -6065,7 +6068,7 @@
         <v>263</v>
       </c>
       <c r="AA75" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="76" spans="1:27">
@@ -6100,10 +6103,10 @@
         <v>1</v>
       </c>
       <c r="K76">
-        <v>1538</v>
+        <v>1540</v>
       </c>
       <c r="L76" s="2">
-        <v>46283.18092592592</v>
+        <v>46284.15655092592</v>
       </c>
       <c r="M76" t="s">
         <v>262</v>
@@ -6112,16 +6115,16 @@
         <v>256</v>
       </c>
       <c r="O76" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P76" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q76" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R76" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W76" s="2">
         <v>46282</v>
@@ -6133,7 +6136,7 @@
         <v>263</v>
       </c>
       <c r="AA76" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="77" spans="1:27">
@@ -6168,10 +6171,10 @@
         <v>2</v>
       </c>
       <c r="K77">
-        <v>1559</v>
+        <v>1563</v>
       </c>
       <c r="L77" s="2">
-        <v>46283.18092592592</v>
+        <v>46284.15655092592</v>
       </c>
       <c r="M77" t="s">
         <v>262</v>
@@ -6180,19 +6183,19 @@
         <v>256</v>
       </c>
       <c r="O77" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P77" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q77" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R77" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W77" s="2">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="Y77" t="s">
         <v>261</v>
@@ -6201,7 +6204,7 @@
         <v>263</v>
       </c>
       <c r="AA77" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="78" spans="1:27">
@@ -6239,7 +6242,7 @@
         <v>1565</v>
       </c>
       <c r="L78" s="2">
-        <v>46283.18092592592</v>
+        <v>46284.15655092592</v>
       </c>
       <c r="M78" t="s">
         <v>263</v>
@@ -6248,16 +6251,16 @@
         <v>256</v>
       </c>
       <c r="O78" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P78" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q78" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R78" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W78" s="2">
         <v>46276</v>
@@ -6269,7 +6272,7 @@
         <v>263</v>
       </c>
       <c r="AA78" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="79" spans="1:27">
@@ -6304,10 +6307,10 @@
         <v>8</v>
       </c>
       <c r="K79">
-        <v>1783</v>
+        <v>1799</v>
       </c>
       <c r="L79" s="2">
-        <v>46283.18092592592</v>
+        <v>46284.15655092592</v>
       </c>
       <c r="M79" t="s">
         <v>261</v>
@@ -6316,16 +6319,16 @@
         <v>256</v>
       </c>
       <c r="O79" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P79" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q79" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R79" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W79" s="2">
         <v>46283</v>
@@ -6337,7 +6340,7 @@
         <v>263</v>
       </c>
       <c r="AA79" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="80" spans="1:27">
@@ -6369,31 +6372,31 @@
         <v>1</v>
       </c>
       <c r="J80">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K80">
         <v>1576</v>
       </c>
       <c r="L80" s="2">
-        <v>46283.18092592592</v>
+        <v>46284.15655092592</v>
       </c>
       <c r="M80" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N80" t="s">
         <v>256</v>
       </c>
       <c r="O80" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P80" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q80" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R80" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W80" s="2">
         <v>46280</v>
@@ -6405,7 +6408,7 @@
         <v>263</v>
       </c>
       <c r="AA80" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="81" spans="1:27">
@@ -6443,7 +6446,7 @@
         <v>3591</v>
       </c>
       <c r="L81" s="2">
-        <v>46283.18092592592</v>
+        <v>46284.15655092592</v>
       </c>
       <c r="M81" t="s">
         <v>263</v>
@@ -6452,16 +6455,16 @@
         <v>256</v>
       </c>
       <c r="O81" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P81" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q81" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R81" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W81" s="2">
         <v>46160</v>
@@ -6473,7 +6476,7 @@
         <v>263</v>
       </c>
       <c r="AA81" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="82" spans="1:27">
@@ -6520,16 +6523,16 @@
         <v>257</v>
       </c>
       <c r="O82" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P82" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q82" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R82" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W82" s="2">
         <v>46161</v>
@@ -6579,16 +6582,16 @@
         <v>257</v>
       </c>
       <c r="O83" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P83" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q83" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R83" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W83" s="2">
         <v>46168</v>
@@ -6638,16 +6641,16 @@
         <v>257</v>
       </c>
       <c r="O84" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P84" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q84" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R84" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W84" s="2">
         <v>46164</v>
@@ -6697,16 +6700,16 @@
         <v>257</v>
       </c>
       <c r="O85" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P85" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q85" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R85" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W85" s="2">
         <v>46168</v>
@@ -6747,7 +6750,7 @@
         <v>652</v>
       </c>
       <c r="L86" s="2">
-        <v>46283.18092592592</v>
+        <v>46284.15655092592</v>
       </c>
       <c r="M86" t="s">
         <v>263</v>
@@ -6756,16 +6759,16 @@
         <v>256</v>
       </c>
       <c r="O86" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P86" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q86" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R86" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W86" s="2">
         <v>46164</v>
@@ -6777,7 +6780,7 @@
         <v>263</v>
       </c>
       <c r="AA86" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="87" spans="1:27">
@@ -6815,7 +6818,7 @@
         <v>3609</v>
       </c>
       <c r="L87" s="2">
-        <v>46283.18092592592</v>
+        <v>46284.15655092592</v>
       </c>
       <c r="M87" t="s">
         <v>263</v>
@@ -6824,16 +6827,16 @@
         <v>256</v>
       </c>
       <c r="O87" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P87" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q87" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R87" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W87" s="2">
         <v>46248</v>
@@ -6845,7 +6848,7 @@
         <v>263</v>
       </c>
       <c r="AA87" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="88" spans="1:27">
@@ -6883,7 +6886,7 @@
         <v>3580</v>
       </c>
       <c r="L88" s="2">
-        <v>46283.18092592592</v>
+        <v>46284.15655092592</v>
       </c>
       <c r="M88" t="s">
         <v>263</v>
@@ -6892,16 +6895,16 @@
         <v>256</v>
       </c>
       <c r="O88" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P88" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q88" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R88" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W88" s="2">
         <v>46253.16666666666</v>
@@ -6913,7 +6916,7 @@
         <v>263</v>
       </c>
       <c r="AA88" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="89" spans="1:27">
@@ -6945,16 +6948,16 @@
         <v>257</v>
       </c>
       <c r="O89" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P89" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q89" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R89" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="90" spans="1:27">
@@ -6992,7 +6995,7 @@
         <v>125</v>
       </c>
       <c r="L90" s="2">
-        <v>46283.18092592592</v>
+        <v>46284.15655092592</v>
       </c>
       <c r="M90" t="s">
         <v>264</v>
@@ -7001,16 +7004,16 @@
         <v>256</v>
       </c>
       <c r="O90" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P90" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q90" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R90" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W90" s="2">
         <v>46154</v>
@@ -7051,16 +7054,16 @@
         <v>256</v>
       </c>
       <c r="O91" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P91" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q91" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R91" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W91" s="2">
         <v>46154</v>
@@ -7110,16 +7113,16 @@
         <v>257</v>
       </c>
       <c r="O92" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P92" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q92" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R92" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="W92" s="2">
         <v>46164</v>

--- a/sites.xlsx
+++ b/sites.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1368" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1368" uniqueCount="274">
   <si>
     <t>site_name</t>
   </si>
@@ -811,9 +811,6 @@
     <t>FAIL</t>
   </si>
   <si>
-    <t>CHECK_REQUIRED</t>
-  </si>
-  <si>
     <t>STEP2-3</t>
   </si>
   <si>
@@ -839,9 +836,6 @@
   </si>
   <si>
     <t>selenium:detail_date</t>
-  </si>
-  <si>
-    <t>RECENT_HINT_BUT_ZERO</t>
   </si>
 </sst>
 </file>
@@ -1320,16 +1314,16 @@
         <v>257</v>
       </c>
       <c r="O2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W2" s="2">
         <v>46155</v>
@@ -1382,16 +1376,16 @@
         <v>257</v>
       </c>
       <c r="O3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W3" s="2">
         <v>46087</v>
@@ -1444,16 +1438,16 @@
         <v>257</v>
       </c>
       <c r="O4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W4" s="2">
         <v>46168</v>
@@ -1506,16 +1500,16 @@
         <v>257</v>
       </c>
       <c r="O5" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P5" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R5" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W5" s="2">
         <v>46161</v>
@@ -1559,7 +1553,7 @@
         <v>169</v>
       </c>
       <c r="L6" s="2">
-        <v>46284.15655092592</v>
+        <v>46286.20085648148</v>
       </c>
       <c r="M6" t="s">
         <v>263</v>
@@ -1568,16 +1562,16 @@
         <v>256</v>
       </c>
       <c r="O6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W6" s="2">
         <v>46168</v>
@@ -1639,16 +1633,16 @@
         <v>257</v>
       </c>
       <c r="O7" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P7" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R7" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W7" s="2">
         <v>46164</v>
@@ -1701,16 +1695,16 @@
         <v>257</v>
       </c>
       <c r="O8" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P8" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q8" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R8" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W8" s="2">
         <v>46155</v>
@@ -1763,16 +1757,16 @@
         <v>257</v>
       </c>
       <c r="O9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P9" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q9" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R9" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W9" s="2">
         <v>46045</v>
@@ -1825,16 +1819,16 @@
         <v>257</v>
       </c>
       <c r="O10" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P10" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q10" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R10" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W10" s="2">
         <v>46045</v>
@@ -1887,16 +1881,16 @@
         <v>257</v>
       </c>
       <c r="O11" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P11" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q11" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R11" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W11" s="2">
         <v>46129</v>
@@ -1949,16 +1943,16 @@
         <v>257</v>
       </c>
       <c r="O12" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P12" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R12" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W12" s="2">
         <v>46164</v>
@@ -2002,7 +1996,7 @@
         <v>170</v>
       </c>
       <c r="L13" s="2">
-        <v>46284.15655092592</v>
+        <v>46286.20085648148</v>
       </c>
       <c r="M13" t="s">
         <v>264</v>
@@ -2011,16 +2005,16 @@
         <v>256</v>
       </c>
       <c r="O13" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P13" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q13" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R13" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W13" s="2">
         <v>46254</v>
@@ -2032,7 +2026,7 @@
         <v>261</v>
       </c>
       <c r="Z13" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="14" spans="1:27">
@@ -2067,10 +2061,10 @@
         <v>1</v>
       </c>
       <c r="K14">
-        <v>3544</v>
+        <v>3547</v>
       </c>
       <c r="L14" s="2">
-        <v>46284.15655092592</v>
+        <v>46286.20085648148</v>
       </c>
       <c r="M14" t="s">
         <v>262</v>
@@ -2079,16 +2073,16 @@
         <v>256</v>
       </c>
       <c r="O14" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P14" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q14" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R14" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W14" s="2">
         <v>46280</v>
@@ -2100,7 +2094,7 @@
         <v>263</v>
       </c>
       <c r="AA14" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="15" spans="1:27">
@@ -2135,10 +2129,10 @@
         <v>1</v>
       </c>
       <c r="K15">
-        <v>3535</v>
+        <v>3538</v>
       </c>
       <c r="L15" s="2">
-        <v>46284.15655092592</v>
+        <v>46286.20085648148</v>
       </c>
       <c r="M15" t="s">
         <v>262</v>
@@ -2147,16 +2141,16 @@
         <v>256</v>
       </c>
       <c r="O15" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P15" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q15" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R15" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W15" s="2">
         <v>46279</v>
@@ -2168,7 +2162,7 @@
         <v>263</v>
       </c>
       <c r="AA15" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="16" spans="1:27">
@@ -2203,10 +2197,10 @@
         <v>2</v>
       </c>
       <c r="K16">
-        <v>3594</v>
+        <v>3600</v>
       </c>
       <c r="L16" s="2">
-        <v>46284.15655092592</v>
+        <v>46286.20085648148</v>
       </c>
       <c r="M16" t="s">
         <v>262</v>
@@ -2215,16 +2209,16 @@
         <v>256</v>
       </c>
       <c r="O16" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P16" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q16" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R16" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W16" s="2">
         <v>46281</v>
@@ -2236,7 +2230,7 @@
         <v>263</v>
       </c>
       <c r="AA16" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="17" spans="1:27">
@@ -2283,16 +2277,16 @@
         <v>257</v>
       </c>
       <c r="O17" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P17" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q17" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R17" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W17" s="2">
         <v>46113</v>
@@ -2327,43 +2321,43 @@
         <v>1</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18">
-        <v>3630</v>
+        <v>3633</v>
       </c>
       <c r="L18" s="2">
-        <v>46284.15655092592</v>
+        <v>46286.20085648148</v>
       </c>
       <c r="M18" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="N18" t="s">
         <v>256</v>
       </c>
       <c r="O18" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P18" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q18" t="s">
+        <v>270</v>
+      </c>
+      <c r="R18" t="s">
+        <v>268</v>
+      </c>
+      <c r="W18" s="2">
+        <v>46285</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>261</v>
+      </c>
+      <c r="Z18" t="s">
         <v>271</v>
       </c>
-      <c r="R18" t="s">
-        <v>269</v>
-      </c>
-      <c r="W18" s="2">
-        <v>46278</v>
-      </c>
-      <c r="Y18" t="s">
-        <v>261</v>
-      </c>
-      <c r="Z18" t="s">
+      <c r="AA18" t="s">
         <v>272</v>
-      </c>
-      <c r="AA18" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="19" spans="1:27">
@@ -2410,16 +2404,16 @@
         <v>257</v>
       </c>
       <c r="O19" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P19" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q19" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R19" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W19" s="2">
         <v>46163</v>
@@ -2469,16 +2463,16 @@
         <v>257</v>
       </c>
       <c r="O20" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P20" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q20" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R20" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W20" s="2">
         <v>46165</v>
@@ -2528,16 +2522,16 @@
         <v>257</v>
       </c>
       <c r="O21" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P21" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q21" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R21" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W21" s="2">
         <v>46166</v>
@@ -2578,7 +2572,7 @@
         <v>3591</v>
       </c>
       <c r="L22" s="2">
-        <v>46284.15655092592</v>
+        <v>46286.20085648148</v>
       </c>
       <c r="M22" t="s">
         <v>263</v>
@@ -2587,16 +2581,16 @@
         <v>256</v>
       </c>
       <c r="O22" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P22" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q22" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R22" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W22" s="2">
         <v>46168</v>
@@ -2608,7 +2602,7 @@
         <v>263</v>
       </c>
       <c r="AA22" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="23" spans="1:27">
@@ -2646,7 +2640,7 @@
         <v>3591</v>
       </c>
       <c r="L23" s="2">
-        <v>46284.15655092592</v>
+        <v>46286.20085648148</v>
       </c>
       <c r="M23" t="s">
         <v>263</v>
@@ -2655,16 +2649,16 @@
         <v>256</v>
       </c>
       <c r="O23" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q23" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W23" s="2">
         <v>46168</v>
@@ -2676,7 +2670,7 @@
         <v>263</v>
       </c>
       <c r="AA23" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="24" spans="1:27">
@@ -2714,7 +2708,7 @@
         <v>131</v>
       </c>
       <c r="L24" s="2">
-        <v>46284.15655092592</v>
+        <v>46286.20085648148</v>
       </c>
       <c r="M24" t="s">
         <v>263</v>
@@ -2723,16 +2717,16 @@
         <v>256</v>
       </c>
       <c r="O24" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P24" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q24" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R24" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W24" s="2">
         <v>46257</v>
@@ -2782,7 +2776,7 @@
         <v>145</v>
       </c>
       <c r="L25" s="2">
-        <v>46284.15655092592</v>
+        <v>46286.20085648148</v>
       </c>
       <c r="M25" t="s">
         <v>263</v>
@@ -2791,16 +2785,16 @@
         <v>256</v>
       </c>
       <c r="O25" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P25" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q25" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R25" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W25" s="2">
         <v>46272</v>
@@ -2844,31 +2838,31 @@
         <v>1</v>
       </c>
       <c r="J26">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K26">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="L26" s="2">
-        <v>46284.15655092592</v>
+        <v>46286.20085648148</v>
       </c>
       <c r="M26" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N26" t="s">
         <v>256</v>
       </c>
       <c r="O26" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P26" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q26" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R26" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W26" s="2">
         <v>46283</v>
@@ -2880,7 +2874,7 @@
         <v>263</v>
       </c>
       <c r="AA26" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="27" spans="1:27">
@@ -2927,16 +2921,16 @@
         <v>257</v>
       </c>
       <c r="O27" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P27" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q27" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R27" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W27" s="2">
         <v>46172</v>
@@ -2986,16 +2980,16 @@
         <v>257</v>
       </c>
       <c r="O28" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P28" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q28" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R28" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W28" s="2">
         <v>46164</v>
@@ -3045,16 +3039,16 @@
         <v>257</v>
       </c>
       <c r="O29" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P29" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q29" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R29" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W29" s="2">
         <v>46168</v>
@@ -3104,16 +3098,16 @@
         <v>257</v>
       </c>
       <c r="O30" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P30" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q30" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R30" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W30" s="2">
         <v>46168</v>
@@ -3163,16 +3157,16 @@
         <v>257</v>
       </c>
       <c r="O31" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P31" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q31" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R31" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W31" s="2">
         <v>46168</v>
@@ -3207,43 +3201,43 @@
         <v>1</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="K32">
-        <v>14043</v>
+        <v>14289</v>
       </c>
       <c r="L32" s="2">
-        <v>46284.15655092592</v>
+        <v>46286.20085648148</v>
       </c>
       <c r="M32" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="N32" t="s">
         <v>256</v>
       </c>
       <c r="O32" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P32" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q32" t="s">
+        <v>270</v>
+      </c>
+      <c r="R32" t="s">
+        <v>268</v>
+      </c>
+      <c r="W32" s="2">
+        <v>46286</v>
+      </c>
+      <c r="Y32" t="s">
+        <v>261</v>
+      </c>
+      <c r="Z32" t="s">
         <v>271</v>
       </c>
-      <c r="R32" t="s">
-        <v>269</v>
-      </c>
-      <c r="W32" s="2">
-        <v>46283</v>
-      </c>
-      <c r="Y32" t="s">
-        <v>261</v>
-      </c>
-      <c r="Z32" t="s">
+      <c r="AA32" t="s">
         <v>272</v>
-      </c>
-      <c r="AA32" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="33" spans="1:27">
@@ -3290,16 +3284,16 @@
         <v>257</v>
       </c>
       <c r="O33" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P33" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q33" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R33" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W33" s="2">
         <v>46168</v>
@@ -3349,16 +3343,16 @@
         <v>257</v>
       </c>
       <c r="O34" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P34" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R34" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W34" s="2">
         <v>46168</v>
@@ -3399,7 +3393,7 @@
         <v>3591</v>
       </c>
       <c r="L35" s="2">
-        <v>46284.15655092592</v>
+        <v>46286.20085648148</v>
       </c>
       <c r="M35" t="s">
         <v>263</v>
@@ -3408,16 +3402,16 @@
         <v>256</v>
       </c>
       <c r="O35" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P35" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q35" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R35" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W35" s="2">
         <v>46157</v>
@@ -3429,7 +3423,7 @@
         <v>263</v>
       </c>
       <c r="AA35" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="36" spans="1:27">
@@ -3467,7 +3461,7 @@
         <v>3591</v>
       </c>
       <c r="L36" s="2">
-        <v>46284.15655092592</v>
+        <v>46286.20085648148</v>
       </c>
       <c r="M36" t="s">
         <v>263</v>
@@ -3476,16 +3470,16 @@
         <v>256</v>
       </c>
       <c r="O36" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P36" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q36" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R36" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W36" s="2">
         <v>46168</v>
@@ -3497,7 +3491,7 @@
         <v>263</v>
       </c>
       <c r="AA36" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="37" spans="1:27">
@@ -3535,7 +3529,7 @@
         <v>1826</v>
       </c>
       <c r="L37" s="2">
-        <v>46284.15655092592</v>
+        <v>46286.20085648148</v>
       </c>
       <c r="M37" t="s">
         <v>263</v>
@@ -3544,16 +3538,16 @@
         <v>256</v>
       </c>
       <c r="O37" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P37" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q37" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R37" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W37" s="2">
         <v>46132</v>
@@ -3565,7 +3559,7 @@
         <v>263</v>
       </c>
       <c r="AA37" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="38" spans="1:27">
@@ -3603,7 +3597,7 @@
         <v>2937</v>
       </c>
       <c r="L38" s="2">
-        <v>46284.15655092592</v>
+        <v>46286.20085648148</v>
       </c>
       <c r="M38" t="s">
         <v>263</v>
@@ -3612,16 +3606,16 @@
         <v>256</v>
       </c>
       <c r="O38" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P38" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q38" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R38" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W38" s="2">
         <v>46113</v>
@@ -3633,7 +3627,7 @@
         <v>263</v>
       </c>
       <c r="AA38" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="39" spans="1:27">
@@ -3671,7 +3665,7 @@
         <v>3176</v>
       </c>
       <c r="L39" s="2">
-        <v>46284.15655092592</v>
+        <v>46286.20085648148</v>
       </c>
       <c r="M39" t="s">
         <v>263</v>
@@ -3680,16 +3674,16 @@
         <v>256</v>
       </c>
       <c r="O39" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P39" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q39" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R39" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W39" s="2">
         <v>46140</v>
@@ -3701,7 +3695,7 @@
         <v>263</v>
       </c>
       <c r="AA39" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="40" spans="1:27">
@@ -3739,7 +3733,7 @@
         <v>3128</v>
       </c>
       <c r="L40" s="2">
-        <v>46284.15655092592</v>
+        <v>46286.20085648148</v>
       </c>
       <c r="M40" t="s">
         <v>263</v>
@@ -3748,16 +3742,16 @@
         <v>256</v>
       </c>
       <c r="O40" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P40" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q40" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R40" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W40" s="2">
         <v>46024</v>
@@ -3769,7 +3763,7 @@
         <v>263</v>
       </c>
       <c r="AA40" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="41" spans="1:27">
@@ -3807,7 +3801,7 @@
         <v>3542</v>
       </c>
       <c r="L41" s="2">
-        <v>46284.15655092592</v>
+        <v>46286.20085648148</v>
       </c>
       <c r="M41" t="s">
         <v>263</v>
@@ -3816,16 +3810,16 @@
         <v>256</v>
       </c>
       <c r="O41" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P41" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q41" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R41" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W41" s="2">
         <v>46168</v>
@@ -3837,7 +3831,7 @@
         <v>263</v>
       </c>
       <c r="AA41" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="42" spans="1:27">
@@ -3875,7 +3869,7 @@
         <v>3533</v>
       </c>
       <c r="L42" s="2">
-        <v>46284.15655092592</v>
+        <v>46286.20085648148</v>
       </c>
       <c r="M42" t="s">
         <v>263</v>
@@ -3884,16 +3878,16 @@
         <v>256</v>
       </c>
       <c r="O42" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P42" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q42" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R42" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W42" s="2">
         <v>46164</v>
@@ -3905,7 +3899,7 @@
         <v>263</v>
       </c>
       <c r="AA42" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="43" spans="1:27">
@@ -3943,7 +3937,7 @@
         <v>3513</v>
       </c>
       <c r="L43" s="2">
-        <v>46284.15655092592</v>
+        <v>46286.20085648148</v>
       </c>
       <c r="M43" t="s">
         <v>263</v>
@@ -3952,16 +3946,16 @@
         <v>256</v>
       </c>
       <c r="O43" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P43" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q43" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R43" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W43" s="2">
         <v>46112</v>
@@ -3973,7 +3967,7 @@
         <v>263</v>
       </c>
       <c r="AA43" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="44" spans="1:27">
@@ -4020,16 +4014,16 @@
         <v>257</v>
       </c>
       <c r="O44" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P44" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q44" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R44" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W44" s="2">
         <v>46171</v>
@@ -4064,13 +4058,13 @@
         <v>1</v>
       </c>
       <c r="J45">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="K45">
-        <v>3681</v>
+        <v>3698</v>
       </c>
       <c r="L45" s="2">
-        <v>46284.15655092592</v>
+        <v>46286.20085648148</v>
       </c>
       <c r="M45" t="s">
         <v>261</v>
@@ -4079,16 +4073,16 @@
         <v>256</v>
       </c>
       <c r="O45" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P45" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q45" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R45" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W45" s="2">
         <v>46283</v>
@@ -4100,7 +4094,7 @@
         <v>263</v>
       </c>
       <c r="AA45" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="46" spans="1:27">
@@ -4132,13 +4126,13 @@
         <v>1</v>
       </c>
       <c r="J46">
-        <v>74</v>
+        <v>26</v>
       </c>
       <c r="K46">
-        <v>9333</v>
+        <v>9439</v>
       </c>
       <c r="L46" s="2">
-        <v>46284.15655092592</v>
+        <v>46286.20085648148</v>
       </c>
       <c r="M46" t="s">
         <v>261</v>
@@ -4147,16 +4141,16 @@
         <v>256</v>
       </c>
       <c r="O46" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P46" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q46" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R46" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W46" s="2">
         <v>46283</v>
@@ -4168,7 +4162,7 @@
         <v>263</v>
       </c>
       <c r="AA46" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="47" spans="1:27">
@@ -4203,10 +4197,10 @@
         <v>18</v>
       </c>
       <c r="K47">
-        <v>4575</v>
+        <v>4629</v>
       </c>
       <c r="L47" s="2">
-        <v>46284.15655092592</v>
+        <v>46286.20085648148</v>
       </c>
       <c r="M47" t="s">
         <v>261</v>
@@ -4215,16 +4209,16 @@
         <v>256</v>
       </c>
       <c r="O47" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P47" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q47" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R47" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W47" s="2">
         <v>46283</v>
@@ -4236,7 +4230,7 @@
         <v>263</v>
       </c>
       <c r="AA47" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="48" spans="1:27">
@@ -4274,7 +4268,7 @@
         <v>2299</v>
       </c>
       <c r="L48" s="2">
-        <v>46284.15655092592</v>
+        <v>46286.20085648148</v>
       </c>
       <c r="M48" t="s">
         <v>263</v>
@@ -4283,16 +4277,16 @@
         <v>256</v>
       </c>
       <c r="O48" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P48" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q48" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R48" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W48" s="2">
         <v>46168</v>
@@ -4304,7 +4298,7 @@
         <v>263</v>
       </c>
       <c r="AA48" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="49" spans="1:27">
@@ -4342,7 +4336,7 @@
         <v>1505</v>
       </c>
       <c r="L49" s="2">
-        <v>46284.15655092592</v>
+        <v>46286.20085648148</v>
       </c>
       <c r="M49" t="s">
         <v>263</v>
@@ -4351,16 +4345,16 @@
         <v>256</v>
       </c>
       <c r="O49" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P49" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q49" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R49" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W49" s="2">
         <v>46273</v>
@@ -4372,7 +4366,7 @@
         <v>263</v>
       </c>
       <c r="AA49" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="50" spans="1:27">
@@ -4410,7 +4404,7 @@
         <v>1765</v>
       </c>
       <c r="L50" s="2">
-        <v>46284.15655092592</v>
+        <v>46286.20085648148</v>
       </c>
       <c r="M50" t="s">
         <v>263</v>
@@ -4419,16 +4413,16 @@
         <v>256</v>
       </c>
       <c r="O50" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P50" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q50" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R50" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W50" s="2">
         <v>46280</v>
@@ -4440,7 +4434,7 @@
         <v>263</v>
       </c>
       <c r="AA50" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="51" spans="1:27">
@@ -4472,31 +4466,31 @@
         <v>1</v>
       </c>
       <c r="J51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K51">
         <v>1509</v>
       </c>
       <c r="L51" s="2">
-        <v>46284.15655092592</v>
+        <v>46286.20085648148</v>
       </c>
       <c r="M51" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N51" t="s">
         <v>256</v>
       </c>
       <c r="O51" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P51" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q51" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R51" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W51" s="2">
         <v>46281</v>
@@ -4508,7 +4502,7 @@
         <v>263</v>
       </c>
       <c r="AA51" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="52" spans="1:27">
@@ -4546,7 +4540,7 @@
         <v>1466</v>
       </c>
       <c r="L52" s="2">
-        <v>46284.15655092592</v>
+        <v>46286.20085648148</v>
       </c>
       <c r="M52" t="s">
         <v>263</v>
@@ -4555,16 +4549,16 @@
         <v>256</v>
       </c>
       <c r="O52" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P52" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q52" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R52" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W52" s="2">
         <v>46142</v>
@@ -4576,7 +4570,7 @@
         <v>263</v>
       </c>
       <c r="AA52" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="53" spans="1:27">
@@ -4608,31 +4602,31 @@
         <v>1</v>
       </c>
       <c r="J53">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K53">
-        <v>2180</v>
+        <v>2182</v>
       </c>
       <c r="L53" s="2">
-        <v>46284.15655092592</v>
+        <v>46286.20085648148</v>
       </c>
       <c r="M53" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="N53" t="s">
         <v>256</v>
       </c>
       <c r="O53" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P53" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q53" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R53" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W53" s="2">
         <v>46282</v>
@@ -4644,7 +4638,7 @@
         <v>263</v>
       </c>
       <c r="AA53" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="54" spans="1:27">
@@ -4676,31 +4670,31 @@
         <v>1</v>
       </c>
       <c r="J54">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K54">
         <v>1380</v>
       </c>
       <c r="L54" s="2">
-        <v>46284.15655092592</v>
+        <v>46286.20085648148</v>
       </c>
       <c r="M54" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N54" t="s">
         <v>256</v>
       </c>
       <c r="O54" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P54" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q54" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R54" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W54" s="2">
         <v>46281</v>
@@ -4712,7 +4706,7 @@
         <v>263</v>
       </c>
       <c r="AA54" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="55" spans="1:27">
@@ -4744,31 +4738,31 @@
         <v>1</v>
       </c>
       <c r="J55">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K55">
-        <v>2385</v>
+        <v>2394</v>
       </c>
       <c r="L55" s="2">
-        <v>46284.15655092592</v>
+        <v>46286.20085648148</v>
       </c>
       <c r="M55" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="N55" t="s">
         <v>256</v>
       </c>
       <c r="O55" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P55" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q55" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R55" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W55" s="2">
         <v>46282</v>
@@ -4777,10 +4771,10 @@
         <v>261</v>
       </c>
       <c r="Z55" t="s">
+        <v>271</v>
+      </c>
+      <c r="AA55" t="s">
         <v>272</v>
-      </c>
-      <c r="AA55" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="56" spans="1:27">
@@ -4827,16 +4821,16 @@
         <v>257</v>
       </c>
       <c r="O56" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P56" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q56" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R56" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W56" s="2">
         <v>46161</v>
@@ -4874,10 +4868,10 @@
         <v>2</v>
       </c>
       <c r="K57">
-        <v>3985</v>
+        <v>3991</v>
       </c>
       <c r="L57" s="2">
-        <v>46284.15655092592</v>
+        <v>46286.20085648148</v>
       </c>
       <c r="M57" t="s">
         <v>262</v>
@@ -4886,16 +4880,16 @@
         <v>256</v>
       </c>
       <c r="O57" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P57" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q57" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R57" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W57" s="2">
         <v>46283</v>
@@ -4907,7 +4901,7 @@
         <v>263</v>
       </c>
       <c r="AA57" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="58" spans="1:27">
@@ -4954,16 +4948,16 @@
         <v>257</v>
       </c>
       <c r="O58" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P58" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q58" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R58" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W58" s="2">
         <v>46148</v>
@@ -5013,16 +5007,16 @@
         <v>257</v>
       </c>
       <c r="O59" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P59" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q59" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R59" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W59" s="2">
         <v>46168</v>
@@ -5072,16 +5066,16 @@
         <v>257</v>
       </c>
       <c r="O60" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P60" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q60" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R60" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W60" s="2">
         <v>46164</v>
@@ -5131,16 +5125,16 @@
         <v>257</v>
       </c>
       <c r="O61" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P61" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q61" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R61" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W61" s="2">
         <v>46168</v>
@@ -5181,7 +5175,7 @@
         <v>1671</v>
       </c>
       <c r="L62" s="2">
-        <v>46284.15655092592</v>
+        <v>46286.20085648148</v>
       </c>
       <c r="M62" t="s">
         <v>263</v>
@@ -5190,16 +5184,16 @@
         <v>256</v>
       </c>
       <c r="O62" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P62" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q62" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R62" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W62" s="2">
         <v>46280</v>
@@ -5211,7 +5205,7 @@
         <v>263</v>
       </c>
       <c r="AA62" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="63" spans="1:27">
@@ -5258,16 +5252,16 @@
         <v>257</v>
       </c>
       <c r="O63" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P63" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q63" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R63" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W63" s="2">
         <v>46164</v>
@@ -5317,16 +5311,16 @@
         <v>257</v>
       </c>
       <c r="O64" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P64" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q64" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R64" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W64" s="2">
         <v>46168</v>
@@ -5361,13 +5355,13 @@
         <v>1</v>
       </c>
       <c r="J65">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K65">
-        <v>4603</v>
+        <v>4640</v>
       </c>
       <c r="L65" s="2">
-        <v>46284.15655092592</v>
+        <v>46286.20085648148</v>
       </c>
       <c r="M65" t="s">
         <v>261</v>
@@ -5376,28 +5370,28 @@
         <v>256</v>
       </c>
       <c r="O65" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P65" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q65" t="s">
+        <v>270</v>
+      </c>
+      <c r="R65" t="s">
+        <v>268</v>
+      </c>
+      <c r="W65" s="2">
+        <v>46285</v>
+      </c>
+      <c r="Y65" t="s">
+        <v>261</v>
+      </c>
+      <c r="Z65" t="s">
         <v>271</v>
       </c>
-      <c r="R65" t="s">
-        <v>269</v>
-      </c>
-      <c r="W65" s="2">
-        <v>46283</v>
-      </c>
-      <c r="Y65" t="s">
-        <v>261</v>
-      </c>
-      <c r="Z65" t="s">
+      <c r="AA65" t="s">
         <v>272</v>
-      </c>
-      <c r="AA65" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="66" spans="1:27">
@@ -5435,7 +5429,7 @@
         <v>3062</v>
       </c>
       <c r="L66" s="2">
-        <v>46284.15655092592</v>
+        <v>46286.20085648148</v>
       </c>
       <c r="M66" t="s">
         <v>263</v>
@@ -5444,16 +5438,16 @@
         <v>256</v>
       </c>
       <c r="O66" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P66" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q66" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R66" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W66" s="2">
         <v>46261</v>
@@ -5465,7 +5459,7 @@
         <v>263</v>
       </c>
       <c r="AA66" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="67" spans="1:27">
@@ -5503,7 +5497,7 @@
         <v>1755</v>
       </c>
       <c r="L67" s="2">
-        <v>46284.15655092592</v>
+        <v>46286.20085648148</v>
       </c>
       <c r="M67" t="s">
         <v>263</v>
@@ -5512,16 +5506,16 @@
         <v>256</v>
       </c>
       <c r="O67" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P67" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q67" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R67" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W67" s="2">
         <v>46280</v>
@@ -5530,10 +5524,10 @@
         <v>261</v>
       </c>
       <c r="Z67" t="s">
+        <v>271</v>
+      </c>
+      <c r="AA67" t="s">
         <v>272</v>
-      </c>
-      <c r="AA67" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="68" spans="1:27">
@@ -5565,13 +5559,13 @@
         <v>1</v>
       </c>
       <c r="J68">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K68">
-        <v>4242</v>
+        <v>4264</v>
       </c>
       <c r="L68" s="2">
-        <v>46284.15655092592</v>
+        <v>46286.20085648148</v>
       </c>
       <c r="M68" t="s">
         <v>261</v>
@@ -5580,28 +5574,28 @@
         <v>256</v>
       </c>
       <c r="O68" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P68" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q68" t="s">
+        <v>270</v>
+      </c>
+      <c r="R68" t="s">
+        <v>268</v>
+      </c>
+      <c r="W68" s="2">
+        <v>46286</v>
+      </c>
+      <c r="Y68" t="s">
+        <v>261</v>
+      </c>
+      <c r="Z68" t="s">
         <v>271</v>
       </c>
-      <c r="R68" t="s">
-        <v>269</v>
-      </c>
-      <c r="W68" s="2">
-        <v>46283</v>
-      </c>
-      <c r="Y68" t="s">
-        <v>261</v>
-      </c>
-      <c r="Z68" t="s">
+      <c r="AA68" t="s">
         <v>272</v>
-      </c>
-      <c r="AA68" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="69" spans="1:27">
@@ -5639,7 +5633,7 @@
         <v>3069</v>
       </c>
       <c r="L69" s="2">
-        <v>46284.15655092592</v>
+        <v>46286.20085648148</v>
       </c>
       <c r="M69" t="s">
         <v>263</v>
@@ -5648,16 +5642,16 @@
         <v>256</v>
       </c>
       <c r="O69" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P69" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q69" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R69" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W69" s="2">
         <v>46280</v>
@@ -5669,7 +5663,7 @@
         <v>263</v>
       </c>
       <c r="AA69" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="70" spans="1:27">
@@ -5701,43 +5695,43 @@
         <v>1</v>
       </c>
       <c r="J70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K70">
-        <v>2612</v>
+        <v>2613</v>
       </c>
       <c r="L70" s="2">
-        <v>46284.15655092592</v>
+        <v>46286.20085648148</v>
       </c>
       <c r="M70" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="N70" t="s">
         <v>256</v>
       </c>
       <c r="O70" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P70" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q70" t="s">
+        <v>270</v>
+      </c>
+      <c r="R70" t="s">
+        <v>268</v>
+      </c>
+      <c r="W70" s="2">
+        <v>46286</v>
+      </c>
+      <c r="Y70" t="s">
+        <v>261</v>
+      </c>
+      <c r="Z70" t="s">
         <v>271</v>
       </c>
-      <c r="R70" t="s">
-        <v>269</v>
-      </c>
-      <c r="W70" s="2">
-        <v>46283</v>
-      </c>
-      <c r="Y70" t="s">
-        <v>261</v>
-      </c>
-      <c r="Z70" t="s">
+      <c r="AA70" t="s">
         <v>272</v>
-      </c>
-      <c r="AA70" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="71" spans="1:27">
@@ -5772,10 +5766,10 @@
         <v>6</v>
       </c>
       <c r="K71">
-        <v>2663</v>
+        <v>2681</v>
       </c>
       <c r="L71" s="2">
-        <v>46284.15655092592</v>
+        <v>46286.20085648148</v>
       </c>
       <c r="M71" t="s">
         <v>261</v>
@@ -5784,16 +5778,16 @@
         <v>256</v>
       </c>
       <c r="O71" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P71" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q71" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R71" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W71" s="2">
         <v>46283</v>
@@ -5802,10 +5796,10 @@
         <v>261</v>
       </c>
       <c r="Z71" t="s">
+        <v>271</v>
+      </c>
+      <c r="AA71" t="s">
         <v>272</v>
-      </c>
-      <c r="AA71" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="72" spans="1:27">
@@ -5852,16 +5846,16 @@
         <v>257</v>
       </c>
       <c r="O72" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P72" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q72" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R72" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W72" s="2">
         <v>46164</v>
@@ -5899,10 +5893,10 @@
         <v>2</v>
       </c>
       <c r="K73">
-        <v>1377</v>
+        <v>1383</v>
       </c>
       <c r="L73" s="2">
-        <v>46284.15655092592</v>
+        <v>46286.20085648148</v>
       </c>
       <c r="M73" t="s">
         <v>262</v>
@@ -5911,16 +5905,16 @@
         <v>256</v>
       </c>
       <c r="O73" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P73" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q73" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R73" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W73" s="2">
         <v>46283</v>
@@ -5932,7 +5926,7 @@
         <v>263</v>
       </c>
       <c r="AA73" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="74" spans="1:27">
@@ -5970,7 +5964,7 @@
         <v>1449</v>
       </c>
       <c r="L74" s="2">
-        <v>46284.15655092592</v>
+        <v>46286.20085648148</v>
       </c>
       <c r="M74" t="s">
         <v>263</v>
@@ -5979,16 +5973,16 @@
         <v>256</v>
       </c>
       <c r="O74" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P74" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q74" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R74" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W74" s="2">
         <v>46185</v>
@@ -6000,7 +5994,7 @@
         <v>263</v>
       </c>
       <c r="AA74" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="75" spans="1:27">
@@ -6038,7 +6032,7 @@
         <v>1482</v>
       </c>
       <c r="L75" s="2">
-        <v>46284.15655092592</v>
+        <v>46286.20085648148</v>
       </c>
       <c r="M75" t="s">
         <v>263</v>
@@ -6047,16 +6041,16 @@
         <v>256</v>
       </c>
       <c r="O75" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P75" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q75" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R75" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W75" s="2">
         <v>46265</v>
@@ -6068,7 +6062,7 @@
         <v>263</v>
       </c>
       <c r="AA75" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="76" spans="1:27">
@@ -6100,31 +6094,31 @@
         <v>1</v>
       </c>
       <c r="J76">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K76">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="L76" s="2">
-        <v>46284.15655092592</v>
+        <v>46286.20085648148</v>
       </c>
       <c r="M76" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N76" t="s">
         <v>256</v>
       </c>
       <c r="O76" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P76" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q76" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R76" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W76" s="2">
         <v>46282</v>
@@ -6136,7 +6130,7 @@
         <v>263</v>
       </c>
       <c r="AA76" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="77" spans="1:27">
@@ -6168,13 +6162,13 @@
         <v>1</v>
       </c>
       <c r="J77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K77">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="L77" s="2">
-        <v>46284.15655092592</v>
+        <v>46286.20085648148</v>
       </c>
       <c r="M77" t="s">
         <v>262</v>
@@ -6183,16 +6177,16 @@
         <v>256</v>
       </c>
       <c r="O77" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P77" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q77" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R77" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W77" s="2">
         <v>46283</v>
@@ -6204,7 +6198,7 @@
         <v>263</v>
       </c>
       <c r="AA77" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="78" spans="1:27">
@@ -6242,7 +6236,7 @@
         <v>1565</v>
       </c>
       <c r="L78" s="2">
-        <v>46284.15655092592</v>
+        <v>46286.20085648148</v>
       </c>
       <c r="M78" t="s">
         <v>263</v>
@@ -6251,16 +6245,16 @@
         <v>256</v>
       </c>
       <c r="O78" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P78" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q78" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R78" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W78" s="2">
         <v>46276</v>
@@ -6272,7 +6266,7 @@
         <v>263</v>
       </c>
       <c r="AA78" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="79" spans="1:27">
@@ -6304,13 +6298,13 @@
         <v>1</v>
       </c>
       <c r="J79">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K79">
-        <v>1799</v>
+        <v>1810</v>
       </c>
       <c r="L79" s="2">
-        <v>46284.15655092592</v>
+        <v>46286.20085648148</v>
       </c>
       <c r="M79" t="s">
         <v>261</v>
@@ -6319,16 +6313,16 @@
         <v>256</v>
       </c>
       <c r="O79" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P79" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q79" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R79" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W79" s="2">
         <v>46283</v>
@@ -6340,7 +6334,7 @@
         <v>263</v>
       </c>
       <c r="AA79" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="80" spans="1:27">
@@ -6378,7 +6372,7 @@
         <v>1576</v>
       </c>
       <c r="L80" s="2">
-        <v>46284.15655092592</v>
+        <v>46286.20085648148</v>
       </c>
       <c r="M80" t="s">
         <v>263</v>
@@ -6387,16 +6381,16 @@
         <v>256</v>
       </c>
       <c r="O80" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P80" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q80" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R80" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W80" s="2">
         <v>46280</v>
@@ -6408,7 +6402,7 @@
         <v>263</v>
       </c>
       <c r="AA80" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="81" spans="1:27">
@@ -6446,7 +6440,7 @@
         <v>3591</v>
       </c>
       <c r="L81" s="2">
-        <v>46284.15655092592</v>
+        <v>46286.20085648148</v>
       </c>
       <c r="M81" t="s">
         <v>263</v>
@@ -6455,16 +6449,16 @@
         <v>256</v>
       </c>
       <c r="O81" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P81" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q81" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R81" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W81" s="2">
         <v>46160</v>
@@ -6476,7 +6470,7 @@
         <v>263</v>
       </c>
       <c r="AA81" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="82" spans="1:27">
@@ -6523,16 +6517,16 @@
         <v>257</v>
       </c>
       <c r="O82" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P82" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q82" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R82" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W82" s="2">
         <v>46161</v>
@@ -6582,16 +6576,16 @@
         <v>257</v>
       </c>
       <c r="O83" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P83" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q83" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R83" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W83" s="2">
         <v>46168</v>
@@ -6641,16 +6635,16 @@
         <v>257</v>
       </c>
       <c r="O84" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P84" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q84" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R84" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W84" s="2">
         <v>46164</v>
@@ -6700,16 +6694,16 @@
         <v>257</v>
       </c>
       <c r="O85" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P85" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q85" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R85" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W85" s="2">
         <v>46168</v>
@@ -6750,7 +6744,7 @@
         <v>652</v>
       </c>
       <c r="L86" s="2">
-        <v>46284.15655092592</v>
+        <v>46286.20085648148</v>
       </c>
       <c r="M86" t="s">
         <v>263</v>
@@ -6759,16 +6753,16 @@
         <v>256</v>
       </c>
       <c r="O86" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P86" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q86" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R86" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W86" s="2">
         <v>46164</v>
@@ -6780,7 +6774,7 @@
         <v>263</v>
       </c>
       <c r="AA86" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="87" spans="1:27">
@@ -6818,7 +6812,7 @@
         <v>3609</v>
       </c>
       <c r="L87" s="2">
-        <v>46284.15655092592</v>
+        <v>46286.20085648148</v>
       </c>
       <c r="M87" t="s">
         <v>263</v>
@@ -6827,16 +6821,16 @@
         <v>256</v>
       </c>
       <c r="O87" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P87" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q87" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R87" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W87" s="2">
         <v>46248</v>
@@ -6848,7 +6842,7 @@
         <v>263</v>
       </c>
       <c r="AA87" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="88" spans="1:27">
@@ -6886,7 +6880,7 @@
         <v>3580</v>
       </c>
       <c r="L88" s="2">
-        <v>46284.15655092592</v>
+        <v>46286.20085648148</v>
       </c>
       <c r="M88" t="s">
         <v>263</v>
@@ -6895,16 +6889,16 @@
         <v>256</v>
       </c>
       <c r="O88" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P88" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q88" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R88" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W88" s="2">
         <v>46253.16666666666</v>
@@ -6916,7 +6910,7 @@
         <v>263</v>
       </c>
       <c r="AA88" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="89" spans="1:27">
@@ -6948,16 +6942,16 @@
         <v>257</v>
       </c>
       <c r="O89" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P89" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q89" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R89" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="90" spans="1:27">
@@ -6995,7 +6989,7 @@
         <v>125</v>
       </c>
       <c r="L90" s="2">
-        <v>46284.15655092592</v>
+        <v>46286.20085648148</v>
       </c>
       <c r="M90" t="s">
         <v>264</v>
@@ -7004,16 +6998,16 @@
         <v>256</v>
       </c>
       <c r="O90" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P90" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q90" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R90" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W90" s="2">
         <v>46154</v>
@@ -7054,16 +7048,16 @@
         <v>256</v>
       </c>
       <c r="O91" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P91" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q91" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R91" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W91" s="2">
         <v>46154</v>
@@ -7113,16 +7107,16 @@
         <v>257</v>
       </c>
       <c r="O92" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P92" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q92" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R92" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W92" s="2">
         <v>46164</v>

--- a/sites.xlsx
+++ b/sites.xlsx
@@ -1553,7 +1553,7 @@
         <v>169</v>
       </c>
       <c r="L6" s="2">
-        <v>46286.20085648148</v>
+        <v>46288.26234953704</v>
       </c>
       <c r="M6" t="s">
         <v>263</v>
@@ -1996,7 +1996,7 @@
         <v>170</v>
       </c>
       <c r="L13" s="2">
-        <v>46286.20085648148</v>
+        <v>46288.26234953704</v>
       </c>
       <c r="M13" t="s">
         <v>264</v>
@@ -2058,16 +2058,16 @@
         <v>1</v>
       </c>
       <c r="J14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14">
-        <v>3547</v>
+        <v>3549</v>
       </c>
       <c r="L14" s="2">
-        <v>46286.20085648148</v>
+        <v>46288.26234953704</v>
       </c>
       <c r="M14" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N14" t="s">
         <v>256</v>
@@ -2126,16 +2126,16 @@
         <v>1</v>
       </c>
       <c r="J15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15">
         <v>3538</v>
       </c>
       <c r="L15" s="2">
-        <v>46286.20085648148</v>
+        <v>46288.26234953704</v>
       </c>
       <c r="M15" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N15" t="s">
         <v>256</v>
@@ -2194,13 +2194,13 @@
         <v>1</v>
       </c>
       <c r="J16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K16">
-        <v>3600</v>
+        <v>3604</v>
       </c>
       <c r="L16" s="2">
-        <v>46286.20085648148</v>
+        <v>46288.26234953704</v>
       </c>
       <c r="M16" t="s">
         <v>262</v>
@@ -2324,10 +2324,10 @@
         <v>1</v>
       </c>
       <c r="K18">
-        <v>3633</v>
+        <v>3637</v>
       </c>
       <c r="L18" s="2">
-        <v>46286.20085648148</v>
+        <v>46288.26234953704</v>
       </c>
       <c r="M18" t="s">
         <v>262</v>
@@ -2572,7 +2572,7 @@
         <v>3591</v>
       </c>
       <c r="L22" s="2">
-        <v>46286.20085648148</v>
+        <v>46288.26234953704</v>
       </c>
       <c r="M22" t="s">
         <v>263</v>
@@ -2640,7 +2640,7 @@
         <v>3591</v>
       </c>
       <c r="L23" s="2">
-        <v>46286.20085648148</v>
+        <v>46288.26234953704</v>
       </c>
       <c r="M23" t="s">
         <v>263</v>
@@ -2708,7 +2708,7 @@
         <v>131</v>
       </c>
       <c r="L24" s="2">
-        <v>46286.20085648148</v>
+        <v>46288.26234953704</v>
       </c>
       <c r="M24" t="s">
         <v>263</v>
@@ -2776,7 +2776,7 @@
         <v>145</v>
       </c>
       <c r="L25" s="2">
-        <v>46286.20085648148</v>
+        <v>46288.26234953704</v>
       </c>
       <c r="M25" t="s">
         <v>263</v>
@@ -2841,10 +2841,10 @@
         <v>1</v>
       </c>
       <c r="K26">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="L26" s="2">
-        <v>46286.20085648148</v>
+        <v>46288.26234953704</v>
       </c>
       <c r="M26" t="s">
         <v>262</v>
@@ -2865,7 +2865,7 @@
         <v>268</v>
       </c>
       <c r="W26" s="2">
-        <v>46283</v>
+        <v>46287</v>
       </c>
       <c r="Y26" t="s">
         <v>261</v>
@@ -3201,13 +3201,13 @@
         <v>1</v>
       </c>
       <c r="J32">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K32">
-        <v>14289</v>
+        <v>14839</v>
       </c>
       <c r="L32" s="2">
-        <v>46286.20085648148</v>
+        <v>46288.26234953704</v>
       </c>
       <c r="M32" t="s">
         <v>261</v>
@@ -3228,7 +3228,7 @@
         <v>268</v>
       </c>
       <c r="W32" s="2">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="Y32" t="s">
         <v>261</v>
@@ -3393,7 +3393,7 @@
         <v>3591</v>
       </c>
       <c r="L35" s="2">
-        <v>46286.20085648148</v>
+        <v>46288.26234953704</v>
       </c>
       <c r="M35" t="s">
         <v>263</v>
@@ -3461,7 +3461,7 @@
         <v>3591</v>
       </c>
       <c r="L36" s="2">
-        <v>46286.20085648148</v>
+        <v>46288.26234953704</v>
       </c>
       <c r="M36" t="s">
         <v>263</v>
@@ -3523,16 +3523,16 @@
         <v>1</v>
       </c>
       <c r="J37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37">
-        <v>1826</v>
+        <v>1827</v>
       </c>
       <c r="L37" s="2">
-        <v>46286.20085648148</v>
+        <v>46288.26234953704</v>
       </c>
       <c r="M37" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="N37" t="s">
         <v>256</v>
@@ -3550,7 +3550,7 @@
         <v>268</v>
       </c>
       <c r="W37" s="2">
-        <v>46132</v>
+        <v>46285</v>
       </c>
       <c r="Y37" t="s">
         <v>261</v>
@@ -3597,7 +3597,7 @@
         <v>2937</v>
       </c>
       <c r="L38" s="2">
-        <v>46286.20085648148</v>
+        <v>46288.26234953704</v>
       </c>
       <c r="M38" t="s">
         <v>263</v>
@@ -3665,7 +3665,7 @@
         <v>3176</v>
       </c>
       <c r="L39" s="2">
-        <v>46286.20085648148</v>
+        <v>46288.26234953704</v>
       </c>
       <c r="M39" t="s">
         <v>263</v>
@@ -3733,7 +3733,7 @@
         <v>3128</v>
       </c>
       <c r="L40" s="2">
-        <v>46286.20085648148</v>
+        <v>46288.26234953704</v>
       </c>
       <c r="M40" t="s">
         <v>263</v>
@@ -3801,7 +3801,7 @@
         <v>3542</v>
       </c>
       <c r="L41" s="2">
-        <v>46286.20085648148</v>
+        <v>46288.26234953704</v>
       </c>
       <c r="M41" t="s">
         <v>263</v>
@@ -3869,7 +3869,7 @@
         <v>3533</v>
       </c>
       <c r="L42" s="2">
-        <v>46286.20085648148</v>
+        <v>46288.26234953704</v>
       </c>
       <c r="M42" t="s">
         <v>263</v>
@@ -3937,7 +3937,7 @@
         <v>3513</v>
       </c>
       <c r="L43" s="2">
-        <v>46286.20085648148</v>
+        <v>46288.26234953704</v>
       </c>
       <c r="M43" t="s">
         <v>263</v>
@@ -4058,13 +4058,13 @@
         <v>1</v>
       </c>
       <c r="J45">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="K45">
-        <v>3698</v>
+        <v>3740</v>
       </c>
       <c r="L45" s="2">
-        <v>46286.20085648148</v>
+        <v>46288.26234953704</v>
       </c>
       <c r="M45" t="s">
         <v>261</v>
@@ -4085,7 +4085,7 @@
         <v>268</v>
       </c>
       <c r="W45" s="2">
-        <v>46283</v>
+        <v>46287</v>
       </c>
       <c r="Y45" t="s">
         <v>261</v>
@@ -4126,13 +4126,13 @@
         <v>1</v>
       </c>
       <c r="J46">
-        <v>26</v>
+        <v>83</v>
       </c>
       <c r="K46">
-        <v>9439</v>
+        <v>9683</v>
       </c>
       <c r="L46" s="2">
-        <v>46286.20085648148</v>
+        <v>46288.26234953704</v>
       </c>
       <c r="M46" t="s">
         <v>261</v>
@@ -4153,7 +4153,7 @@
         <v>268</v>
       </c>
       <c r="W46" s="2">
-        <v>46283</v>
+        <v>46287</v>
       </c>
       <c r="Y46" t="s">
         <v>261</v>
@@ -4194,13 +4194,13 @@
         <v>1</v>
       </c>
       <c r="J47">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K47">
-        <v>4629</v>
+        <v>4707</v>
       </c>
       <c r="L47" s="2">
-        <v>46286.20085648148</v>
+        <v>46288.26234953704</v>
       </c>
       <c r="M47" t="s">
         <v>261</v>
@@ -4221,7 +4221,7 @@
         <v>268</v>
       </c>
       <c r="W47" s="2">
-        <v>46283</v>
+        <v>46287</v>
       </c>
       <c r="Y47" t="s">
         <v>261</v>
@@ -4268,7 +4268,7 @@
         <v>2299</v>
       </c>
       <c r="L48" s="2">
-        <v>46286.20085648148</v>
+        <v>46288.26234953704</v>
       </c>
       <c r="M48" t="s">
         <v>263</v>
@@ -4330,16 +4330,16 @@
         <v>1</v>
       </c>
       <c r="J49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K49">
-        <v>1505</v>
+        <v>1509</v>
       </c>
       <c r="L49" s="2">
-        <v>46286.20085648148</v>
+        <v>46288.26234953704</v>
       </c>
       <c r="M49" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="N49" t="s">
         <v>256</v>
@@ -4357,7 +4357,7 @@
         <v>268</v>
       </c>
       <c r="W49" s="2">
-        <v>46273</v>
+        <v>46286</v>
       </c>
       <c r="Y49" t="s">
         <v>261</v>
@@ -4404,7 +4404,7 @@
         <v>1765</v>
       </c>
       <c r="L50" s="2">
-        <v>46286.20085648148</v>
+        <v>46288.26234953704</v>
       </c>
       <c r="M50" t="s">
         <v>263</v>
@@ -4466,16 +4466,16 @@
         <v>1</v>
       </c>
       <c r="J51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K51">
-        <v>1509</v>
+        <v>1511</v>
       </c>
       <c r="L51" s="2">
-        <v>46286.20085648148</v>
+        <v>46288.26234953704</v>
       </c>
       <c r="M51" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="N51" t="s">
         <v>256</v>
@@ -4493,7 +4493,7 @@
         <v>268</v>
       </c>
       <c r="W51" s="2">
-        <v>46281</v>
+        <v>46286</v>
       </c>
       <c r="Y51" t="s">
         <v>261</v>
@@ -4540,7 +4540,7 @@
         <v>1466</v>
       </c>
       <c r="L52" s="2">
-        <v>46286.20085648148</v>
+        <v>46288.26234953704</v>
       </c>
       <c r="M52" t="s">
         <v>263</v>
@@ -4602,16 +4602,16 @@
         <v>1</v>
       </c>
       <c r="J53">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K53">
-        <v>2182</v>
+        <v>2194</v>
       </c>
       <c r="L53" s="2">
-        <v>46286.20085648148</v>
+        <v>46288.26234953704</v>
       </c>
       <c r="M53" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="N53" t="s">
         <v>256</v>
@@ -4629,7 +4629,7 @@
         <v>268</v>
       </c>
       <c r="W53" s="2">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="Y53" t="s">
         <v>261</v>
@@ -4670,16 +4670,16 @@
         <v>1</v>
       </c>
       <c r="J54">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K54">
-        <v>1380</v>
+        <v>1386</v>
       </c>
       <c r="L54" s="2">
-        <v>46286.20085648148</v>
+        <v>46288.26234953704</v>
       </c>
       <c r="M54" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="N54" t="s">
         <v>256</v>
@@ -4697,7 +4697,7 @@
         <v>268</v>
       </c>
       <c r="W54" s="2">
-        <v>46281</v>
+        <v>46287</v>
       </c>
       <c r="Y54" t="s">
         <v>261</v>
@@ -4738,16 +4738,16 @@
         <v>1</v>
       </c>
       <c r="J55">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K55">
-        <v>2394</v>
+        <v>2434</v>
       </c>
       <c r="L55" s="2">
-        <v>46286.20085648148</v>
+        <v>46288.26234953704</v>
       </c>
       <c r="M55" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="N55" t="s">
         <v>256</v>
@@ -4765,7 +4765,7 @@
         <v>268</v>
       </c>
       <c r="W55" s="2">
-        <v>46282</v>
+        <v>46287</v>
       </c>
       <c r="Y55" t="s">
         <v>261</v>
@@ -4865,16 +4865,16 @@
         <v>1</v>
       </c>
       <c r="J57">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K57">
         <v>3991</v>
       </c>
       <c r="L57" s="2">
-        <v>46286.20085648148</v>
+        <v>46288.26234953704</v>
       </c>
       <c r="M57" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N57" t="s">
         <v>256</v>
@@ -5169,16 +5169,16 @@
         <v>1</v>
       </c>
       <c r="J62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K62">
-        <v>1671</v>
+        <v>1675</v>
       </c>
       <c r="L62" s="2">
-        <v>46286.20085648148</v>
+        <v>46288.26234953704</v>
       </c>
       <c r="M62" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="N62" t="s">
         <v>256</v>
@@ -5196,7 +5196,7 @@
         <v>268</v>
       </c>
       <c r="W62" s="2">
-        <v>46280</v>
+        <v>46286</v>
       </c>
       <c r="Y62" t="s">
         <v>261</v>
@@ -5355,13 +5355,13 @@
         <v>1</v>
       </c>
       <c r="J65">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="K65">
-        <v>4640</v>
+        <v>4692</v>
       </c>
       <c r="L65" s="2">
-        <v>46286.20085648148</v>
+        <v>46288.26234953704</v>
       </c>
       <c r="M65" t="s">
         <v>261</v>
@@ -5382,7 +5382,7 @@
         <v>268</v>
       </c>
       <c r="W65" s="2">
-        <v>46285</v>
+        <v>46287</v>
       </c>
       <c r="Y65" t="s">
         <v>261</v>
@@ -5429,7 +5429,7 @@
         <v>3062</v>
       </c>
       <c r="L66" s="2">
-        <v>46286.20085648148</v>
+        <v>46288.26234953704</v>
       </c>
       <c r="M66" t="s">
         <v>263</v>
@@ -5491,16 +5491,16 @@
         <v>1</v>
       </c>
       <c r="J67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K67">
-        <v>1755</v>
+        <v>1759</v>
       </c>
       <c r="L67" s="2">
-        <v>46286.20085648148</v>
+        <v>46288.26234953704</v>
       </c>
       <c r="M67" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="N67" t="s">
         <v>256</v>
@@ -5518,7 +5518,7 @@
         <v>268</v>
       </c>
       <c r="W67" s="2">
-        <v>46280</v>
+        <v>46287</v>
       </c>
       <c r="Y67" t="s">
         <v>261</v>
@@ -5562,10 +5562,10 @@
         <v>8</v>
       </c>
       <c r="K68">
-        <v>4264</v>
+        <v>4293</v>
       </c>
       <c r="L68" s="2">
-        <v>46286.20085648148</v>
+        <v>46288.26234953704</v>
       </c>
       <c r="M68" t="s">
         <v>261</v>
@@ -5586,7 +5586,7 @@
         <v>268</v>
       </c>
       <c r="W68" s="2">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="Y68" t="s">
         <v>261</v>
@@ -5633,7 +5633,7 @@
         <v>3069</v>
       </c>
       <c r="L69" s="2">
-        <v>46286.20085648148</v>
+        <v>46288.26234953704</v>
       </c>
       <c r="M69" t="s">
         <v>263</v>
@@ -5695,16 +5695,16 @@
         <v>1</v>
       </c>
       <c r="J70">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="K70">
-        <v>2613</v>
+        <v>2663</v>
       </c>
       <c r="L70" s="2">
-        <v>46286.20085648148</v>
+        <v>46288.26234953704</v>
       </c>
       <c r="M70" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="N70" t="s">
         <v>256</v>
@@ -5722,7 +5722,7 @@
         <v>268</v>
       </c>
       <c r="W70" s="2">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="Y70" t="s">
         <v>261</v>
@@ -5763,13 +5763,13 @@
         <v>1</v>
       </c>
       <c r="J71">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K71">
-        <v>2681</v>
+        <v>2719</v>
       </c>
       <c r="L71" s="2">
-        <v>46286.20085648148</v>
+        <v>46288.26234953704</v>
       </c>
       <c r="M71" t="s">
         <v>261</v>
@@ -5790,7 +5790,7 @@
         <v>268</v>
       </c>
       <c r="W71" s="2">
-        <v>46283</v>
+        <v>46288</v>
       </c>
       <c r="Y71" t="s">
         <v>261</v>
@@ -5890,16 +5890,16 @@
         <v>1</v>
       </c>
       <c r="J73">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K73">
         <v>1383</v>
       </c>
       <c r="L73" s="2">
-        <v>46286.20085648148</v>
+        <v>46288.26234953704</v>
       </c>
       <c r="M73" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N73" t="s">
         <v>256</v>
@@ -5964,7 +5964,7 @@
         <v>1449</v>
       </c>
       <c r="L74" s="2">
-        <v>46286.20085648148</v>
+        <v>46288.26234953704</v>
       </c>
       <c r="M74" t="s">
         <v>263</v>
@@ -6032,7 +6032,7 @@
         <v>1482</v>
       </c>
       <c r="L75" s="2">
-        <v>46286.20085648148</v>
+        <v>46288.26234953704</v>
       </c>
       <c r="M75" t="s">
         <v>263</v>
@@ -6100,7 +6100,7 @@
         <v>1541</v>
       </c>
       <c r="L76" s="2">
-        <v>46286.20085648148</v>
+        <v>46288.26234953704</v>
       </c>
       <c r="M76" t="s">
         <v>263</v>
@@ -6162,13 +6162,13 @@
         <v>1</v>
       </c>
       <c r="J77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K77">
-        <v>1566</v>
+        <v>1574</v>
       </c>
       <c r="L77" s="2">
-        <v>46286.20085648148</v>
+        <v>46288.26234953704</v>
       </c>
       <c r="M77" t="s">
         <v>262</v>
@@ -6189,7 +6189,7 @@
         <v>268</v>
       </c>
       <c r="W77" s="2">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="Y77" t="s">
         <v>261</v>
@@ -6230,16 +6230,16 @@
         <v>1</v>
       </c>
       <c r="J78">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K78">
-        <v>1565</v>
+        <v>1571</v>
       </c>
       <c r="L78" s="2">
-        <v>46286.20085648148</v>
+        <v>46288.26234953704</v>
       </c>
       <c r="M78" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="N78" t="s">
         <v>256</v>
@@ -6257,7 +6257,7 @@
         <v>268</v>
       </c>
       <c r="W78" s="2">
-        <v>46276</v>
+        <v>46287</v>
       </c>
       <c r="Y78" t="s">
         <v>261</v>
@@ -6298,13 +6298,13 @@
         <v>1</v>
       </c>
       <c r="J79">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K79">
-        <v>1810</v>
+        <v>1832</v>
       </c>
       <c r="L79" s="2">
-        <v>46286.20085648148</v>
+        <v>46288.26234953704</v>
       </c>
       <c r="M79" t="s">
         <v>261</v>
@@ -6325,7 +6325,7 @@
         <v>268</v>
       </c>
       <c r="W79" s="2">
-        <v>46283</v>
+        <v>46287</v>
       </c>
       <c r="Y79" t="s">
         <v>261</v>
@@ -6372,7 +6372,7 @@
         <v>1576</v>
       </c>
       <c r="L80" s="2">
-        <v>46286.20085648148</v>
+        <v>46288.26234953704</v>
       </c>
       <c r="M80" t="s">
         <v>263</v>
@@ -6440,7 +6440,7 @@
         <v>3591</v>
       </c>
       <c r="L81" s="2">
-        <v>46286.20085648148</v>
+        <v>46288.26234953704</v>
       </c>
       <c r="M81" t="s">
         <v>263</v>
@@ -6744,7 +6744,7 @@
         <v>652</v>
       </c>
       <c r="L86" s="2">
-        <v>46286.20085648148</v>
+        <v>46288.26234953704</v>
       </c>
       <c r="M86" t="s">
         <v>263</v>
@@ -6812,7 +6812,7 @@
         <v>3609</v>
       </c>
       <c r="L87" s="2">
-        <v>46286.20085648148</v>
+        <v>46288.26234953704</v>
       </c>
       <c r="M87" t="s">
         <v>263</v>
@@ -6880,7 +6880,7 @@
         <v>3580</v>
       </c>
       <c r="L88" s="2">
-        <v>46286.20085648148</v>
+        <v>46288.26234953704</v>
       </c>
       <c r="M88" t="s">
         <v>263</v>
@@ -6989,7 +6989,7 @@
         <v>125</v>
       </c>
       <c r="L90" s="2">
-        <v>46286.20085648148</v>
+        <v>46288.26234953704</v>
       </c>
       <c r="M90" t="s">
         <v>264</v>
